--- a/research/traditional_assets/database/data/curacao/curacao_business_consumer_services.xlsx
+++ b/research/traditional_assets/database/data/curacao/curacao_business_consumer_services.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="enxtam_more" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -587,8 +589,29 @@
           <t>Business &amp; Consumer Services</t>
         </is>
       </c>
+      <c r="D2">
+        <v>-0.167</v>
+      </c>
+      <c r="E2">
+        <v>0.415</v>
+      </c>
+      <c r="G2">
+        <v>0.05464678178963893</v>
+      </c>
+      <c r="H2">
+        <v>0.05463108320251177</v>
+      </c>
+      <c r="I2">
+        <v>0.09921507064364207</v>
+      </c>
+      <c r="J2">
+        <v>0.07476065182302608</v>
+      </c>
       <c r="K2">
-        <v>0.513</v>
+        <v>3.82</v>
+      </c>
+      <c r="L2">
+        <v>0.05996860282574568</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,67 +635,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.014</v>
+        <v>0.492</v>
       </c>
       <c r="V2">
-        <v>0.0006698564593301436</v>
+        <v>0.01708333333333333</v>
       </c>
       <c r="W2">
-        <v>0.2035714285714286</v>
+        <v>0.7974947807933194</v>
       </c>
       <c r="X2">
-        <v>0.1307596670662203</v>
+        <v>0.1710016097480703</v>
       </c>
       <c r="Y2">
-        <v>0.07281176150520824</v>
+        <v>0.626493171045249</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>13.30131551472124</v>
       </c>
       <c r="AA2">
-        <v>-0.03971119133574007</v>
+        <v>0.9944150179842892</v>
       </c>
       <c r="AB2">
-        <v>0.1307596670662203</v>
+        <v>0.1076371918844786</v>
       </c>
       <c r="AC2">
-        <v>-0.1704708584019604</v>
+        <v>0.8867778260998106</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>32.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>32.4</v>
       </c>
       <c r="AG2">
-        <v>-0.014</v>
+        <v>31.908</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>0.6893617021276596</v>
       </c>
       <c r="AJ2">
-        <v>-0.0006703054677774586</v>
+        <v>0.5255979442577584</v>
       </c>
       <c r="AK2">
-        <v>-0.003052769297863062</v>
+        <v>0.6860755138900835</v>
       </c>
       <c r="AL2">
-        <v>0.125</v>
+        <v>1.45</v>
       </c>
       <c r="AM2">
-        <v>-0.07300000000000001</v>
+        <v>1.119</v>
       </c>
       <c r="AO2">
-        <v>-0.792</v>
+        <v>4.358620689655173</v>
       </c>
       <c r="AQ2">
-        <v>1.356164383561644</v>
+        <v>5.647899910634496</v>
       </c>
     </row>
     <row r="3">
@@ -691,8 +714,29 @@
           <t>Business &amp; Consumer Services</t>
         </is>
       </c>
+      <c r="D3">
+        <v>-0.167</v>
+      </c>
+      <c r="E3">
+        <v>0.415</v>
+      </c>
+      <c r="G3">
+        <v>0.05464678178963893</v>
+      </c>
+      <c r="H3">
+        <v>0.05463108320251177</v>
+      </c>
+      <c r="I3">
+        <v>0.09921507064364207</v>
+      </c>
+      <c r="J3">
+        <v>0.07476065182302608</v>
+      </c>
       <c r="K3">
-        <v>0.513</v>
+        <v>3.82</v>
+      </c>
+      <c r="L3">
+        <v>0.05996860282574568</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -716,67 +760,8832 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.014</v>
+        <v>0.492</v>
       </c>
       <c r="V3">
-        <v>0.0006698564593301436</v>
+        <v>0.01708333333333333</v>
       </c>
       <c r="W3">
-        <v>0.2035714285714286</v>
+        <v>0.7974947807933194</v>
       </c>
       <c r="X3">
-        <v>0.1307596670662203</v>
+        <v>0.1710016097480703</v>
       </c>
       <c r="Y3">
-        <v>0.07281176150520824</v>
+        <v>0.626493171045249</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>13.30131551472124</v>
       </c>
       <c r="AA3">
-        <v>-0.03971119133574007</v>
+        <v>0.9944150179842892</v>
       </c>
       <c r="AB3">
-        <v>0.1307596670662203</v>
+        <v>0.1076371918844786</v>
       </c>
       <c r="AC3">
-        <v>-0.1704708584019604</v>
+        <v>0.8867778260998106</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>32.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>32.4</v>
       </c>
       <c r="AG3">
-        <v>-0.014</v>
+        <v>31.908</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.6893617021276596</v>
       </c>
       <c r="AJ3">
-        <v>-0.0006703054677774586</v>
+        <v>0.5255979442577584</v>
       </c>
       <c r="AK3">
-        <v>-0.003052769297863062</v>
+        <v>0.6860755138900835</v>
       </c>
       <c r="AL3">
-        <v>0.125</v>
+        <v>1.45</v>
       </c>
       <c r="AM3">
-        <v>-0.07300000000000001</v>
+        <v>1.119</v>
       </c>
       <c r="AO3">
-        <v>-0.792</v>
+        <v>4.358620689655173</v>
       </c>
       <c r="AQ3">
-        <v>1.356164383561644</v>
+        <v>5.647899910634496</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Morefield Group N.V. (ENXTAM:MORE)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ENXTAM:MORE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Business &amp; Consumer Services</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>-4.29655172413793</v>
+      </c>
+      <c r="F2">
+        <v>-42.6287209467818</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="I2">
+        <v>0.529411764705882</v>
+      </c>
+      <c r="J2">
+        <v>0.01</v>
+      </c>
+      <c r="K2">
+        <v>28.8</v>
+      </c>
+      <c r="L2">
+        <v>41.0875513177959</v>
+      </c>
+      <c r="M2">
+        <v>60.708</v>
+      </c>
+      <c r="N2">
+        <v>41.2075513177959</v>
+      </c>
+      <c r="O2">
+        <v>32.4</v>
+      </c>
+      <c r="P2">
+        <v>0.612</v>
+      </c>
+      <c r="Q2">
+        <v>0.107637191884479</v>
+      </c>
+      <c r="R2">
+        <v>0.140212680717046</v>
+      </c>
+      <c r="S2">
+        <v>0.0513132648946194</v>
+      </c>
+      <c r="T2">
+        <v>2.47834248366013</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.17100160974807</v>
+      </c>
+      <c r="X2">
+        <v>0.116595207960045</v>
+      </c>
+      <c r="Y2">
+        <v>1.79022070836664</v>
+      </c>
+      <c r="Z2">
+        <v>1.05347122903543</v>
+      </c>
+      <c r="AA2">
+        <v>32.4</v>
+      </c>
+      <c r="AB2">
+        <v>0.06578623704438383</v>
+      </c>
+      <c r="AC2">
+        <v>-4.296551724137932</v>
+      </c>
+      <c r="AD2">
+        <v>32.4</v>
+      </c>
+      <c r="AE2">
+        <v>1.45</v>
+      </c>
+      <c r="AF2">
+        <v>6.23</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>28.8</v>
+      </c>
+      <c r="AK2">
+        <v>0.07384654256887045</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.22</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>7.848</v>
+      </c>
+      <c r="AR2">
+        <v>1.45</v>
+      </c>
+      <c r="AS2">
+        <v>32.4</v>
+      </c>
+      <c r="AT2">
+        <v>0.492</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>-32.4</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.492</v>
+      </c>
+      <c r="H2">
+        <v>28.8</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>6.23</v>
+      </c>
+      <c r="L2">
+        <v>-6.23</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>-6.23</v>
+      </c>
+      <c r="O2">
+        <v>-1.3706</v>
+      </c>
+      <c r="P2">
+        <v>-4.859400000000001</v>
+      </c>
+      <c r="Q2">
+        <v>1.3706</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-Inf</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1402126807170461</v>
+      </c>
+      <c r="C3">
+        <v>41.08755131779589</v>
+      </c>
+      <c r="D3">
+        <v>41.2075513177959</v>
+      </c>
+      <c r="E3">
+        <v>-31.788</v>
+      </c>
+      <c r="F3">
+        <v>0.612</v>
+      </c>
+      <c r="G3">
+        <v>0.492</v>
+      </c>
+      <c r="H3">
+        <v>28.8</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>6.23</v>
+      </c>
+      <c r="L3">
+        <v>-6.23</v>
+      </c>
+      <c r="M3">
+        <v>0.1461456</v>
+      </c>
+      <c r="N3">
+        <v>-6.3761456</v>
+      </c>
+      <c r="O3">
+        <v>-1.402752032</v>
+      </c>
+      <c r="P3">
+        <v>-4.973393568000001</v>
+      </c>
+      <c r="Q3">
+        <v>1.256606432</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1165952079600453</v>
+      </c>
+      <c r="T3">
+        <v>1.053471229035431</v>
+      </c>
+      <c r="U3">
+        <v>0.2388</v>
+      </c>
+      <c r="V3">
+        <v>-9.378318608292005</v>
+      </c>
+      <c r="W3">
+        <v>2.478342483660131</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>-42.62872094678183</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1422126807170461</v>
+      </c>
+      <c r="C4">
+        <v>39.67859777144027</v>
+      </c>
+      <c r="D4">
+        <v>40.41059777144027</v>
+      </c>
+      <c r="E4">
+        <v>-31.176</v>
+      </c>
+      <c r="F4">
+        <v>1.224</v>
+      </c>
+      <c r="G4">
+        <v>0.492</v>
+      </c>
+      <c r="H4">
+        <v>28.8</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>6.23</v>
+      </c>
+      <c r="L4">
+        <v>-6.23</v>
+      </c>
+      <c r="M4">
+        <v>0.2922912</v>
+      </c>
+      <c r="N4">
+        <v>-6.522291200000001</v>
+      </c>
+      <c r="O4">
+        <v>-1.434904064</v>
+      </c>
+      <c r="P4">
+        <v>-5.087387136</v>
+      </c>
+      <c r="Q4">
+        <v>1.142612864</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1173890366126988</v>
+      </c>
+      <c r="T4">
+        <v>1.06422093545416</v>
+      </c>
+      <c r="U4">
+        <v>0.2388</v>
+      </c>
+      <c r="V4">
+        <v>-4.689159304146003</v>
+      </c>
+      <c r="W4">
+        <v>1.358571241830066</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>-21.31436047339092</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1442126807170461</v>
+      </c>
+      <c r="C5">
+        <v>38.29988550311437</v>
+      </c>
+      <c r="D5">
+        <v>39.64388550311438</v>
+      </c>
+      <c r="E5">
+        <v>-30.564</v>
+      </c>
+      <c r="F5">
+        <v>1.836</v>
+      </c>
+      <c r="G5">
+        <v>0.492</v>
+      </c>
+      <c r="H5">
+        <v>28.8</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>6.23</v>
+      </c>
+      <c r="L5">
+        <v>-6.23</v>
+      </c>
+      <c r="M5">
+        <v>0.4384368</v>
+      </c>
+      <c r="N5">
+        <v>-6.6684368</v>
+      </c>
+      <c r="O5">
+        <v>-1.467056096</v>
+      </c>
+      <c r="P5">
+        <v>-5.201380704</v>
+      </c>
+      <c r="Q5">
+        <v>1.028619296</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1181992328664379</v>
+      </c>
+      <c r="T5">
+        <v>1.075192285304203</v>
+      </c>
+      <c r="U5">
+        <v>0.2388</v>
+      </c>
+      <c r="V5">
+        <v>-3.126106202764002</v>
+      </c>
+      <c r="W5">
+        <v>0.9853141612200436</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>-14.20957364892728</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1462126807170461</v>
+      </c>
+      <c r="C6">
+        <v>36.94972525539563</v>
+      </c>
+      <c r="D6">
+        <v>38.90572525539564</v>
+      </c>
+      <c r="E6">
+        <v>-29.952</v>
+      </c>
+      <c r="F6">
+        <v>2.448</v>
+      </c>
+      <c r="G6">
+        <v>0.492</v>
+      </c>
+      <c r="H6">
+        <v>28.8</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>6.23</v>
+      </c>
+      <c r="L6">
+        <v>-6.23</v>
+      </c>
+      <c r="M6">
+        <v>0.5845824000000001</v>
+      </c>
+      <c r="N6">
+        <v>-6.814582400000001</v>
+      </c>
+      <c r="O6">
+        <v>-1.499208128</v>
+      </c>
+      <c r="P6">
+        <v>-5.315374272000001</v>
+      </c>
+      <c r="Q6">
+        <v>0.9146257279999999</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1190263082087967</v>
+      </c>
+      <c r="T6">
+        <v>1.086392204942789</v>
+      </c>
+      <c r="U6">
+        <v>0.2388</v>
+      </c>
+      <c r="V6">
+        <v>-2.344579652073001</v>
+      </c>
+      <c r="W6">
+        <v>0.7986856209150328</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>-10.65718023669546</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1482126807170461</v>
+      </c>
+      <c r="C7">
+        <v>35.6265512854239</v>
+      </c>
+      <c r="D7">
+        <v>38.19455128542391</v>
+      </c>
+      <c r="E7">
+        <v>-29.34</v>
+      </c>
+      <c r="F7">
+        <v>3.06</v>
+      </c>
+      <c r="G7">
+        <v>0.492</v>
+      </c>
+      <c r="H7">
+        <v>28.8</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>6.23</v>
+      </c>
+      <c r="L7">
+        <v>-6.23</v>
+      </c>
+      <c r="M7">
+        <v>0.7307280000000002</v>
+      </c>
+      <c r="N7">
+        <v>-6.960728</v>
+      </c>
+      <c r="O7">
+        <v>-1.53136016</v>
+      </c>
+      <c r="P7">
+        <v>-5.42936784</v>
+      </c>
+      <c r="Q7">
+        <v>0.8006321600000001</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1198707956636261</v>
+      </c>
+      <c r="T7">
+        <v>1.097827912363239</v>
+      </c>
+      <c r="U7">
+        <v>0.2388</v>
+      </c>
+      <c r="V7">
+        <v>-1.875663721658401</v>
+      </c>
+      <c r="W7">
+        <v>0.6867084967320262</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>-8.525744189356367</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1502126807170461</v>
+      </c>
+      <c r="C8">
+        <v>34.32891027868023</v>
+      </c>
+      <c r="D8">
+        <v>37.50891027868023</v>
+      </c>
+      <c r="E8">
+        <v>-28.728</v>
+      </c>
+      <c r="F8">
+        <v>3.672</v>
+      </c>
+      <c r="G8">
+        <v>0.492</v>
+      </c>
+      <c r="H8">
+        <v>28.8</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>6.23</v>
+      </c>
+      <c r="L8">
+        <v>-6.23</v>
+      </c>
+      <c r="M8">
+        <v>0.8768736</v>
+      </c>
+      <c r="N8">
+        <v>-7.1068736</v>
+      </c>
+      <c r="O8">
+        <v>-1.563512192</v>
+      </c>
+      <c r="P8">
+        <v>-5.543361408</v>
+      </c>
+      <c r="Q8">
+        <v>0.6866385920000004</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1207332509366434</v>
+      </c>
+      <c r="T8">
+        <v>1.109506932707529</v>
+      </c>
+      <c r="U8">
+        <v>0.2388</v>
+      </c>
+      <c r="V8">
+        <v>-1.563053101382001</v>
+      </c>
+      <c r="W8">
+        <v>0.6120570806100217</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>-7.104786824463639</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1522126807170461</v>
+      </c>
+      <c r="C9">
+        <v>33.05545143577955</v>
+      </c>
+      <c r="D9">
+        <v>36.84745143577955</v>
+      </c>
+      <c r="E9">
+        <v>-28.116</v>
+      </c>
+      <c r="F9">
+        <v>4.284000000000001</v>
+      </c>
+      <c r="G9">
+        <v>0.492</v>
+      </c>
+      <c r="H9">
+        <v>28.8</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>6.23</v>
+      </c>
+      <c r="L9">
+        <v>-6.23</v>
+      </c>
+      <c r="M9">
+        <v>1.0230192</v>
+      </c>
+      <c r="N9">
+        <v>-7.253019200000001</v>
+      </c>
+      <c r="O9">
+        <v>-1.595664224</v>
+      </c>
+      <c r="P9">
+        <v>-5.657354976000001</v>
+      </c>
+      <c r="Q9">
+        <v>0.5726450239999998</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1216142536348869</v>
+      </c>
+      <c r="T9">
+        <v>1.121437114779653</v>
+      </c>
+      <c r="U9">
+        <v>0.2388</v>
+      </c>
+      <c r="V9">
+        <v>-1.339759801184572</v>
+      </c>
+      <c r="W9">
+        <v>0.5587346405228758</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>-6.08981727811169</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1542126807170461</v>
+      </c>
+      <c r="C10">
+        <v>31.80491758998634</v>
+      </c>
+      <c r="D10">
+        <v>36.20891758998634</v>
+      </c>
+      <c r="E10">
+        <v>-27.504</v>
+      </c>
+      <c r="F10">
+        <v>4.896</v>
+      </c>
+      <c r="G10">
+        <v>0.492</v>
+      </c>
+      <c r="H10">
+        <v>28.8</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>6.23</v>
+      </c>
+      <c r="L10">
+        <v>-6.23</v>
+      </c>
+      <c r="M10">
+        <v>1.1691648</v>
+      </c>
+      <c r="N10">
+        <v>-7.3991648</v>
+      </c>
+      <c r="O10">
+        <v>-1.627816256</v>
+      </c>
+      <c r="P10">
+        <v>-5.771348544</v>
+      </c>
+      <c r="Q10">
+        <v>0.4586514560000001</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1225144085657009</v>
+      </c>
+      <c r="T10">
+        <v>1.133626648635953</v>
+      </c>
+      <c r="U10">
+        <v>0.2388</v>
+      </c>
+      <c r="V10">
+        <v>-1.172289826036501</v>
+      </c>
+      <c r="W10">
+        <v>0.5187428104575164</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>-5.32859011834773</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1562126807170461</v>
+      </c>
+      <c r="C11">
+        <v>30.5761372325521</v>
+      </c>
+      <c r="D11">
+        <v>35.5921372325521</v>
+      </c>
+      <c r="E11">
+        <v>-26.892</v>
+      </c>
+      <c r="F11">
+        <v>5.508</v>
+      </c>
+      <c r="G11">
+        <v>0.492</v>
+      </c>
+      <c r="H11">
+        <v>28.8</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>6.23</v>
+      </c>
+      <c r="L11">
+        <v>-6.23</v>
+      </c>
+      <c r="M11">
+        <v>1.3153104</v>
+      </c>
+      <c r="N11">
+        <v>-7.5453104</v>
+      </c>
+      <c r="O11">
+        <v>-1.659968288</v>
+      </c>
+      <c r="P11">
+        <v>-5.885342112</v>
+      </c>
+      <c r="Q11">
+        <v>0.3446578880000004</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1234343471213679</v>
+      </c>
+      <c r="T11">
+        <v>1.14608408433525</v>
+      </c>
+      <c r="U11">
+        <v>0.2388</v>
+      </c>
+      <c r="V11">
+        <v>-1.042035400921334</v>
+      </c>
+      <c r="W11">
+        <v>0.4876380537400145</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>-4.736524549642427</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1582126807170461</v>
+      </c>
+      <c r="C12">
+        <v>29.36801733944143</v>
+      </c>
+      <c r="D12">
+        <v>34.99601733944143</v>
+      </c>
+      <c r="E12">
+        <v>-26.28</v>
+      </c>
+      <c r="F12">
+        <v>6.120000000000001</v>
+      </c>
+      <c r="G12">
+        <v>0.492</v>
+      </c>
+      <c r="H12">
+        <v>28.8</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>6.23</v>
+      </c>
+      <c r="L12">
+        <v>-6.23</v>
+      </c>
+      <c r="M12">
+        <v>1.461456</v>
+      </c>
+      <c r="N12">
+        <v>-7.691456000000001</v>
+      </c>
+      <c r="O12">
+        <v>-1.69212032</v>
+      </c>
+      <c r="P12">
+        <v>-5.999335680000001</v>
+      </c>
+      <c r="Q12">
+        <v>0.2306643199999998</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1243747287560498</v>
+      </c>
+      <c r="T12">
+        <v>1.158818351938974</v>
+      </c>
+      <c r="U12">
+        <v>0.2388</v>
+      </c>
+      <c r="V12">
+        <v>-0.9378318608292003</v>
+      </c>
+      <c r="W12">
+        <v>0.4627542483660131</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>-4.262872094678183</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1602126807170461</v>
+      </c>
+      <c r="C13">
+        <v>28.17953690703915</v>
+      </c>
+      <c r="D13">
+        <v>34.41953690703915</v>
+      </c>
+      <c r="E13">
+        <v>-25.668</v>
+      </c>
+      <c r="F13">
+        <v>6.732</v>
+      </c>
+      <c r="G13">
+        <v>0.492</v>
+      </c>
+      <c r="H13">
+        <v>28.8</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>6.23</v>
+      </c>
+      <c r="L13">
+        <v>-6.23</v>
+      </c>
+      <c r="M13">
+        <v>1.6076016</v>
+      </c>
+      <c r="N13">
+        <v>-7.837601600000001</v>
+      </c>
+      <c r="O13">
+        <v>-1.724272352</v>
+      </c>
+      <c r="P13">
+        <v>-6.113329248000001</v>
+      </c>
+      <c r="Q13">
+        <v>0.1166707519999992</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1253362425622975</v>
+      </c>
+      <c r="T13">
+        <v>1.171838782859637</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>-0.8525744189356368</v>
+      </c>
+      <c r="W13">
+        <v>0.4423947712418301</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>-3.875338267889259</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1622126807170461</v>
+      </c>
+      <c r="C14">
+        <v>27.00974111641121</v>
+      </c>
+      <c r="D14">
+        <v>33.86174111641121</v>
+      </c>
+      <c r="E14">
+        <v>-25.056</v>
+      </c>
+      <c r="F14">
+        <v>7.344</v>
+      </c>
+      <c r="G14">
+        <v>0.492</v>
+      </c>
+      <c r="H14">
+        <v>28.8</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>6.23</v>
+      </c>
+      <c r="L14">
+        <v>-6.23</v>
+      </c>
+      <c r="M14">
+        <v>1.7537472</v>
+      </c>
+      <c r="N14">
+        <v>-7.983747200000001</v>
+      </c>
+      <c r="O14">
+        <v>-1.756424384</v>
+      </c>
+      <c r="P14">
+        <v>-6.227322816000001</v>
+      </c>
+      <c r="Q14">
+        <v>0.0026771839999995</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1263196089550509</v>
+      </c>
+      <c r="T14">
+        <v>1.18515513266486</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>-0.7815265506910004</v>
+      </c>
+      <c r="W14">
+        <v>0.4254285403050109</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>-3.552393412231821</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1642126807170461</v>
+      </c>
+      <c r="C15">
+        <v>25.85773605595309</v>
+      </c>
+      <c r="D15">
+        <v>33.3217360559531</v>
+      </c>
+      <c r="E15">
+        <v>-24.444</v>
+      </c>
+      <c r="F15">
+        <v>7.956</v>
+      </c>
+      <c r="G15">
+        <v>0.492</v>
+      </c>
+      <c r="H15">
+        <v>28.8</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>6.23</v>
+      </c>
+      <c r="L15">
+        <v>-6.23</v>
+      </c>
+      <c r="M15">
+        <v>1.8998928</v>
+      </c>
+      <c r="N15">
+        <v>-8.1298928</v>
+      </c>
+      <c r="O15">
+        <v>-1.788576416</v>
+      </c>
+      <c r="P15">
+        <v>-6.341316384000001</v>
+      </c>
+      <c r="Q15">
+        <v>-0.1113163840000002</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1273255814717756</v>
+      </c>
+      <c r="T15">
+        <v>1.198777605454111</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>-0.7214091237147696</v>
+      </c>
+      <c r="W15">
+        <v>0.411072498743087</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>-3.27913238052168</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1662126807170461</v>
+      </c>
+      <c r="C16">
+        <v>24.72268394107054</v>
+      </c>
+      <c r="D16">
+        <v>32.79868394107054</v>
+      </c>
+      <c r="E16">
+        <v>-23.832</v>
+      </c>
+      <c r="F16">
+        <v>8.568000000000001</v>
+      </c>
+      <c r="G16">
+        <v>0.492</v>
+      </c>
+      <c r="H16">
+        <v>28.8</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>6.23</v>
+      </c>
+      <c r="L16">
+        <v>-6.23</v>
+      </c>
+      <c r="M16">
+        <v>2.0460384</v>
+      </c>
+      <c r="N16">
+        <v>-8.276038400000001</v>
+      </c>
+      <c r="O16">
+        <v>-1.820728448</v>
+      </c>
+      <c r="P16">
+        <v>-6.455309952</v>
+      </c>
+      <c r="Q16">
+        <v>-0.2253099519999999</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1283549486981916</v>
+      </c>
+      <c r="T16">
+        <v>1.212716879936136</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>-0.669879900592286</v>
+      </c>
+      <c r="W16">
+        <v>0.3987673202614379</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>-3.044908639055845</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1682126807170461</v>
+      </c>
+      <c r="C17">
+        <v>23.60379877712307</v>
+      </c>
+      <c r="D17">
+        <v>32.29179877712308</v>
+      </c>
+      <c r="E17">
+        <v>-23.22</v>
+      </c>
+      <c r="F17">
+        <v>9.18</v>
+      </c>
+      <c r="G17">
+        <v>0.492</v>
+      </c>
+      <c r="H17">
+        <v>28.8</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>6.23</v>
+      </c>
+      <c r="L17">
+        <v>-6.23</v>
+      </c>
+      <c r="M17">
+        <v>2.192184</v>
+      </c>
+      <c r="N17">
+        <v>-8.422184000000001</v>
+      </c>
+      <c r="O17">
+        <v>-1.85288048</v>
+      </c>
+      <c r="P17">
+        <v>-6.569303520000001</v>
+      </c>
+      <c r="Q17">
+        <v>-0.3393035200000005</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1294085363299351</v>
+      </c>
+      <c r="T17">
+        <v>1.22698413734715</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>-0.6252212405528004</v>
+      </c>
+      <c r="W17">
+        <v>0.3881028322440088</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>-2.841914729785457</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1702126807170461</v>
+      </c>
+      <c r="C18">
+        <v>22.50034241840755</v>
+      </c>
+      <c r="D18">
+        <v>31.80034241840755</v>
+      </c>
+      <c r="E18">
+        <v>-22.608</v>
+      </c>
+      <c r="F18">
+        <v>9.792</v>
+      </c>
+      <c r="G18">
+        <v>0.492</v>
+      </c>
+      <c r="H18">
+        <v>28.8</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>6.23</v>
+      </c>
+      <c r="L18">
+        <v>-6.23</v>
+      </c>
+      <c r="M18">
+        <v>2.3383296</v>
+      </c>
+      <c r="N18">
+        <v>-8.5683296</v>
+      </c>
+      <c r="O18">
+        <v>-1.885032512</v>
+      </c>
+      <c r="P18">
+        <v>-6.683297088</v>
+      </c>
+      <c r="Q18">
+        <v>-0.4532970879999993</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1304872093814819</v>
+      </c>
+      <c r="T18">
+        <v>1.241591091363187</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>-0.5861449130182503</v>
+      </c>
+      <c r="W18">
+        <v>0.3787714052287582</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>-2.664295059173865</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1722126807170461</v>
+      </c>
+      <c r="C19">
+        <v>21.41162098162219</v>
+      </c>
+      <c r="D19">
+        <v>31.32362098162219</v>
+      </c>
+      <c r="E19">
+        <v>-21.996</v>
+      </c>
+      <c r="F19">
+        <v>10.404</v>
+      </c>
+      <c r="G19">
+        <v>0.492</v>
+      </c>
+      <c r="H19">
+        <v>28.8</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>6.23</v>
+      </c>
+      <c r="L19">
+        <v>-6.23</v>
+      </c>
+      <c r="M19">
+        <v>2.4844752</v>
+      </c>
+      <c r="N19">
+        <v>-8.714475200000001</v>
+      </c>
+      <c r="O19">
+        <v>-1.917184544</v>
+      </c>
+      <c r="P19">
+        <v>-6.797290656</v>
+      </c>
+      <c r="Q19">
+        <v>-0.5672906559999999</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1315918745547528</v>
+      </c>
+      <c r="T19">
+        <v>1.256550020174792</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>-0.5516658004877649</v>
+      </c>
+      <c r="W19">
+        <v>0.3705377931564783</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>-2.507571820398931</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1742126807170461</v>
+      </c>
+      <c r="C20">
+        <v>20.33698157716236</v>
+      </c>
+      <c r="D20">
+        <v>30.86098157716236</v>
+      </c>
+      <c r="E20">
+        <v>-21.384</v>
+      </c>
+      <c r="F20">
+        <v>11.016</v>
+      </c>
+      <c r="G20">
+        <v>0.492</v>
+      </c>
+      <c r="H20">
+        <v>28.8</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>6.23</v>
+      </c>
+      <c r="L20">
+        <v>-6.23</v>
+      </c>
+      <c r="M20">
+        <v>2.6306208</v>
+      </c>
+      <c r="N20">
+        <v>-8.8606208</v>
+      </c>
+      <c r="O20">
+        <v>-1.949336576</v>
+      </c>
+      <c r="P20">
+        <v>-6.911284223999999</v>
+      </c>
+      <c r="Q20">
+        <v>-0.6812842239999988</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1327234827810302</v>
+      </c>
+      <c r="T20">
+        <v>1.271873800908631</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>-0.521017700460667</v>
+      </c>
+      <c r="W20">
+        <v>0.3632190268700073</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>-2.368262274821213</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1762126807170461</v>
+      </c>
+      <c r="C21">
+        <v>19.27580932586613</v>
+      </c>
+      <c r="D21">
+        <v>30.41180932586613</v>
+      </c>
+      <c r="E21">
+        <v>-20.772</v>
+      </c>
+      <c r="F21">
+        <v>11.628</v>
+      </c>
+      <c r="G21">
+        <v>0.492</v>
+      </c>
+      <c r="H21">
+        <v>28.8</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>6.23</v>
+      </c>
+      <c r="L21">
+        <v>-6.23</v>
+      </c>
+      <c r="M21">
+        <v>2.7767664</v>
+      </c>
+      <c r="N21">
+        <v>-9.0067664</v>
+      </c>
+      <c r="O21">
+        <v>-1.981488608</v>
+      </c>
+      <c r="P21">
+        <v>-7.025277792</v>
+      </c>
+      <c r="Q21">
+        <v>-0.7952777919999994</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1338830319511664</v>
+      </c>
+      <c r="T21">
+        <v>1.287575946598861</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>-0.493595716225895</v>
+      </c>
+      <c r="W21">
+        <v>0.3566706570347438</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>-2.243616891935886</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1782126807170461</v>
+      </c>
+      <c r="C22">
+        <v>18.22752463254486</v>
+      </c>
+      <c r="D22">
+        <v>29.97552463254486</v>
+      </c>
+      <c r="E22">
+        <v>-20.16</v>
+      </c>
+      <c r="F22">
+        <v>12.24</v>
+      </c>
+      <c r="G22">
+        <v>0.492</v>
+      </c>
+      <c r="H22">
+        <v>28.8</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>6.23</v>
+      </c>
+      <c r="L22">
+        <v>-6.23</v>
+      </c>
+      <c r="M22">
+        <v>2.922912000000001</v>
+      </c>
+      <c r="N22">
+        <v>-9.152912000000001</v>
+      </c>
+      <c r="O22">
+        <v>-2.01364064</v>
+      </c>
+      <c r="P22">
+        <v>-7.13927136</v>
+      </c>
+      <c r="Q22">
+        <v>-0.90927136</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.135071569850556</v>
+      </c>
+      <c r="T22">
+        <v>1.303670645931346</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>-0.4689159304146002</v>
+      </c>
+      <c r="W22">
+        <v>0.3507771241830066</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>-2.131436047339092</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1802126807170461</v>
+      </c>
+      <c r="C23">
+        <v>17.1915806908764</v>
+      </c>
+      <c r="D23">
+        <v>29.5515806908764</v>
+      </c>
+      <c r="E23">
+        <v>-19.548</v>
+      </c>
+      <c r="F23">
+        <v>12.852</v>
+      </c>
+      <c r="G23">
+        <v>0.492</v>
+      </c>
+      <c r="H23">
+        <v>28.8</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>6.23</v>
+      </c>
+      <c r="L23">
+        <v>-6.23</v>
+      </c>
+      <c r="M23">
+        <v>3.0690576</v>
+      </c>
+      <c r="N23">
+        <v>-9.299057600000001</v>
+      </c>
+      <c r="O23">
+        <v>-2.045792672</v>
+      </c>
+      <c r="P23">
+        <v>-7.253264928000001</v>
+      </c>
+      <c r="Q23">
+        <v>-1.023264928000001</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1362901973170187</v>
+      </c>
+      <c r="T23">
+        <v>1.320172806006426</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>-0.4465866003948574</v>
+      </c>
+      <c r="W23">
+        <v>0.3454448801742919</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>-2.029939092703897</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1822126807170461</v>
+      </c>
+      <c r="C24">
+        <v>16.1674611970754</v>
+      </c>
+      <c r="D24">
+        <v>29.1394611970754</v>
+      </c>
+      <c r="E24">
+        <v>-18.936</v>
+      </c>
+      <c r="F24">
+        <v>13.464</v>
+      </c>
+      <c r="G24">
+        <v>0.492</v>
+      </c>
+      <c r="H24">
+        <v>28.8</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>6.23</v>
+      </c>
+      <c r="L24">
+        <v>-6.23</v>
+      </c>
+      <c r="M24">
+        <v>3.2152032</v>
+      </c>
+      <c r="N24">
+        <v>-9.445203200000002</v>
+      </c>
+      <c r="O24">
+        <v>-2.077944704000001</v>
+      </c>
+      <c r="P24">
+        <v>-7.367258496000002</v>
+      </c>
+      <c r="Q24">
+        <v>-1.137258496000001</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1375400716415959</v>
+      </c>
+      <c r="T24">
+        <v>1.337098098391124</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>-0.4262872094678184</v>
+      </c>
+      <c r="W24">
+        <v>0.3405973856209151</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>-1.937669133944629</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1842126807170461</v>
+      </c>
+      <c r="C25">
+        <v>15.15467825224025</v>
+      </c>
+      <c r="D25">
+        <v>28.73867825224025</v>
+      </c>
+      <c r="E25">
+        <v>-18.324</v>
+      </c>
+      <c r="F25">
+        <v>14.076</v>
+      </c>
+      <c r="G25">
+        <v>0.492</v>
+      </c>
+      <c r="H25">
+        <v>28.8</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>6.23</v>
+      </c>
+      <c r="L25">
+        <v>-6.23</v>
+      </c>
+      <c r="M25">
+        <v>3.3613488</v>
+      </c>
+      <c r="N25">
+        <v>-9.5913488</v>
+      </c>
+      <c r="O25">
+        <v>-2.110096736</v>
+      </c>
+      <c r="P25">
+        <v>-7.481252064</v>
+      </c>
+      <c r="Q25">
+        <v>-1.251252064</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1388224102343439</v>
+      </c>
+      <c r="T25">
+        <v>1.35446300875984</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>-0.4077529829692176</v>
+      </c>
+      <c r="W25">
+        <v>0.3361714123330491</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>-1.85342264986008</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1862126807170461</v>
+      </c>
+      <c r="C26">
+        <v>14.15277043545747</v>
+      </c>
+      <c r="D26">
+        <v>28.34877043545747</v>
+      </c>
+      <c r="E26">
+        <v>-17.712</v>
+      </c>
+      <c r="F26">
+        <v>14.688</v>
+      </c>
+      <c r="G26">
+        <v>0.492</v>
+      </c>
+      <c r="H26">
+        <v>28.8</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>6.23</v>
+      </c>
+      <c r="L26">
+        <v>-6.23</v>
+      </c>
+      <c r="M26">
+        <v>3.5074944</v>
+      </c>
+      <c r="N26">
+        <v>-9.737494400000001</v>
+      </c>
+      <c r="O26">
+        <v>-2.142248768</v>
+      </c>
+      <c r="P26">
+        <v>-7.595245632000001</v>
+      </c>
+      <c r="Q26">
+        <v>-1.365245632000001</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1401384945795326</v>
+      </c>
+      <c r="T26">
+        <v>1.372284890454049</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>-0.3907632753455002</v>
+      </c>
+      <c r="W26">
+        <v>0.3321142701525054</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>-1.77619670611591</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1882126807170461</v>
+      </c>
+      <c r="C27">
+        <v>13.16130103166378</v>
+      </c>
+      <c r="D27">
+        <v>27.96930103166378</v>
+      </c>
+      <c r="E27">
+        <v>-17.1</v>
+      </c>
+      <c r="F27">
+        <v>15.3</v>
+      </c>
+      <c r="G27">
+        <v>0.492</v>
+      </c>
+      <c r="H27">
+        <v>28.8</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>6.23</v>
+      </c>
+      <c r="L27">
+        <v>-6.23</v>
+      </c>
+      <c r="M27">
+        <v>3.65364</v>
+      </c>
+      <c r="N27">
+        <v>-9.88364</v>
+      </c>
+      <c r="O27">
+        <v>-2.1744008</v>
+      </c>
+      <c r="P27">
+        <v>-7.7092392</v>
+      </c>
+      <c r="Q27">
+        <v>-1.479239199999999</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1414896745072597</v>
+      </c>
+      <c r="T27">
+        <v>1.390582022326769</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>-0.3751327443316802</v>
+      </c>
+      <c r="W27">
+        <v>0.3283816993464052</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>-1.705148837871273</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1902126807170461</v>
+      </c>
+      <c r="C28">
+        <v>12.17985639995645</v>
+      </c>
+      <c r="D28">
+        <v>27.59985639995645</v>
+      </c>
+      <c r="E28">
+        <v>-16.488</v>
+      </c>
+      <c r="F28">
+        <v>15.912</v>
+      </c>
+      <c r="G28">
+        <v>0.492</v>
+      </c>
+      <c r="H28">
+        <v>28.8</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>6.23</v>
+      </c>
+      <c r="L28">
+        <v>-6.23</v>
+      </c>
+      <c r="M28">
+        <v>3.7997856</v>
+      </c>
+      <c r="N28">
+        <v>-10.0297856</v>
+      </c>
+      <c r="O28">
+        <v>-2.206552832</v>
+      </c>
+      <c r="P28">
+        <v>-7.823232768</v>
+      </c>
+      <c r="Q28">
+        <v>-1.593232768</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1428773728114119</v>
+      </c>
+      <c r="T28">
+        <v>1.409373671277131</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>-0.3607045618573848</v>
+      </c>
+      <c r="W28">
+        <v>0.3249362493715435</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>-1.63956619026084</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1922126807170462</v>
+      </c>
+      <c r="C29">
+        <v>11.20804446953511</v>
+      </c>
+      <c r="D29">
+        <v>27.24004446953511</v>
+      </c>
+      <c r="E29">
+        <v>-15.876</v>
+      </c>
+      <c r="F29">
+        <v>16.524</v>
+      </c>
+      <c r="G29">
+        <v>0.492</v>
+      </c>
+      <c r="H29">
+        <v>28.8</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>6.23</v>
+      </c>
+      <c r="L29">
+        <v>-6.23</v>
+      </c>
+      <c r="M29">
+        <v>3.9459312</v>
+      </c>
+      <c r="N29">
+        <v>-10.1759312</v>
+      </c>
+      <c r="O29">
+        <v>-2.238704864</v>
+      </c>
+      <c r="P29">
+        <v>-7.937226336</v>
+      </c>
+      <c r="Q29">
+        <v>-1.707226336</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1443030902471847</v>
+      </c>
+      <c r="T29">
+        <v>1.428680159924763</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>-0.3473451336404446</v>
+      </c>
+      <c r="W29">
+        <v>0.3217460179133382</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>-1.578841516547476</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1942126807170461</v>
+      </c>
+      <c r="C30">
+        <v>10.24549335177749</v>
+      </c>
+      <c r="D30">
+        <v>26.88949335177749</v>
+      </c>
+      <c r="E30">
+        <v>-15.264</v>
+      </c>
+      <c r="F30">
+        <v>17.136</v>
+      </c>
+      <c r="G30">
+        <v>0.492</v>
+      </c>
+      <c r="H30">
+        <v>28.8</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>6.23</v>
+      </c>
+      <c r="L30">
+        <v>-6.23</v>
+      </c>
+      <c r="M30">
+        <v>4.092076800000001</v>
+      </c>
+      <c r="N30">
+        <v>-10.3220768</v>
+      </c>
+      <c r="O30">
+        <v>-2.270856896</v>
+      </c>
+      <c r="P30">
+        <v>-8.051219904000002</v>
+      </c>
+      <c r="Q30">
+        <v>-1.821219904000001</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1457684109450622</v>
+      </c>
+      <c r="T30">
+        <v>1.448522939923718</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>-0.334939950296143</v>
+      </c>
+      <c r="W30">
+        <v>0.318783660130719</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>-1.522454319527923</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1962126807170461</v>
+      </c>
+      <c r="C31">
+        <v>9.291850058120453</v>
+      </c>
+      <c r="D31">
+        <v>26.54785005812045</v>
+      </c>
+      <c r="E31">
+        <v>-14.652</v>
+      </c>
+      <c r="F31">
+        <v>17.748</v>
+      </c>
+      <c r="G31">
+        <v>0.492</v>
+      </c>
+      <c r="H31">
+        <v>28.8</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>6.23</v>
+      </c>
+      <c r="L31">
+        <v>-6.23</v>
+      </c>
+      <c r="M31">
+        <v>4.238222400000001</v>
+      </c>
+      <c r="N31">
+        <v>-10.4682224</v>
+      </c>
+      <c r="O31">
+        <v>-2.303008928000001</v>
+      </c>
+      <c r="P31">
+        <v>-8.165213472000001</v>
+      </c>
+      <c r="Q31">
+        <v>-1.935213472000001</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1472750082823166</v>
+      </c>
+      <c r="T31">
+        <v>1.46892467147194</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>-0.3233902968376554</v>
+      </c>
+      <c r="W31">
+        <v>0.3160256028848321</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>-1.469955894716615</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1982126807170461</v>
+      </c>
+      <c r="C32">
+        <v>8.346779314454299</v>
+      </c>
+      <c r="D32">
+        <v>26.2147793144543</v>
+      </c>
+      <c r="E32">
+        <v>-14.04</v>
+      </c>
+      <c r="F32">
+        <v>18.36</v>
+      </c>
+      <c r="G32">
+        <v>0.492</v>
+      </c>
+      <c r="H32">
+        <v>28.8</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>6.23</v>
+      </c>
+      <c r="L32">
+        <v>-6.23</v>
+      </c>
+      <c r="M32">
+        <v>4.384368</v>
+      </c>
+      <c r="N32">
+        <v>-10.614368</v>
+      </c>
+      <c r="O32">
+        <v>-2.33516096</v>
+      </c>
+      <c r="P32">
+        <v>-8.279207040000001</v>
+      </c>
+      <c r="Q32">
+        <v>-2.049207040000001</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1488246512577783</v>
+      </c>
+      <c r="T32">
+        <v>1.489909309635824</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>-0.3126106202764002</v>
+      </c>
+      <c r="W32">
+        <v>0.3134514161220044</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>-1.420957364892728</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.2002126807170461</v>
+      </c>
+      <c r="C33">
+        <v>7.409962463659188</v>
+      </c>
+      <c r="D33">
+        <v>25.88996246365919</v>
+      </c>
+      <c r="E33">
+        <v>-13.428</v>
+      </c>
+      <c r="F33">
+        <v>18.972</v>
+      </c>
+      <c r="G33">
+        <v>0.492</v>
+      </c>
+      <c r="H33">
+        <v>28.8</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>6.23</v>
+      </c>
+      <c r="L33">
+        <v>-6.23</v>
+      </c>
+      <c r="M33">
+        <v>4.530513600000001</v>
+      </c>
+      <c r="N33">
+        <v>-10.7605136</v>
+      </c>
+      <c r="O33">
+        <v>-2.367312992</v>
+      </c>
+      <c r="P33">
+        <v>-8.393200608000001</v>
+      </c>
+      <c r="Q33">
+        <v>-2.163200608</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1504192114209345</v>
+      </c>
+      <c r="T33">
+        <v>1.511502198181271</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>-0.3025264067190969</v>
+      </c>
+      <c r="W33">
+        <v>0.3110433059245203</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>-1.375120030541349</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.2022126807170461</v>
+      </c>
+      <c r="C34">
+        <v>6.481096448732369</v>
+      </c>
+      <c r="D34">
+        <v>25.57309644873237</v>
+      </c>
+      <c r="E34">
+        <v>-12.816</v>
+      </c>
+      <c r="F34">
+        <v>19.584</v>
+      </c>
+      <c r="G34">
+        <v>0.492</v>
+      </c>
+      <c r="H34">
+        <v>28.8</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>6.23</v>
+      </c>
+      <c r="L34">
+        <v>-6.23</v>
+      </c>
+      <c r="M34">
+        <v>4.6766592</v>
+      </c>
+      <c r="N34">
+        <v>-10.9066592</v>
+      </c>
+      <c r="O34">
+        <v>-2.399465024</v>
+      </c>
+      <c r="P34">
+        <v>-8.507194176</v>
+      </c>
+      <c r="Q34">
+        <v>-2.277194176</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1520606704124188</v>
+      </c>
+      <c r="T34">
+        <v>1.533730171683937</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>-0.2930724565091252</v>
+      </c>
+      <c r="W34">
+        <v>0.3087857026143791</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>-1.332147529586932</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.2042126807170461</v>
+      </c>
+      <c r="C35">
+        <v>5.559892869685402</v>
+      </c>
+      <c r="D35">
+        <v>25.2638928696854</v>
+      </c>
+      <c r="E35">
+        <v>-12.204</v>
+      </c>
+      <c r="F35">
+        <v>20.196</v>
+      </c>
+      <c r="G35">
+        <v>0.492</v>
+      </c>
+      <c r="H35">
+        <v>28.8</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>6.23</v>
+      </c>
+      <c r="L35">
+        <v>-6.23</v>
+      </c>
+      <c r="M35">
+        <v>4.822804800000001</v>
+      </c>
+      <c r="N35">
+        <v>-11.0528048</v>
+      </c>
+      <c r="O35">
+        <v>-2.431617056</v>
+      </c>
+      <c r="P35">
+        <v>-8.621187744</v>
+      </c>
+      <c r="Q35">
+        <v>-2.391187744</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1537511281797684</v>
+      </c>
+      <c r="T35">
+        <v>1.556621666783697</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>-0.2841914729785456</v>
+      </c>
+      <c r="W35">
+        <v>0.3066649237472767</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>-1.291779422629753</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.2062126807170461</v>
+      </c>
+      <c r="C36">
+        <v>4.646077108042036</v>
+      </c>
+      <c r="D36">
+        <v>24.96207710804204</v>
+      </c>
+      <c r="E36">
+        <v>-11.592</v>
+      </c>
+      <c r="F36">
+        <v>20.808</v>
+      </c>
+      <c r="G36">
+        <v>0.492</v>
+      </c>
+      <c r="H36">
+        <v>28.8</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>6.23</v>
+      </c>
+      <c r="L36">
+        <v>-6.23</v>
+      </c>
+      <c r="M36">
+        <v>4.968950400000001</v>
+      </c>
+      <c r="N36">
+        <v>-11.1989504</v>
+      </c>
+      <c r="O36">
+        <v>-2.463769088</v>
+      </c>
+      <c r="P36">
+        <v>-8.735181312000002</v>
+      </c>
+      <c r="Q36">
+        <v>-2.505181312000001</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1554928119400679</v>
+      </c>
+      <c r="T36">
+        <v>1.580206843553147</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>-0.2758329002438825</v>
+      </c>
+      <c r="W36">
+        <v>0.3046688965782391</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>-1.253785910199466</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.2082126807170461</v>
+      </c>
+      <c r="C37">
+        <v>3.739387513350671</v>
+      </c>
+      <c r="D37">
+        <v>24.66738751335067</v>
+      </c>
+      <c r="E37">
+        <v>-10.98</v>
+      </c>
+      <c r="F37">
+        <v>21.42</v>
+      </c>
+      <c r="G37">
+        <v>0.492</v>
+      </c>
+      <c r="H37">
+        <v>28.8</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>6.23</v>
+      </c>
+      <c r="L37">
+        <v>-6.23</v>
+      </c>
+      <c r="M37">
+        <v>5.115096</v>
+      </c>
+      <c r="N37">
+        <v>-11.345096</v>
+      </c>
+      <c r="O37">
+        <v>-2.49592112</v>
+      </c>
+      <c r="P37">
+        <v>-8.849174880000001</v>
+      </c>
+      <c r="Q37">
+        <v>-2.619174880000001</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1572880859699151</v>
+      </c>
+      <c r="T37">
+        <v>1.60451771806935</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>-0.2679519602369144</v>
+      </c>
+      <c r="W37">
+        <v>0.3027869281045752</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>-1.217963455622339</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.2102126807170461</v>
+      </c>
+      <c r="C38">
+        <v>2.839574646646028</v>
+      </c>
+      <c r="D38">
+        <v>24.37957464664603</v>
+      </c>
+      <c r="E38">
+        <v>-10.368</v>
+      </c>
+      <c r="F38">
+        <v>22.032</v>
+      </c>
+      <c r="G38">
+        <v>0.492</v>
+      </c>
+      <c r="H38">
+        <v>28.8</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>6.23</v>
+      </c>
+      <c r="L38">
+        <v>-6.23</v>
+      </c>
+      <c r="M38">
+        <v>5.2612416</v>
+      </c>
+      <c r="N38">
+        <v>-11.4912416</v>
+      </c>
+      <c r="O38">
+        <v>-2.528073152</v>
+      </c>
+      <c r="P38">
+        <v>-8.963168448000001</v>
+      </c>
+      <c r="Q38">
+        <v>-2.733168448000001</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.159139462313195</v>
+      </c>
+      <c r="T38">
+        <v>1.629588307414183</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>-0.2605088502303335</v>
+      </c>
+      <c r="W38">
+        <v>0.3010095134350037</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>-1.184131137410607</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.2122126807170461</v>
+      </c>
+      <c r="C39">
+        <v>1.946400576262725</v>
+      </c>
+      <c r="D39">
+        <v>24.09840057626273</v>
+      </c>
+      <c r="E39">
+        <v>-9.755999999999997</v>
+      </c>
+      <c r="F39">
+        <v>22.644</v>
+      </c>
+      <c r="G39">
+        <v>0.492</v>
+      </c>
+      <c r="H39">
+        <v>28.8</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>6.23</v>
+      </c>
+      <c r="L39">
+        <v>-6.23</v>
+      </c>
+      <c r="M39">
+        <v>5.407387200000001</v>
+      </c>
+      <c r="N39">
+        <v>-11.6373872</v>
+      </c>
+      <c r="O39">
+        <v>-2.560225184</v>
+      </c>
+      <c r="P39">
+        <v>-9.077162016000001</v>
+      </c>
+      <c r="Q39">
+        <v>-2.847162016</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1610496125086426</v>
+      </c>
+      <c r="T39">
+        <v>1.655454788484249</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>-0.2534680704943785</v>
+      </c>
+      <c r="W39">
+        <v>0.2993281752340576</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>-1.152127593156266</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2142126807170461</v>
+      </c>
+      <c r="C40">
+        <v>1.059638221822286</v>
+      </c>
+      <c r="D40">
+        <v>23.82363822182229</v>
+      </c>
+      <c r="E40">
+        <v>-9.143999999999998</v>
+      </c>
+      <c r="F40">
+        <v>23.256</v>
+      </c>
+      <c r="G40">
+        <v>0.492</v>
+      </c>
+      <c r="H40">
+        <v>28.8</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>6.23</v>
+      </c>
+      <c r="L40">
+        <v>-6.23</v>
+      </c>
+      <c r="M40">
+        <v>5.5535328</v>
+      </c>
+      <c r="N40">
+        <v>-11.7835328</v>
+      </c>
+      <c r="O40">
+        <v>-2.592377216</v>
+      </c>
+      <c r="P40">
+        <v>-9.191155584000001</v>
+      </c>
+      <c r="Q40">
+        <v>-2.961155584</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1630213804523303</v>
+      </c>
+      <c r="T40">
+        <v>1.682155672169479</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>-0.2467978581129475</v>
+      </c>
+      <c r="W40">
+        <v>0.2977353285173719</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>-1.121808445967943</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2162126807170461</v>
+      </c>
+      <c r="C41">
+        <v>0.1790707425921134</v>
+      </c>
+      <c r="D41">
+        <v>23.55507074259211</v>
+      </c>
+      <c r="E41">
+        <v>-8.531999999999996</v>
+      </c>
+      <c r="F41">
+        <v>23.868</v>
+      </c>
+      <c r="G41">
+        <v>0.492</v>
+      </c>
+      <c r="H41">
+        <v>28.8</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>6.23</v>
+      </c>
+      <c r="L41">
+        <v>-6.23</v>
+      </c>
+      <c r="M41">
+        <v>5.699678400000001</v>
+      </c>
+      <c r="N41">
+        <v>-11.9296784</v>
+      </c>
+      <c r="O41">
+        <v>-2.624529248</v>
+      </c>
+      <c r="P41">
+        <v>-9.305149152</v>
+      </c>
+      <c r="Q41">
+        <v>-3.075149152</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1650577965253194</v>
+      </c>
+      <c r="T41">
+        <v>1.709731994664061</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>-0.2404697079049232</v>
+      </c>
+      <c r="W41">
+        <v>0.2962241662476957</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>-1.09304412684056</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2182126807170461</v>
+      </c>
+      <c r="C42">
+        <v>-0.6955090332459335</v>
+      </c>
+      <c r="D42">
+        <v>23.29249096675407</v>
+      </c>
+      <c r="E42">
+        <v>-7.919999999999995</v>
+      </c>
+      <c r="F42">
+        <v>24.48</v>
+      </c>
+      <c r="G42">
+        <v>0.492</v>
+      </c>
+      <c r="H42">
+        <v>28.8</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>6.23</v>
+      </c>
+      <c r="L42">
+        <v>-6.23</v>
+      </c>
+      <c r="M42">
+        <v>5.845824000000001</v>
+      </c>
+      <c r="N42">
+        <v>-12.075824</v>
+      </c>
+      <c r="O42">
+        <v>-2.65668128</v>
+      </c>
+      <c r="P42">
+        <v>-9.41914272</v>
+      </c>
+      <c r="Q42">
+        <v>-3.18914272</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1671620931340747</v>
+      </c>
+      <c r="T42">
+        <v>1.738227527908462</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>-0.2344579652073001</v>
+      </c>
+      <c r="W42">
+        <v>0.2947885620915033</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>-1.065718023669546</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2202126807170461</v>
+      </c>
+      <c r="C43">
+        <v>-1.564299141574512</v>
+      </c>
+      <c r="D43">
+        <v>23.03570085842549</v>
+      </c>
+      <c r="E43">
+        <v>-7.307999999999996</v>
+      </c>
+      <c r="F43">
+        <v>25.092</v>
+      </c>
+      <c r="G43">
+        <v>0.492</v>
+      </c>
+      <c r="H43">
+        <v>28.8</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>6.23</v>
+      </c>
+      <c r="L43">
+        <v>-6.23</v>
+      </c>
+      <c r="M43">
+        <v>5.991969600000001</v>
+      </c>
+      <c r="N43">
+        <v>-12.2219696</v>
+      </c>
+      <c r="O43">
+        <v>-2.688833312</v>
+      </c>
+      <c r="P43">
+        <v>-9.533136288000001</v>
+      </c>
+      <c r="Q43">
+        <v>-3.303136288000001</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1693377218312624</v>
+      </c>
+      <c r="T43">
+        <v>1.767689011432334</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>-0.2287394782510245</v>
+      </c>
+      <c r="W43">
+        <v>0.2934229874063447</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>-1.039724901141021</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2222126807170461</v>
+      </c>
+      <c r="C44">
+        <v>-2.427488980448992</v>
+      </c>
+      <c r="D44">
+        <v>22.78451101955101</v>
+      </c>
+      <c r="E44">
+        <v>-6.695999999999998</v>
+      </c>
+      <c r="F44">
+        <v>25.704</v>
+      </c>
+      <c r="G44">
+        <v>0.492</v>
+      </c>
+      <c r="H44">
+        <v>28.8</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>6.23</v>
+      </c>
+      <c r="L44">
+        <v>-6.23</v>
+      </c>
+      <c r="M44">
+        <v>6.138115200000001</v>
+      </c>
+      <c r="N44">
+        <v>-12.3681152</v>
+      </c>
+      <c r="O44">
+        <v>-2.720985344</v>
+      </c>
+      <c r="P44">
+        <v>-9.647129856000001</v>
+      </c>
+      <c r="Q44">
+        <v>-3.417129856000001</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1715883722076634</v>
+      </c>
+      <c r="T44">
+        <v>1.798166408181167</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>-0.2232933001974287</v>
+      </c>
+      <c r="W44">
+        <v>0.292122440087146</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>-1.014969546351949</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2242126807170461</v>
+      </c>
+      <c r="C45">
+        <v>-3.285259775967791</v>
+      </c>
+      <c r="D45">
+        <v>22.53874022403221</v>
+      </c>
+      <c r="E45">
+        <v>-6.083999999999996</v>
+      </c>
+      <c r="F45">
+        <v>26.316</v>
+      </c>
+      <c r="G45">
+        <v>0.492</v>
+      </c>
+      <c r="H45">
+        <v>28.8</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>6.23</v>
+      </c>
+      <c r="L45">
+        <v>-6.23</v>
+      </c>
+      <c r="M45">
+        <v>6.284260800000001</v>
+      </c>
+      <c r="N45">
+        <v>-12.5142608</v>
+      </c>
+      <c r="O45">
+        <v>-2.753137376000001</v>
+      </c>
+      <c r="P45">
+        <v>-9.761123424000001</v>
+      </c>
+      <c r="Q45">
+        <v>-3.531123424</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1739179927727102</v>
+      </c>
+      <c r="T45">
+        <v>1.829713187272065</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>-0.2181004327509768</v>
+      </c>
+      <c r="W45">
+        <v>0.2908823833409332</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>-0.9913656034135312</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2262126807170461</v>
+      </c>
+      <c r="C46">
+        <v>-4.137785018313174</v>
+      </c>
+      <c r="D46">
+        <v>22.29821498168683</v>
+      </c>
+      <c r="E46">
+        <v>-5.471999999999998</v>
+      </c>
+      <c r="F46">
+        <v>26.928</v>
+      </c>
+      <c r="G46">
+        <v>0.492</v>
+      </c>
+      <c r="H46">
+        <v>28.8</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>6.23</v>
+      </c>
+      <c r="L46">
+        <v>-6.23</v>
+      </c>
+      <c r="M46">
+        <v>6.430406400000001</v>
+      </c>
+      <c r="N46">
+        <v>-12.6604064</v>
+      </c>
+      <c r="O46">
+        <v>-2.785289408</v>
+      </c>
+      <c r="P46">
+        <v>-9.875116992000001</v>
+      </c>
+      <c r="Q46">
+        <v>-3.645116992</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1763308140722229</v>
+      </c>
+      <c r="T46">
+        <v>1.86238663704478</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>-0.2131436047339092</v>
+      </c>
+      <c r="W46">
+        <v>0.2896986928104576</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>-0.9688345669723144</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2282126807170461</v>
+      </c>
+      <c r="C47">
+        <v>-4.985230870167168</v>
+      </c>
+      <c r="D47">
+        <v>22.06276912983283</v>
+      </c>
+      <c r="E47">
+        <v>-4.859999999999996</v>
+      </c>
+      <c r="F47">
+        <v>27.54</v>
+      </c>
+      <c r="G47">
+        <v>0.492</v>
+      </c>
+      <c r="H47">
+        <v>28.8</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>6.23</v>
+      </c>
+      <c r="L47">
+        <v>-6.23</v>
+      </c>
+      <c r="M47">
+        <v>6.576552000000001</v>
+      </c>
+      <c r="N47">
+        <v>-12.806552</v>
+      </c>
+      <c r="O47">
+        <v>-2.817441440000001</v>
+      </c>
+      <c r="P47">
+        <v>-9.98911056</v>
+      </c>
+      <c r="Q47">
+        <v>-3.75911056</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1788313743280814</v>
+      </c>
+      <c r="T47">
+        <v>1.896248212263776</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>-0.2084070801842667</v>
+      </c>
+      <c r="W47">
+        <v>0.2885676107480029</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>-0.9473049099284852</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2302126807170461</v>
+      </c>
+      <c r="C48">
+        <v>-5.827756549523244</v>
+      </c>
+      <c r="D48">
+        <v>21.83224345047676</v>
+      </c>
+      <c r="E48">
+        <v>-4.247999999999998</v>
+      </c>
+      <c r="F48">
+        <v>28.152</v>
+      </c>
+      <c r="G48">
+        <v>0.492</v>
+      </c>
+      <c r="H48">
+        <v>28.8</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>6.23</v>
+      </c>
+      <c r="L48">
+        <v>-6.23</v>
+      </c>
+      <c r="M48">
+        <v>6.722697600000001</v>
+      </c>
+      <c r="N48">
+        <v>-12.9526976</v>
+      </c>
+      <c r="O48">
+        <v>-2.849593472</v>
+      </c>
+      <c r="P48">
+        <v>-10.103104128</v>
+      </c>
+      <c r="Q48">
+        <v>-3.873104128</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1814245479267496</v>
+      </c>
+      <c r="T48">
+        <v>1.931363919898291</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>-0.2038764914846088</v>
+      </c>
+      <c r="W48">
+        <v>0.2874857061665246</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>-0.9267113249300398</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2322126807170461</v>
+      </c>
+      <c r="C49">
+        <v>-6.665514688746981</v>
+      </c>
+      <c r="D49">
+        <v>21.60648531125302</v>
+      </c>
+      <c r="E49">
+        <v>-3.635999999999996</v>
+      </c>
+      <c r="F49">
+        <v>28.764</v>
+      </c>
+      <c r="G49">
+        <v>0.492</v>
+      </c>
+      <c r="H49">
+        <v>28.8</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>6.23</v>
+      </c>
+      <c r="L49">
+        <v>-6.23</v>
+      </c>
+      <c r="M49">
+        <v>6.868843200000001</v>
+      </c>
+      <c r="N49">
+        <v>-13.0988432</v>
+      </c>
+      <c r="O49">
+        <v>-2.881745504</v>
+      </c>
+      <c r="P49">
+        <v>-10.217097696</v>
+      </c>
+      <c r="Q49">
+        <v>-3.987097695999999</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1841155771329147</v>
+      </c>
+      <c r="T49">
+        <v>1.967804748575617</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>-0.1995386937934469</v>
+      </c>
+      <c r="W49">
+        <v>0.2864498400778752</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>-0.9069940626974857</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2342126807170461</v>
+      </c>
+      <c r="C50">
+        <v>-7.49865167158729</v>
+      </c>
+      <c r="D50">
+        <v>21.38534832841271</v>
+      </c>
+      <c r="E50">
+        <v>-3.023999999999997</v>
+      </c>
+      <c r="F50">
+        <v>29.376</v>
+      </c>
+      <c r="G50">
+        <v>0.492</v>
+      </c>
+      <c r="H50">
+        <v>28.8</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>6.23</v>
+      </c>
+      <c r="L50">
+        <v>-6.23</v>
+      </c>
+      <c r="M50">
+        <v>7.0149888</v>
+      </c>
+      <c r="N50">
+        <v>-13.2449888</v>
+      </c>
+      <c r="O50">
+        <v>-2.913897536</v>
+      </c>
+      <c r="P50">
+        <v>-10.331091264</v>
+      </c>
+      <c r="Q50">
+        <v>-4.101091264000001</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1869101074623938</v>
+      </c>
+      <c r="T50">
+        <v>2.005647147586686</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>-0.1953816376727501</v>
+      </c>
+      <c r="W50">
+        <v>0.2854571350762528</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>-0.8880983530579551</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2362126807170461</v>
+      </c>
+      <c r="C51">
+        <v>-8.327307949702114</v>
+      </c>
+      <c r="D51">
+        <v>21.16869205029789</v>
+      </c>
+      <c r="E51">
+        <v>-2.411999999999999</v>
+      </c>
+      <c r="F51">
+        <v>29.988</v>
+      </c>
+      <c r="G51">
+        <v>0.492</v>
+      </c>
+      <c r="H51">
+        <v>28.8</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>6.23</v>
+      </c>
+      <c r="L51">
+        <v>-6.23</v>
+      </c>
+      <c r="M51">
+        <v>7.1611344</v>
+      </c>
+      <c r="N51">
+        <v>-13.3911344</v>
+      </c>
+      <c r="O51">
+        <v>-2.946049568</v>
+      </c>
+      <c r="P51">
+        <v>-10.445084832</v>
+      </c>
+      <c r="Q51">
+        <v>-4.215084831999999</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1898142272165584</v>
+      </c>
+      <c r="T51">
+        <v>2.044973562245249</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>-0.1913942573120817</v>
+      </c>
+      <c r="W51">
+        <v>0.2845049486461251</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>-0.8699738968730988</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2382126807170461</v>
+      </c>
+      <c r="C52">
+        <v>-9.151618340136462</v>
+      </c>
+      <c r="D52">
+        <v>20.95638165986354</v>
+      </c>
+      <c r="E52">
+        <v>-1.799999999999997</v>
+      </c>
+      <c r="F52">
+        <v>30.6</v>
+      </c>
+      <c r="G52">
+        <v>0.492</v>
+      </c>
+      <c r="H52">
+        <v>28.8</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>6.23</v>
+      </c>
+      <c r="L52">
+        <v>-6.23</v>
+      </c>
+      <c r="M52">
+        <v>7.30728</v>
+      </c>
+      <c r="N52">
+        <v>-13.53728</v>
+      </c>
+      <c r="O52">
+        <v>-2.9782016</v>
+      </c>
+      <c r="P52">
+        <v>-10.5590784</v>
+      </c>
+      <c r="Q52">
+        <v>-4.3290784</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1928345117608896</v>
+      </c>
+      <c r="T52">
+        <v>2.085873033490154</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>-0.1875663721658401</v>
+      </c>
+      <c r="W52">
+        <v>0.2835908496732026</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>-0.8525744189356368</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2402126807170461</v>
+      </c>
+      <c r="C53">
+        <v>-9.971712305077073</v>
+      </c>
+      <c r="D53">
+        <v>20.74828769492293</v>
+      </c>
+      <c r="E53">
+        <v>-1.187999999999995</v>
+      </c>
+      <c r="F53">
+        <v>31.212</v>
+      </c>
+      <c r="G53">
+        <v>0.492</v>
+      </c>
+      <c r="H53">
+        <v>28.8</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>6.23</v>
+      </c>
+      <c r="L53">
+        <v>-6.23</v>
+      </c>
+      <c r="M53">
+        <v>7.453425600000001</v>
+      </c>
+      <c r="N53">
+        <v>-13.6834256</v>
+      </c>
+      <c r="O53">
+        <v>-3.010353632</v>
+      </c>
+      <c r="P53">
+        <v>-10.673071968</v>
+      </c>
+      <c r="Q53">
+        <v>-4.443071968000002</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1959780732253976</v>
+      </c>
+      <c r="T53">
+        <v>2.128441870908321</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>-0.1838886001625883</v>
+      </c>
+      <c r="W53">
+        <v>0.2827125977188261</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>-0.8358572734663106</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2422126807170461</v>
+      </c>
+      <c r="C54">
+        <v>-10.78771421510336</v>
+      </c>
+      <c r="D54">
+        <v>20.54428578489664</v>
+      </c>
+      <c r="E54">
+        <v>-0.575999999999997</v>
+      </c>
+      <c r="F54">
+        <v>31.824</v>
+      </c>
+      <c r="G54">
+        <v>0.492</v>
+      </c>
+      <c r="H54">
+        <v>28.8</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>6.23</v>
+      </c>
+      <c r="L54">
+        <v>-6.23</v>
+      </c>
+      <c r="M54">
+        <v>7.599571200000001</v>
+      </c>
+      <c r="N54">
+        <v>-13.8295712</v>
+      </c>
+      <c r="O54">
+        <v>-3.042505664</v>
+      </c>
+      <c r="P54">
+        <v>-10.787065536</v>
+      </c>
+      <c r="Q54">
+        <v>-4.557065536</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1992526164175933</v>
+      </c>
+      <c r="T54">
+        <v>2.172784409885577</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>-0.1803522809286924</v>
+      </c>
+      <c r="W54">
+        <v>0.2818681246857718</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>-0.8197830951304199</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2442126807170461</v>
+      </c>
+      <c r="C55">
+        <v>-11.59974359705954</v>
+      </c>
+      <c r="D55">
+        <v>20.34425640294046</v>
+      </c>
+      <c r="E55">
+        <v>0.03600000000000136</v>
+      </c>
+      <c r="F55">
+        <v>32.436</v>
+      </c>
+      <c r="G55">
+        <v>0.492</v>
+      </c>
+      <c r="H55">
+        <v>28.8</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>6.23</v>
+      </c>
+      <c r="L55">
+        <v>-6.23</v>
+      </c>
+      <c r="M55">
+        <v>7.7457168</v>
+      </c>
+      <c r="N55">
+        <v>-13.9757168</v>
+      </c>
+      <c r="O55">
+        <v>-3.074657696</v>
+      </c>
+      <c r="P55">
+        <v>-10.901059104</v>
+      </c>
+      <c r="Q55">
+        <v>-4.671059104000001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2026665018732868</v>
+      </c>
+      <c r="T55">
+        <v>2.219013865415058</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>-0.1769494077036227</v>
+      </c>
+      <c r="W55">
+        <v>0.2810555185596251</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>-0.8043154895619216</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2462126807170461</v>
+      </c>
+      <c r="C56">
+        <v>-12.4079153675859</v>
+      </c>
+      <c r="D56">
+        <v>20.1480846324141</v>
+      </c>
+      <c r="E56">
+        <v>0.6480000000000032</v>
+      </c>
+      <c r="F56">
+        <v>33.048</v>
+      </c>
+      <c r="G56">
+        <v>0.492</v>
+      </c>
+      <c r="H56">
+        <v>28.8</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>6.23</v>
+      </c>
+      <c r="L56">
+        <v>-6.23</v>
+      </c>
+      <c r="M56">
+        <v>7.891862400000001</v>
+      </c>
+      <c r="N56">
+        <v>-14.1218624</v>
+      </c>
+      <c r="O56">
+        <v>-3.106809728</v>
+      </c>
+      <c r="P56">
+        <v>-11.015052672</v>
+      </c>
+      <c r="Q56">
+        <v>-4.785052672000001</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2062288171314018</v>
+      </c>
+      <c r="T56">
+        <v>2.267253297271907</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>-0.1736725668202223</v>
+      </c>
+      <c r="W56">
+        <v>0.2802730089566691</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>-0.7894207582737378</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2482126807170461</v>
+      </c>
+      <c r="C57">
+        <v>-13.21234005326803</v>
+      </c>
+      <c r="D57">
+        <v>19.95565994673197</v>
+      </c>
+      <c r="E57">
+        <v>1.260000000000005</v>
+      </c>
+      <c r="F57">
+        <v>33.66</v>
+      </c>
+      <c r="G57">
+        <v>0.492</v>
+      </c>
+      <c r="H57">
+        <v>28.8</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>6.23</v>
+      </c>
+      <c r="L57">
+        <v>-6.23</v>
+      </c>
+      <c r="M57">
+        <v>8.038008000000001</v>
+      </c>
+      <c r="N57">
+        <v>-14.268008</v>
+      </c>
+      <c r="O57">
+        <v>-3.13896176</v>
+      </c>
+      <c r="P57">
+        <v>-11.12904624</v>
+      </c>
+      <c r="Q57">
+        <v>-4.899046240000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2099494575120996</v>
+      </c>
+      <c r="T57">
+        <v>2.317636703877949</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>-0.1705148837871273</v>
+      </c>
+      <c r="W57">
+        <v>0.279518954248366</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>-0.7750676535778516</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2502126807170462</v>
+      </c>
+      <c r="C58">
+        <v>-14.01312399829014</v>
+      </c>
+      <c r="D58">
+        <v>19.76687600170986</v>
+      </c>
+      <c r="E58">
+        <v>1.872000000000007</v>
+      </c>
+      <c r="F58">
+        <v>34.27200000000001</v>
+      </c>
+      <c r="G58">
+        <v>0.492</v>
+      </c>
+      <c r="H58">
+        <v>28.8</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>6.23</v>
+      </c>
+      <c r="L58">
+        <v>-6.23</v>
+      </c>
+      <c r="M58">
+        <v>8.184153600000002</v>
+      </c>
+      <c r="N58">
+        <v>-14.4141536</v>
+      </c>
+      <c r="O58">
+        <v>-3.171113792</v>
+      </c>
+      <c r="P58">
+        <v>-11.243039808</v>
+      </c>
+      <c r="Q58">
+        <v>-5.013039808000002</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2138392179101019</v>
+      </c>
+      <c r="T58">
+        <v>2.370310265329721</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>-0.1674699751480715</v>
+      </c>
+      <c r="W58">
+        <v>0.2787918300653595</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>-0.7612271597639613</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2522126807170462</v>
+      </c>
+      <c r="C59">
+        <v>-14.81036956041228</v>
+      </c>
+      <c r="D59">
+        <v>19.58163043958773</v>
+      </c>
+      <c r="E59">
+        <v>2.484000000000009</v>
+      </c>
+      <c r="F59">
+        <v>34.88400000000001</v>
+      </c>
+      <c r="G59">
+        <v>0.492</v>
+      </c>
+      <c r="H59">
+        <v>28.8</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>6.23</v>
+      </c>
+      <c r="L59">
+        <v>-6.23</v>
+      </c>
+      <c r="M59">
+        <v>8.330299200000002</v>
+      </c>
+      <c r="N59">
+        <v>-14.5602992</v>
+      </c>
+      <c r="O59">
+        <v>-3.203265824000001</v>
+      </c>
+      <c r="P59">
+        <v>-11.357033376</v>
+      </c>
+      <c r="Q59">
+        <v>-5.127033376000002</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2179098973963833</v>
+      </c>
+      <c r="T59">
+        <v>2.425433759872273</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>-0.1645319054086316</v>
+      </c>
+      <c r="W59">
+        <v>0.2780902190115813</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>-0.747872297311962</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2542126807170461</v>
+      </c>
+      <c r="C60">
+        <v>-15.60417529603011</v>
+      </c>
+      <c r="D60">
+        <v>19.39982470396989</v>
+      </c>
+      <c r="E60">
+        <v>3.096000000000004</v>
+      </c>
+      <c r="F60">
+        <v>35.496</v>
+      </c>
+      <c r="G60">
+        <v>0.492</v>
+      </c>
+      <c r="H60">
+        <v>28.8</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>6.23</v>
+      </c>
+      <c r="L60">
+        <v>-6.23</v>
+      </c>
+      <c r="M60">
+        <v>8.476444800000001</v>
+      </c>
+      <c r="N60">
+        <v>-14.7064448</v>
+      </c>
+      <c r="O60">
+        <v>-3.235417856</v>
+      </c>
+      <c r="P60">
+        <v>-11.471026944</v>
+      </c>
+      <c r="Q60">
+        <v>-5.241026944000001</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2221744187629638</v>
+      </c>
+      <c r="T60">
+        <v>2.483182182726373</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>-0.1616951484188277</v>
+      </c>
+      <c r="W60">
+        <v>0.277412801442416</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>-0.7349779473583076</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2562126807170461</v>
+      </c>
+      <c r="C61">
+        <v>-16.39463613502062</v>
+      </c>
+      <c r="D61">
+        <v>19.22136386497938</v>
+      </c>
+      <c r="E61">
+        <v>3.707999999999998</v>
+      </c>
+      <c r="F61">
+        <v>36.108</v>
+      </c>
+      <c r="G61">
+        <v>0.492</v>
+      </c>
+      <c r="H61">
+        <v>28.8</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>6.23</v>
+      </c>
+      <c r="L61">
+        <v>-6.23</v>
+      </c>
+      <c r="M61">
+        <v>8.6225904</v>
+      </c>
+      <c r="N61">
+        <v>-14.8525904</v>
+      </c>
+      <c r="O61">
+        <v>-3.267569888</v>
+      </c>
+      <c r="P61">
+        <v>-11.585020512</v>
+      </c>
+      <c r="Q61">
+        <v>-5.355020511999999</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2266469655620605</v>
+      </c>
+      <c r="T61">
+        <v>2.543747601817261</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>-0.1589545526829154</v>
+      </c>
+      <c r="W61">
+        <v>0.2767583471806802</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>-0.7225206940132516</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2582126807170461</v>
+      </c>
+      <c r="C62">
+        <v>-17.18184354602498</v>
+      </c>
+      <c r="D62">
+        <v>19.04615645397502</v>
+      </c>
+      <c r="E62">
+        <v>4.32</v>
+      </c>
+      <c r="F62">
+        <v>36.72</v>
+      </c>
+      <c r="G62">
+        <v>0.492</v>
+      </c>
+      <c r="H62">
+        <v>28.8</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>6.23</v>
+      </c>
+      <c r="L62">
+        <v>-6.23</v>
+      </c>
+      <c r="M62">
+        <v>8.768736000000001</v>
+      </c>
+      <c r="N62">
+        <v>-14.998736</v>
+      </c>
+      <c r="O62">
+        <v>-3.29972192</v>
+      </c>
+      <c r="P62">
+        <v>-11.69901408</v>
+      </c>
+      <c r="Q62">
+        <v>-5.469014080000001</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.231343139701112</v>
+      </c>
+      <c r="T62">
+        <v>2.607341291862692</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>-0.1563053101382001</v>
+      </c>
+      <c r="W62">
+        <v>0.2761257080610022</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>-0.710478682446364</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2602126807170461</v>
+      </c>
+      <c r="C63">
+        <v>-17.9658856927737</v>
+      </c>
+      <c r="D63">
+        <v>18.8741143072263</v>
+      </c>
+      <c r="E63">
+        <v>4.932000000000002</v>
+      </c>
+      <c r="F63">
+        <v>37.332</v>
+      </c>
+      <c r="G63">
+        <v>0.492</v>
+      </c>
+      <c r="H63">
+        <v>28.8</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>6.23</v>
+      </c>
+      <c r="L63">
+        <v>-6.23</v>
+      </c>
+      <c r="M63">
+        <v>8.914881600000001</v>
+      </c>
+      <c r="N63">
+        <v>-15.1448816</v>
+      </c>
+      <c r="O63">
+        <v>-3.331873952</v>
+      </c>
+      <c r="P63">
+        <v>-11.813007648</v>
+      </c>
+      <c r="Q63">
+        <v>-5.583007648000001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2362801432831918</v>
+      </c>
+      <c r="T63">
+        <v>2.674196196782249</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>-0.153742928004787</v>
+      </c>
+      <c r="W63">
+        <v>0.2755138112075431</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>-0.6988314909308497</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2622126807170461</v>
+      </c>
+      <c r="C64">
+        <v>-18.74684758201517</v>
+      </c>
+      <c r="D64">
+        <v>18.70515241798483</v>
+      </c>
+      <c r="E64">
+        <v>5.544000000000004</v>
+      </c>
+      <c r="F64">
+        <v>37.944</v>
+      </c>
+      <c r="G64">
+        <v>0.492</v>
+      </c>
+      <c r="H64">
+        <v>28.8</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>6.23</v>
+      </c>
+      <c r="L64">
+        <v>-6.23</v>
+      </c>
+      <c r="M64">
+        <v>9.061027200000002</v>
+      </c>
+      <c r="N64">
+        <v>-15.2910272</v>
+      </c>
+      <c r="O64">
+        <v>-3.364025984</v>
+      </c>
+      <c r="P64">
+        <v>-11.927001216</v>
+      </c>
+      <c r="Q64">
+        <v>-5.697001216</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2414769891590653</v>
+      </c>
+      <c r="T64">
+        <v>2.744569780908098</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>-0.1512632033595485</v>
+      </c>
+      <c r="W64">
+        <v>0.2749216529622602</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>-0.6875600152706747</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2642126807170461</v>
+      </c>
+      <c r="C65">
+        <v>-19.52481120356905</v>
+      </c>
+      <c r="D65">
+        <v>18.53918879643095</v>
+      </c>
+      <c r="E65">
+        <v>6.156000000000006</v>
+      </c>
+      <c r="F65">
+        <v>38.556</v>
+      </c>
+      <c r="G65">
+        <v>0.492</v>
+      </c>
+      <c r="H65">
+        <v>28.8</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>6.23</v>
+      </c>
+      <c r="L65">
+        <v>-6.23</v>
+      </c>
+      <c r="M65">
+        <v>9.207172800000002</v>
+      </c>
+      <c r="N65">
+        <v>-15.4371728</v>
+      </c>
+      <c r="O65">
+        <v>-3.396178016000001</v>
+      </c>
+      <c r="P65">
+        <v>-12.040994784</v>
+      </c>
+      <c r="Q65">
+        <v>-5.810994784000002</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2469547456228238</v>
+      </c>
+      <c r="T65">
+        <v>2.818747342554262</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>-0.1488622001316191</v>
+      </c>
+      <c r="W65">
+        <v>0.2743482933914306</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>-0.6766463642346323</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2662126807170461</v>
+      </c>
+      <c r="C66">
+        <v>-20.29985566298948</v>
+      </c>
+      <c r="D66">
+        <v>18.37614433701052</v>
+      </c>
+      <c r="E66">
+        <v>6.768000000000001</v>
+      </c>
+      <c r="F66">
+        <v>39.168</v>
+      </c>
+      <c r="G66">
+        <v>0.492</v>
+      </c>
+      <c r="H66">
+        <v>28.8</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>6.23</v>
+      </c>
+      <c r="L66">
+        <v>-6.23</v>
+      </c>
+      <c r="M66">
+        <v>9.353318400000001</v>
+      </c>
+      <c r="N66">
+        <v>-15.5833184</v>
+      </c>
+      <c r="O66">
+        <v>-3.428330048</v>
+      </c>
+      <c r="P66">
+        <v>-12.154988352</v>
+      </c>
+      <c r="Q66">
+        <v>-5.924988352</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2527368218901245</v>
+      </c>
+      <c r="T66">
+        <v>2.897045879847437</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>-0.1465362282545626</v>
+      </c>
+      <c r="W66">
+        <v>0.2737928513071896</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>-0.6660737647934662</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2682126807170461</v>
+      </c>
+      <c r="C67">
+        <v>-21.07205730728896</v>
+      </c>
+      <c r="D67">
+        <v>18.21594269271104</v>
+      </c>
+      <c r="E67">
+        <v>7.380000000000003</v>
+      </c>
+      <c r="F67">
+        <v>39.78</v>
+      </c>
+      <c r="G67">
+        <v>0.492</v>
+      </c>
+      <c r="H67">
+        <v>28.8</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>6.23</v>
+      </c>
+      <c r="L67">
+        <v>-6.23</v>
+      </c>
+      <c r="M67">
+        <v>9.499464000000001</v>
+      </c>
+      <c r="N67">
+        <v>-15.729464</v>
+      </c>
+      <c r="O67">
+        <v>-3.46048208</v>
+      </c>
+      <c r="P67">
+        <v>-12.26898192</v>
+      </c>
+      <c r="Q67">
+        <v>-6.038981920000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2588493025155566</v>
+      </c>
+      <c r="T67">
+        <v>2.979818619271649</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>-0.1442818247429539</v>
+      </c>
+      <c r="W67">
+        <v>0.2732544997486174</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>-0.655826476104336</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2702126807170461</v>
+      </c>
+      <c r="C68">
+        <v>-21.84148984414275</v>
+      </c>
+      <c r="D68">
+        <v>18.05851015585725</v>
+      </c>
+      <c r="E68">
+        <v>7.992000000000004</v>
+      </c>
+      <c r="F68">
+        <v>40.392</v>
+      </c>
+      <c r="G68">
+        <v>0.492</v>
+      </c>
+      <c r="H68">
+        <v>28.8</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>6.23</v>
+      </c>
+      <c r="L68">
+        <v>-6.23</v>
+      </c>
+      <c r="M68">
+        <v>9.645609600000002</v>
+      </c>
+      <c r="N68">
+        <v>-15.8756096</v>
+      </c>
+      <c r="O68">
+        <v>-3.492634112000001</v>
+      </c>
+      <c r="P68">
+        <v>-12.382975488</v>
+      </c>
+      <c r="Q68">
+        <v>-6.152975488000001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2653213408248377</v>
+      </c>
+      <c r="T68">
+        <v>3.067460343367874</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>-0.1420957364892728</v>
+      </c>
+      <c r="W68">
+        <v>0.2727324618736384</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>-0.6458897113148763</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2722126807170461</v>
+      </c>
+      <c r="C69">
+        <v>-22.60822445496494</v>
+      </c>
+      <c r="D69">
+        <v>17.90377554503507</v>
+      </c>
+      <c r="E69">
+        <v>8.604000000000006</v>
+      </c>
+      <c r="F69">
+        <v>41.004</v>
+      </c>
+      <c r="G69">
+        <v>0.492</v>
+      </c>
+      <c r="H69">
+        <v>28.8</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>6.23</v>
+      </c>
+      <c r="L69">
+        <v>-6.23</v>
+      </c>
+      <c r="M69">
+        <v>9.791755200000003</v>
+      </c>
+      <c r="N69">
+        <v>-16.0217552</v>
+      </c>
+      <c r="O69">
+        <v>-3.524786144</v>
+      </c>
+      <c r="P69">
+        <v>-12.496969056</v>
+      </c>
+      <c r="Q69">
+        <v>-6.266969056000001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2721856238801358</v>
+      </c>
+      <c r="T69">
+        <v>3.160413687106294</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>-0.1399749046013732</v>
+      </c>
+      <c r="W69">
+        <v>0.2722260072188079</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>-0.636249566369878</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2742126807170461</v>
+      </c>
+      <c r="C70">
+        <v>-23.37232990222038</v>
+      </c>
+      <c r="D70">
+        <v>17.75167009777962</v>
+      </c>
+      <c r="E70">
+        <v>9.216000000000008</v>
+      </c>
+      <c r="F70">
+        <v>41.61600000000001</v>
+      </c>
+      <c r="G70">
+        <v>0.492</v>
+      </c>
+      <c r="H70">
+        <v>28.8</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>6.23</v>
+      </c>
+      <c r="L70">
+        <v>-6.23</v>
+      </c>
+      <c r="M70">
+        <v>9.937900800000001</v>
+      </c>
+      <c r="N70">
+        <v>-16.1679008</v>
+      </c>
+      <c r="O70">
+        <v>-3.556938176000001</v>
+      </c>
+      <c r="P70">
+        <v>-12.610962624</v>
+      </c>
+      <c r="Q70">
+        <v>-6.380962624</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.27947892462639</v>
+      </c>
+      <c r="T70">
+        <v>3.259176614828366</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>-0.1379164501219412</v>
+      </c>
+      <c r="W70">
+        <v>0.2717344482891196</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>-0.6268929550997329</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2762126807170461</v>
+      </c>
+      <c r="C71">
+        <v>-24.13387263131275</v>
+      </c>
+      <c r="D71">
+        <v>17.60212736868726</v>
+      </c>
+      <c r="E71">
+        <v>9.82800000000001</v>
+      </c>
+      <c r="F71">
+        <v>42.22800000000001</v>
+      </c>
+      <c r="G71">
+        <v>0.492</v>
+      </c>
+      <c r="H71">
+        <v>28.8</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>6.23</v>
+      </c>
+      <c r="L71">
+        <v>-6.23</v>
+      </c>
+      <c r="M71">
+        <v>10.0840464</v>
+      </c>
+      <c r="N71">
+        <v>-16.3140464</v>
+      </c>
+      <c r="O71">
+        <v>-3.589090208</v>
+      </c>
+      <c r="P71">
+        <v>-12.724956192</v>
+      </c>
+      <c r="Q71">
+        <v>-6.494956192000002</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2872427609046607</v>
+      </c>
+      <c r="T71">
+        <v>3.364311344338959</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>-0.1359176609897392</v>
+      </c>
+      <c r="W71">
+        <v>0.2712571374443498</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>-0.61780754995336</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2782126807170461</v>
+      </c>
+      <c r="C72">
+        <v>-24.89291686736547</v>
+      </c>
+      <c r="D72">
+        <v>17.45508313263453</v>
+      </c>
+      <c r="E72">
+        <v>10.44</v>
+      </c>
+      <c r="F72">
+        <v>42.84</v>
+      </c>
+      <c r="G72">
+        <v>0.492</v>
+      </c>
+      <c r="H72">
+        <v>28.8</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>6.23</v>
+      </c>
+      <c r="L72">
+        <v>-6.23</v>
+      </c>
+      <c r="M72">
+        <v>10.230192</v>
+      </c>
+      <c r="N72">
+        <v>-16.460192</v>
+      </c>
+      <c r="O72">
+        <v>-3.62124224</v>
+      </c>
+      <c r="P72">
+        <v>-12.83894976</v>
+      </c>
+      <c r="Q72">
+        <v>-6.608949759999998</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2955241862681494</v>
+      </c>
+      <c r="T72">
+        <v>3.476455055816924</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>-0.1339759801184572</v>
+      </c>
+      <c r="W72">
+        <v>0.2707934640522876</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>-0.6089817278111689</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2802126807170461</v>
+      </c>
+      <c r="C73">
+        <v>-25.64952470719218</v>
+      </c>
+      <c r="D73">
+        <v>17.31047529280782</v>
+      </c>
+      <c r="E73">
+        <v>11.052</v>
+      </c>
+      <c r="F73">
+        <v>43.452</v>
+      </c>
+      <c r="G73">
+        <v>0.492</v>
+      </c>
+      <c r="H73">
+        <v>28.8</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>6.23</v>
+      </c>
+      <c r="L73">
+        <v>-6.23</v>
+      </c>
+      <c r="M73">
+        <v>10.3763376</v>
+      </c>
+      <c r="N73">
+        <v>-16.6063376</v>
+      </c>
+      <c r="O73">
+        <v>-3.653394272</v>
+      </c>
+      <c r="P73">
+        <v>-12.952943328</v>
+      </c>
+      <c r="Q73">
+        <v>-6.722943327999999</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3043767444153269</v>
+      </c>
+      <c r="T73">
+        <v>3.596332816362334</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>-0.132088994482986</v>
+      </c>
+      <c r="W73">
+        <v>0.270342851882537</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>-0.600404520377209</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2822126807170461</v>
+      </c>
+      <c r="C74">
+        <v>-26.40375620673291</v>
+      </c>
+      <c r="D74">
+        <v>17.16824379326708</v>
+      </c>
+      <c r="E74">
+        <v>11.664</v>
+      </c>
+      <c r="F74">
+        <v>44.064</v>
+      </c>
+      <c r="G74">
+        <v>0.492</v>
+      </c>
+      <c r="H74">
+        <v>28.8</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>6.23</v>
+      </c>
+      <c r="L74">
+        <v>-6.23</v>
+      </c>
+      <c r="M74">
+        <v>10.5224832</v>
+      </c>
+      <c r="N74">
+        <v>-16.7524832</v>
+      </c>
+      <c r="O74">
+        <v>-3.685546304</v>
+      </c>
+      <c r="P74">
+        <v>-13.066936896</v>
+      </c>
+      <c r="Q74">
+        <v>-6.836936895999999</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3138616281444457</v>
+      </c>
+      <c r="T74">
+        <v>3.72477327408956</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>-0.1302544251151667</v>
+      </c>
+      <c r="W74">
+        <v>0.2699047567175018</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>-0.5920655687053034</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2842126807170461</v>
+      </c>
+      <c r="C75">
+        <v>-27.15566946421501</v>
+      </c>
+      <c r="D75">
+        <v>17.02833053578499</v>
+      </c>
+      <c r="E75">
+        <v>12.276</v>
+      </c>
+      <c r="F75">
+        <v>44.676</v>
+      </c>
+      <c r="G75">
+        <v>0.492</v>
+      </c>
+      <c r="H75">
+        <v>28.8</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>6.23</v>
+      </c>
+      <c r="L75">
+        <v>-6.23</v>
+      </c>
+      <c r="M75">
+        <v>10.6686288</v>
+      </c>
+      <c r="N75">
+        <v>-16.8986288</v>
+      </c>
+      <c r="O75">
+        <v>-3.717698336</v>
+      </c>
+      <c r="P75">
+        <v>-13.180930464</v>
+      </c>
+      <c r="Q75">
+        <v>-6.950930464000001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3240490958534992</v>
+      </c>
+      <c r="T75">
+        <v>3.862727839796581</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>-0.1284701179218083</v>
+      </c>
+      <c r="W75">
+        <v>0.2694786641597279</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>-0.583955081462765</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2862126807170461</v>
+      </c>
+      <c r="C76">
+        <v>-27.90532069928052</v>
+      </c>
+      <c r="D76">
+        <v>16.89067930071948</v>
+      </c>
+      <c r="E76">
+        <v>12.88800000000001</v>
+      </c>
+      <c r="F76">
+        <v>45.288</v>
+      </c>
+      <c r="G76">
+        <v>0.492</v>
+      </c>
+      <c r="H76">
+        <v>28.8</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>6.23</v>
+      </c>
+      <c r="L76">
+        <v>-6.23</v>
+      </c>
+      <c r="M76">
+        <v>10.8147744</v>
+      </c>
+      <c r="N76">
+        <v>-17.0447744</v>
+      </c>
+      <c r="O76">
+        <v>-3.749850368</v>
+      </c>
+      <c r="P76">
+        <v>-13.294924032</v>
+      </c>
+      <c r="Q76">
+        <v>-7.064924032</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3350202149247876</v>
+      </c>
+      <c r="T76">
+        <v>4.011294295173372</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>-0.1267340352471893</v>
+      </c>
+      <c r="W76">
+        <v>0.2690640876170288</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>-0.576063796578133</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2882126807170461</v>
+      </c>
+      <c r="C77">
+        <v>-28.6527643283066</v>
+      </c>
+      <c r="D77">
+        <v>16.75523567169341</v>
+      </c>
+      <c r="E77">
+        <v>13.50000000000001</v>
+      </c>
+      <c r="F77">
+        <v>45.90000000000001</v>
+      </c>
+      <c r="G77">
+        <v>0.492</v>
+      </c>
+      <c r="H77">
+        <v>28.8</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>6.23</v>
+      </c>
+      <c r="L77">
+        <v>-6.23</v>
+      </c>
+      <c r="M77">
+        <v>10.96092</v>
+      </c>
+      <c r="N77">
+        <v>-17.19092</v>
+      </c>
+      <c r="O77">
+        <v>-3.782002400000001</v>
+      </c>
+      <c r="P77">
+        <v>-13.4089176</v>
+      </c>
+      <c r="Q77">
+        <v>-7.178917600000002</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3468690235217791</v>
+      </c>
+      <c r="T77">
+        <v>4.171746066980307</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>-0.1250442481105601</v>
+      </c>
+      <c r="W77">
+        <v>0.2686605664488018</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>-0.568382945957091</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2902126807170461</v>
+      </c>
+      <c r="C78">
+        <v>-29.39805303613077</v>
+      </c>
+      <c r="D78">
+        <v>16.62194696386923</v>
+      </c>
+      <c r="E78">
+        <v>14.112</v>
+      </c>
+      <c r="F78">
+        <v>46.512</v>
+      </c>
+      <c r="G78">
+        <v>0.492</v>
+      </c>
+      <c r="H78">
+        <v>28.8</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>6.23</v>
+      </c>
+      <c r="L78">
+        <v>-6.23</v>
+      </c>
+      <c r="M78">
+        <v>11.1070656</v>
+      </c>
+      <c r="N78">
+        <v>-17.3370656</v>
+      </c>
+      <c r="O78">
+        <v>-3.814154432</v>
+      </c>
+      <c r="P78">
+        <v>-13.522911168</v>
+      </c>
+      <c r="Q78">
+        <v>-7.292911168000002</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3597052328351867</v>
+      </c>
+      <c r="T78">
+        <v>4.345568819771154</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>-0.1233989290564737</v>
+      </c>
+      <c r="W78">
+        <v>0.2682676642586859</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>-0.5609042229839718</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2922126807170461</v>
+      </c>
+      <c r="C79">
+        <v>-30.14123784437981</v>
+      </c>
+      <c r="D79">
+        <v>16.4907621556202</v>
+      </c>
+      <c r="E79">
+        <v>14.724</v>
+      </c>
+      <c r="F79">
+        <v>47.124</v>
+      </c>
+      <c r="G79">
+        <v>0.492</v>
+      </c>
+      <c r="H79">
+        <v>28.8</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>6.23</v>
+      </c>
+      <c r="L79">
+        <v>-6.23</v>
+      </c>
+      <c r="M79">
+        <v>11.2532112</v>
+      </c>
+      <c r="N79">
+        <v>-17.4832112</v>
+      </c>
+      <c r="O79">
+        <v>-3.846306464</v>
+      </c>
+      <c r="P79">
+        <v>-13.636904736</v>
+      </c>
+      <c r="Q79">
+        <v>-7.406904736</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3736576342628035</v>
+      </c>
+      <c r="T79">
+        <v>4.534506594543813</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>-0.1217963455622338</v>
+      </c>
+      <c r="W79">
+        <v>0.2678849673202614</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>-0.5536197525556081</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2942126807170461</v>
+      </c>
+      <c r="C80">
+        <v>-30.88236817658825</v>
+      </c>
+      <c r="D80">
+        <v>16.36163182341176</v>
+      </c>
+      <c r="E80">
+        <v>15.33600000000001</v>
+      </c>
+      <c r="F80">
+        <v>47.736</v>
+      </c>
+      <c r="G80">
+        <v>0.492</v>
+      </c>
+      <c r="H80">
+        <v>28.8</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>6.23</v>
+      </c>
+      <c r="L80">
+        <v>-6.23</v>
+      </c>
+      <c r="M80">
+        <v>11.3993568</v>
+      </c>
+      <c r="N80">
+        <v>-17.6293568</v>
+      </c>
+      <c r="O80">
+        <v>-3.878458496000001</v>
+      </c>
+      <c r="P80">
+        <v>-13.750898304</v>
+      </c>
+      <c r="Q80">
+        <v>-7.520898304000003</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3888784358202037</v>
+      </c>
+      <c r="T80">
+        <v>4.740620530659442</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>-0.1202348539524616</v>
+      </c>
+      <c r="W80">
+        <v>0.2675120831238478</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>-0.5465220634202801</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2962126807170461</v>
+      </c>
+      <c r="C81">
+        <v>-31.62149192028133</v>
+      </c>
+      <c r="D81">
+        <v>16.23450807971868</v>
+      </c>
+      <c r="E81">
+        <v>15.94800000000001</v>
+      </c>
+      <c r="F81">
+        <v>48.34800000000001</v>
+      </c>
+      <c r="G81">
+        <v>0.492</v>
+      </c>
+      <c r="H81">
+        <v>28.8</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>6.23</v>
+      </c>
+      <c r="L81">
+        <v>-6.23</v>
+      </c>
+      <c r="M81">
+        <v>11.5455024</v>
+      </c>
+      <c r="N81">
+        <v>-17.7755024</v>
+      </c>
+      <c r="O81">
+        <v>-3.910610528</v>
+      </c>
+      <c r="P81">
+        <v>-13.864891872</v>
+      </c>
+      <c r="Q81">
+        <v>-7.634891872000001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.4055488375259277</v>
+      </c>
+      <c r="T81">
+        <v>4.966364365452749</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>-0.1187128937758481</v>
+      </c>
+      <c r="W81">
+        <v>0.2671486390336725</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>-0.5396040626174914</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2982126807170461</v>
+      </c>
+      <c r="C82">
+        <v>-32.35865548618601</v>
+      </c>
+      <c r="D82">
+        <v>16.10934451381399</v>
+      </c>
+      <c r="E82">
+        <v>16.56000000000001</v>
+      </c>
+      <c r="F82">
+        <v>48.96000000000001</v>
+      </c>
+      <c r="G82">
+        <v>0.492</v>
+      </c>
+      <c r="H82">
+        <v>28.8</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>6.23</v>
+      </c>
+      <c r="L82">
+        <v>-6.23</v>
+      </c>
+      <c r="M82">
+        <v>11.691648</v>
+      </c>
+      <c r="N82">
+        <v>-17.921648</v>
+      </c>
+      <c r="O82">
+        <v>-3.942762560000001</v>
+      </c>
+      <c r="P82">
+        <v>-13.97888544</v>
+      </c>
+      <c r="Q82">
+        <v>-7.748885440000002</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4238862794022241</v>
+      </c>
+      <c r="T82">
+        <v>5.214682583725386</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>-0.11722898260365</v>
+      </c>
+      <c r="W82">
+        <v>0.2667942810457516</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>-0.5328590118347731</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.3002126807170462</v>
+      </c>
+      <c r="C83">
+        <v>-33.09390386472393</v>
+      </c>
+      <c r="D83">
+        <v>15.98609613527607</v>
+      </c>
+      <c r="E83">
+        <v>17.172</v>
+      </c>
+      <c r="F83">
+        <v>49.572</v>
+      </c>
+      <c r="G83">
+        <v>0.492</v>
+      </c>
+      <c r="H83">
+        <v>28.8</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>6.23</v>
+      </c>
+      <c r="L83">
+        <v>-6.23</v>
+      </c>
+      <c r="M83">
+        <v>11.8377936</v>
+      </c>
+      <c r="N83">
+        <v>-18.0677936</v>
+      </c>
+      <c r="O83">
+        <v>-3.974914592</v>
+      </c>
+      <c r="P83">
+        <v>-14.092879008</v>
+      </c>
+      <c r="Q83">
+        <v>-7.862879008</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4441539783181307</v>
+      </c>
+      <c r="T83">
+        <v>5.489139561816197</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>-0.1157817112134815</v>
+      </c>
+      <c r="W83">
+        <v>0.2664486726377794</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>-0.5262805055158251</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.3022126807170461</v>
+      </c>
+      <c r="C84">
+        <v>-33.82728067993085</v>
+      </c>
+      <c r="D84">
+        <v>15.86471932006916</v>
+      </c>
+      <c r="E84">
+        <v>17.78400000000001</v>
+      </c>
+      <c r="F84">
+        <v>50.184</v>
+      </c>
+      <c r="G84">
+        <v>0.492</v>
+      </c>
+      <c r="H84">
+        <v>28.8</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>6.23</v>
+      </c>
+      <c r="L84">
+        <v>-6.23</v>
+      </c>
+      <c r="M84">
+        <v>11.9839392</v>
+      </c>
+      <c r="N84">
+        <v>-18.2139392</v>
+      </c>
+      <c r="O84">
+        <v>-4.007066624</v>
+      </c>
+      <c r="P84">
+        <v>-14.206872576</v>
+      </c>
+      <c r="Q84">
+        <v>-7.976872576000002</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.466673643780249</v>
+      </c>
+      <c r="T84">
+        <v>5.794091759694874</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>-0.1143697391255122</v>
+      </c>
+      <c r="W84">
+        <v>0.2661114937031723</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>-0.5198624505705103</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.3042126807170461</v>
+      </c>
+      <c r="C85">
+        <v>-34.55882824093818</v>
+      </c>
+      <c r="D85">
+        <v>15.74517175906183</v>
+      </c>
+      <c r="E85">
+        <v>18.39600000000001</v>
+      </c>
+      <c r="F85">
+        <v>50.79600000000001</v>
+      </c>
+      <c r="G85">
+        <v>0.492</v>
+      </c>
+      <c r="H85">
+        <v>28.8</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>6.23</v>
+      </c>
+      <c r="L85">
+        <v>-6.23</v>
+      </c>
+      <c r="M85">
+        <v>12.1300848</v>
+      </c>
+      <c r="N85">
+        <v>-18.3600848</v>
+      </c>
+      <c r="O85">
+        <v>-4.039218656000001</v>
+      </c>
+      <c r="P85">
+        <v>-14.320866144</v>
+      </c>
+      <c r="Q85">
+        <v>-8.090866144000001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4918426816496755</v>
+      </c>
+      <c r="T85">
+        <v>6.134920686735749</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>-0.1129917904613494</v>
+      </c>
+      <c r="W85">
+        <v>0.2657824395621702</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>-0.5135990475515884</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.3062126807170461</v>
+      </c>
+      <c r="C86">
+        <v>-35.28858759114432</v>
+      </c>
+      <c r="D86">
+        <v>15.62741240885568</v>
+      </c>
+      <c r="E86">
+        <v>19.008</v>
+      </c>
+      <c r="F86">
+        <v>51.408</v>
+      </c>
+      <c r="G86">
+        <v>0.492</v>
+      </c>
+      <c r="H86">
+        <v>28.8</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>6.23</v>
+      </c>
+      <c r="L86">
+        <v>-6.23</v>
+      </c>
+      <c r="M86">
+        <v>12.2762304</v>
+      </c>
+      <c r="N86">
+        <v>-18.5062304</v>
+      </c>
+      <c r="O86">
+        <v>-4.071370688</v>
+      </c>
+      <c r="P86">
+        <v>-14.434859712</v>
+      </c>
+      <c r="Q86">
+        <v>-8.204859711999999</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.5201578492527799</v>
+      </c>
+      <c r="T86">
+        <v>6.51835322965673</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>-0.1116466500987143</v>
+      </c>
+      <c r="W86">
+        <v>0.265461220043573</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>-0.5074847731759742</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.3082126807170461</v>
+      </c>
+      <c r="C87">
+        <v>-36.01659855519593</v>
+      </c>
+      <c r="D87">
+        <v>15.51140144480408</v>
+      </c>
+      <c r="E87">
+        <v>19.62</v>
+      </c>
+      <c r="F87">
+        <v>52.02</v>
+      </c>
+      <c r="G87">
+        <v>0.492</v>
+      </c>
+      <c r="H87">
+        <v>28.8</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>6.23</v>
+      </c>
+      <c r="L87">
+        <v>-6.23</v>
+      </c>
+      <c r="M87">
+        <v>12.422376</v>
+      </c>
+      <c r="N87">
+        <v>-18.652376</v>
+      </c>
+      <c r="O87">
+        <v>-4.103522720000001</v>
+      </c>
+      <c r="P87">
+        <v>-14.54885328</v>
+      </c>
+      <c r="Q87">
+        <v>-8.318853280000003</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5522483725362985</v>
+      </c>
+      <c r="T87">
+        <v>6.952910111633846</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>-0.110333160097553</v>
+      </c>
+      <c r="W87">
+        <v>0.2651475586312957</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>-0.5015143640797866</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.3102126807170462</v>
+      </c>
+      <c r="C88">
+        <v>-36.74289978389184</v>
+      </c>
+      <c r="D88">
+        <v>15.39710021610816</v>
+      </c>
+      <c r="E88">
+        <v>20.23200000000001</v>
+      </c>
+      <c r="F88">
+        <v>52.63200000000001</v>
+      </c>
+      <c r="G88">
+        <v>0.492</v>
+      </c>
+      <c r="H88">
+        <v>28.8</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>6.23</v>
+      </c>
+      <c r="L88">
+        <v>-6.23</v>
+      </c>
+      <c r="M88">
+        <v>12.5685216</v>
+      </c>
+      <c r="N88">
+        <v>-18.7985216</v>
+      </c>
+      <c r="O88">
+        <v>-4.135674752</v>
+      </c>
+      <c r="P88">
+        <v>-14.662846848</v>
+      </c>
+      <c r="Q88">
+        <v>-8.432846848000001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5889232562888915</v>
+      </c>
+      <c r="T88">
+        <v>7.449546548179121</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>-0.1090502163754884</v>
+      </c>
+      <c r="W88">
+        <v>0.2648411916704667</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>-0.4956828017067654</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.3122126807170461</v>
+      </c>
+      <c r="C89">
+        <v>-37.46752879711629</v>
+      </c>
+      <c r="D89">
+        <v>15.28447120288371</v>
+      </c>
+      <c r="E89">
+        <v>20.844</v>
+      </c>
+      <c r="F89">
+        <v>53.244</v>
+      </c>
+      <c r="G89">
+        <v>0.492</v>
+      </c>
+      <c r="H89">
+        <v>28.8</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>6.23</v>
+      </c>
+      <c r="L89">
+        <v>-6.23</v>
+      </c>
+      <c r="M89">
+        <v>12.7146672</v>
+      </c>
+      <c r="N89">
+        <v>-18.9446672</v>
+      </c>
+      <c r="O89">
+        <v>-4.167826784000001</v>
+      </c>
+      <c r="P89">
+        <v>-14.776840416</v>
+      </c>
+      <c r="Q89">
+        <v>-8.546840416</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.6312404298495753</v>
+      </c>
+      <c r="T89">
+        <v>8.022588590346745</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>-0.1077967656125518</v>
+      </c>
+      <c r="W89">
+        <v>0.2645418676282774</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>-0.4899852982388717</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3142126807170461</v>
+      </c>
+      <c r="C90">
+        <v>-38.19052202490153</v>
+      </c>
+      <c r="D90">
+        <v>15.17347797509848</v>
+      </c>
+      <c r="E90">
+        <v>21.456</v>
+      </c>
+      <c r="F90">
+        <v>53.856</v>
+      </c>
+      <c r="G90">
+        <v>0.492</v>
+      </c>
+      <c r="H90">
+        <v>28.8</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>6.23</v>
+      </c>
+      <c r="L90">
+        <v>-6.23</v>
+      </c>
+      <c r="M90">
+        <v>12.8608128</v>
+      </c>
+      <c r="N90">
+        <v>-19.0908128</v>
+      </c>
+      <c r="O90">
+        <v>-4.199978816000001</v>
+      </c>
+      <c r="P90">
+        <v>-14.890833984</v>
+      </c>
+      <c r="Q90">
+        <v>-8.660833984</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6806104656703733</v>
+      </c>
+      <c r="T90">
+        <v>8.691137639542308</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>-0.1065718023669546</v>
+      </c>
+      <c r="W90">
+        <v>0.2642493464052288</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>-0.4844172834861573</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3162126807170461</v>
+      </c>
+      <c r="C91">
+        <v>-38.91191484671398</v>
+      </c>
+      <c r="D91">
+        <v>15.06408515328602</v>
+      </c>
+      <c r="E91">
+        <v>22.068</v>
+      </c>
+      <c r="F91">
+        <v>54.468</v>
+      </c>
+      <c r="G91">
+        <v>0.492</v>
+      </c>
+      <c r="H91">
+        <v>28.8</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <v>6.23</v>
+      </c>
+      <c r="L91">
+        <v>-6.23</v>
+      </c>
+      <c r="M91">
+        <v>13.0069584</v>
+      </c>
+      <c r="N91">
+        <v>-19.2369584</v>
+      </c>
+      <c r="O91">
+        <v>-4.232130848000001</v>
+      </c>
+      <c r="P91">
+        <v>-15.004827552</v>
+      </c>
+      <c r="Q91">
+        <v>-8.774827552000001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.7389568716404074</v>
+      </c>
+      <c r="T91">
+        <v>9.481241061318883</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>-0.1053743663853034</v>
+      </c>
+      <c r="W91">
+        <v>0.2639633986928105</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>-0.4789743926604701</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3182126807170461</v>
+      </c>
+      <c r="C92">
+        <v>-39.63174162905348</v>
+      </c>
+      <c r="D92">
+        <v>14.95625837094652</v>
+      </c>
+      <c r="E92">
+        <v>22.68000000000001</v>
+      </c>
+      <c r="F92">
+        <v>55.08000000000001</v>
+      </c>
+      <c r="G92">
+        <v>0.492</v>
+      </c>
+      <c r="H92">
+        <v>28.8</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92">
+        <v>6.23</v>
+      </c>
+      <c r="L92">
+        <v>-6.23</v>
+      </c>
+      <c r="M92">
+        <v>13.153104</v>
+      </c>
+      <c r="N92">
+        <v>-19.383104</v>
+      </c>
+      <c r="O92">
+        <v>-4.264282880000001</v>
+      </c>
+      <c r="P92">
+        <v>-15.11882112</v>
+      </c>
+      <c r="Q92">
+        <v>-8.888821120000003</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.8089725588044481</v>
+      </c>
+      <c r="T92">
+        <v>10.42936516745077</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>-0.1042035400921334</v>
+      </c>
+      <c r="W92">
+        <v>0.2636838053740014</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>-0.4736524549642427</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3202126807170461</v>
+      </c>
+      <c r="C93">
+        <v>-40.35003576144893</v>
+      </c>
+      <c r="D93">
+        <v>14.84996423855108</v>
+      </c>
+      <c r="E93">
+        <v>23.29200000000001</v>
+      </c>
+      <c r="F93">
+        <v>55.69200000000001</v>
+      </c>
+      <c r="G93">
+        <v>0.492</v>
+      </c>
+      <c r="H93">
+        <v>28.8</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>6.23</v>
+      </c>
+      <c r="L93">
+        <v>-6.23</v>
+      </c>
+      <c r="M93">
+        <v>13.2992496</v>
+      </c>
+      <c r="N93">
+        <v>-19.5292496</v>
+      </c>
+      <c r="O93">
+        <v>-4.296434912</v>
+      </c>
+      <c r="P93">
+        <v>-15.232814688</v>
+      </c>
+      <c r="Q93">
+        <v>-9.002814688000003</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.8945472875604981</v>
+      </c>
+      <c r="T93">
+        <v>11.58818351938975</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>-0.1030584462449671</v>
+      </c>
+      <c r="W93">
+        <v>0.2634103569632982</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>-0.4684474829316685</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3222126807170461</v>
+      </c>
+      <c r="C94">
+        <v>-41.06682969092999</v>
+      </c>
+      <c r="D94">
+        <v>14.74517030907001</v>
+      </c>
+      <c r="E94">
+        <v>23.904</v>
+      </c>
+      <c r="F94">
+        <v>56.304</v>
+      </c>
+      <c r="G94">
+        <v>0.492</v>
+      </c>
+      <c r="H94">
+        <v>28.8</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <v>6.23</v>
+      </c>
+      <c r="L94">
+        <v>-6.23</v>
+      </c>
+      <c r="M94">
+        <v>13.4453952</v>
+      </c>
+      <c r="N94">
+        <v>-19.6753952</v>
+      </c>
+      <c r="O94">
+        <v>-4.328586944000001</v>
+      </c>
+      <c r="P94">
+        <v>-15.346808256</v>
+      </c>
+      <c r="Q94">
+        <v>-9.116808256000002</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.00151569850556</v>
+      </c>
+      <c r="T94">
+        <v>13.03670645931347</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>-0.1019382457423044</v>
+      </c>
+      <c r="W94">
+        <v>0.2631428530832623</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>-0.4633556624650201</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3242126807170461</v>
+      </c>
+      <c r="C95">
+        <v>-41.78215495504948</v>
+      </c>
+      <c r="D95">
+        <v>14.64184504495052</v>
+      </c>
+      <c r="E95">
+        <v>24.51600000000001</v>
+      </c>
+      <c r="F95">
+        <v>56.916</v>
+      </c>
+      <c r="G95">
+        <v>0.492</v>
+      </c>
+      <c r="H95">
+        <v>28.8</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>6.23</v>
+      </c>
+      <c r="L95">
+        <v>-6.23</v>
+      </c>
+      <c r="M95">
+        <v>13.5915408</v>
+      </c>
+      <c r="N95">
+        <v>-19.8215408</v>
+      </c>
+      <c r="O95">
+        <v>-4.360738976</v>
+      </c>
+      <c r="P95">
+        <v>-15.460801824</v>
+      </c>
+      <c r="Q95">
+        <v>-9.230801824</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.139046512577784</v>
+      </c>
+      <c r="T95">
+        <v>14.89909309635825</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>-0.1008421355730323</v>
+      </c>
+      <c r="W95">
+        <v>0.2628811019748401</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>-0.4583733435137831</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3262126807170461</v>
+      </c>
+      <c r="C96">
+        <v>-42.49604221352688</v>
+      </c>
+      <c r="D96">
+        <v>14.53995778647313</v>
+      </c>
+      <c r="E96">
+        <v>25.12800000000001</v>
+      </c>
+      <c r="F96">
+        <v>57.52800000000001</v>
+      </c>
+      <c r="G96">
+        <v>0.492</v>
+      </c>
+      <c r="H96">
+        <v>28.8</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>6.23</v>
+      </c>
+      <c r="L96">
+        <v>-6.23</v>
+      </c>
+      <c r="M96">
+        <v>13.7376864</v>
+      </c>
+      <c r="N96">
+        <v>-19.96768640000001</v>
+      </c>
+      <c r="O96">
+        <v>-4.392891008000001</v>
+      </c>
+      <c r="P96">
+        <v>-15.574795392</v>
+      </c>
+      <c r="Q96">
+        <v>-9.344795392000004</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.322420931340748</v>
+      </c>
+      <c r="T96">
+        <v>17.38227527908463</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>-0.09976934689672344</v>
+      </c>
+      <c r="W96">
+        <v>0.2626249200389376</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>-0.453497031348743</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3282126807170462</v>
+      </c>
+      <c r="C97">
+        <v>-43.20852127857994</v>
+      </c>
+      <c r="D97">
+        <v>14.43947872142007</v>
+      </c>
+      <c r="E97">
+        <v>25.74000000000001</v>
+      </c>
+      <c r="F97">
+        <v>58.14000000000001</v>
+      </c>
+      <c r="G97">
+        <v>0.492</v>
+      </c>
+      <c r="H97">
+        <v>28.8</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>6.23</v>
+      </c>
+      <c r="L97">
+        <v>-6.23</v>
+      </c>
+      <c r="M97">
+        <v>13.883832</v>
+      </c>
+      <c r="N97">
+        <v>-20.113832</v>
+      </c>
+      <c r="O97">
+        <v>-4.42504304</v>
+      </c>
+      <c r="P97">
+        <v>-15.68878896</v>
+      </c>
+      <c r="Q97">
+        <v>-9.458788960000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.579145117608898</v>
+      </c>
+      <c r="T97">
+        <v>20.85873033490157</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>-0.098719143245179</v>
+      </c>
+      <c r="W97">
+        <v>0.2623741314069488</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>-0.4487233783871771</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3302126807170461</v>
+      </c>
+      <c r="C98">
+        <v>-43.91962114400714</v>
+      </c>
+      <c r="D98">
+        <v>14.34037885599287</v>
+      </c>
+      <c r="E98">
+        <v>26.352</v>
+      </c>
+      <c r="F98">
+        <v>58.752</v>
+      </c>
+      <c r="G98">
+        <v>0.492</v>
+      </c>
+      <c r="H98">
+        <v>28.8</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <v>6.23</v>
+      </c>
+      <c r="L98">
+        <v>-6.23</v>
+      </c>
+      <c r="M98">
+        <v>14.0299776</v>
+      </c>
+      <c r="N98">
+        <v>-20.2599776</v>
+      </c>
+      <c r="O98">
+        <v>-4.457195072</v>
+      </c>
+      <c r="P98">
+        <v>-15.802782528</v>
+      </c>
+      <c r="Q98">
+        <v>-9.572782527999998</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.964231397011118</v>
+      </c>
+      <c r="T98">
+        <v>26.0734129186269</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>-0.09769081883637505</v>
+      </c>
+      <c r="W98">
+        <v>0.2621285675381264</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>-0.4440491765289774</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3322126807170461</v>
+      </c>
+      <c r="C99">
+        <v>-44.62937001308087</v>
+      </c>
+      <c r="D99">
+        <v>14.24262998691913</v>
+      </c>
+      <c r="E99">
+        <v>26.96400000000001</v>
+      </c>
+      <c r="F99">
+        <v>59.364</v>
+      </c>
+      <c r="G99">
+        <v>0.492</v>
+      </c>
+      <c r="H99">
+        <v>28.8</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99">
+        <v>6.23</v>
+      </c>
+      <c r="L99">
+        <v>-6.23</v>
+      </c>
+      <c r="M99">
+        <v>14.1761232</v>
+      </c>
+      <c r="N99">
+        <v>-20.4061232</v>
+      </c>
+      <c r="O99">
+        <v>-4.489347104000001</v>
+      </c>
+      <c r="P99">
+        <v>-15.916776096</v>
+      </c>
+      <c r="Q99">
+        <v>-9.686776096000003</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.606041862681491</v>
+      </c>
+      <c r="T99">
+        <v>34.7645505581692</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>-0.09668369699270107</v>
+      </c>
+      <c r="W99">
+        <v>0.261888066841857</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>-0.4394713499668232</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3342126807170461</v>
+      </c>
+      <c r="C100">
+        <v>-45.33779532530747</v>
+      </c>
+      <c r="D100">
+        <v>14.14620467469253</v>
+      </c>
+      <c r="E100">
+        <v>27.576</v>
+      </c>
+      <c r="F100">
+        <v>59.976</v>
+      </c>
+      <c r="G100">
+        <v>0.492</v>
+      </c>
+      <c r="H100">
+        <v>28.8</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <v>6.23</v>
+      </c>
+      <c r="L100">
+        <v>-6.23</v>
+      </c>
+      <c r="M100">
+        <v>14.3222688</v>
+      </c>
+      <c r="N100">
+        <v>-20.5522688</v>
+      </c>
+      <c r="O100">
+        <v>-4.521499136</v>
+      </c>
+      <c r="P100">
+        <v>-16.030769664</v>
+      </c>
+      <c r="Q100">
+        <v>-9.800769664000001</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.889662794022236</v>
+      </c>
+      <c r="T100">
+        <v>52.1468258372538</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>-0.09569712865604087</v>
+      </c>
+      <c r="W100">
+        <v>0.2616524743230625</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>-0.4349869484365494</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3362126807170461</v>
+      </c>
+      <c r="C101">
+        <v>-46.04492378210755</v>
+      </c>
+      <c r="D101">
+        <v>14.05107621789245</v>
+      </c>
+      <c r="E101">
+        <v>28.188</v>
+      </c>
+      <c r="F101">
+        <v>60.588</v>
+      </c>
+      <c r="G101">
+        <v>0.492</v>
+      </c>
+      <c r="H101">
+        <v>28.8</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>6.23</v>
+      </c>
+      <c r="L101">
+        <v>-6.23</v>
+      </c>
+      <c r="M101">
+        <v>14.4684144</v>
+      </c>
+      <c r="N101">
+        <v>-20.6984144</v>
+      </c>
+      <c r="O101">
+        <v>-4.553651168</v>
+      </c>
+      <c r="P101">
+        <v>-16.144763232</v>
+      </c>
+      <c r="Q101">
+        <v>-9.914763232000002</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>7.740525588044473</v>
+      </c>
+      <c r="T101">
+        <v>104.2936516745076</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>-0.09473049099284853</v>
+      </c>
+      <c r="W101">
+        <v>0.2614216412490922</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>-0.4305931408765842</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/curacao/curacao_business_consumer_services.xlsx
+++ b/research/traditional_assets/database/data/curacao/curacao_business_consumer_services.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1150689396235904</v>
+        <v>0.1148508879564185</v>
       </c>
       <c r="C2">
-        <v>63.29129677411435</v>
+        <v>62.85388584084324</v>
       </c>
       <c r="D2">
-        <v>63.20429677411435</v>
+        <v>63.40388584084324</v>
       </c>
       <c r="E2">
-        <v>-30.6</v>
+        <v>-29.963</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.637</v>
       </c>
       <c r="G2">
         <v>0.08699999999999999</v>
@@ -1439,28 +1439,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0320411</v>
       </c>
       <c r="N2">
-        <v>9.77888888888889</v>
+        <v>9.746847788888889</v>
       </c>
       <c r="O2">
-        <v>2.151355555555556</v>
+        <v>2.144306513555556</v>
       </c>
       <c r="P2">
-        <v>7.627533333333334</v>
+        <v>7.602541275333333</v>
       </c>
       <c r="Q2">
-        <v>16.73753333333333</v>
+        <v>16.71254127533333</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1150689396235904</v>
+        <v>0.1156146949054732</v>
       </c>
       <c r="T2">
-        <v>0.9535130270927493</v>
+        <v>0.9610255539728739</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>305.1982887256958</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1148508879564185</v>
+        <v>0.1146328362892466</v>
       </c>
       <c r="C3">
-        <v>62.85388584084324</v>
+        <v>62.4177394415096</v>
       </c>
       <c r="D3">
-        <v>63.40388584084324</v>
+        <v>63.60473944150959</v>
       </c>
       <c r="E3">
-        <v>-29.963</v>
+        <v>-29.326</v>
       </c>
       <c r="F3">
-        <v>0.637</v>
+        <v>1.274</v>
       </c>
       <c r="G3">
         <v>0.08699999999999999</v>
@@ -1521,28 +1521,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M3">
-        <v>0.0320411</v>
+        <v>0.06408219999999999</v>
       </c>
       <c r="N3">
-        <v>9.746847788888889</v>
+        <v>9.71480668888889</v>
       </c>
       <c r="O3">
-        <v>2.144306513555556</v>
+        <v>2.137257471555556</v>
       </c>
       <c r="P3">
-        <v>7.602541275333333</v>
+        <v>7.577549217333335</v>
       </c>
       <c r="Q3">
-        <v>16.71254127533333</v>
+        <v>16.68754921733333</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1156146949054732</v>
+        <v>0.1161715880502516</v>
       </c>
       <c r="T3">
-        <v>0.9610255539728739</v>
+        <v>0.9686913977281033</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>305.1982887256958</v>
+        <v>152.5991443628479</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1146328362892466</v>
+        <v>0.1144147846220747</v>
       </c>
       <c r="C4">
-        <v>62.4177394415096</v>
+        <v>61.98286963184168</v>
       </c>
       <c r="D4">
-        <v>63.60473944150959</v>
+        <v>63.80686963184168</v>
       </c>
       <c r="E4">
-        <v>-29.326</v>
+        <v>-28.689</v>
       </c>
       <c r="F4">
-        <v>1.274</v>
+        <v>1.911</v>
       </c>
       <c r="G4">
         <v>0.08699999999999999</v>
@@ -1603,28 +1603,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M4">
-        <v>0.06408219999999999</v>
+        <v>0.09612329999999999</v>
       </c>
       <c r="N4">
-        <v>9.71480668888889</v>
+        <v>9.682765588888889</v>
       </c>
       <c r="O4">
-        <v>2.137257471555556</v>
+        <v>2.130208429555556</v>
       </c>
       <c r="P4">
-        <v>7.577549217333335</v>
+        <v>7.552557159333334</v>
       </c>
       <c r="Q4">
-        <v>16.68754921733333</v>
+        <v>16.66255715933333</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1161715880502516</v>
+        <v>0.116739963527912</v>
       </c>
       <c r="T4">
-        <v>0.9686913977281033</v>
+        <v>0.976515300117461</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>152.5991443628479</v>
+        <v>101.7327629085652</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1144147846220747</v>
+        <v>0.1141967329549027</v>
       </c>
       <c r="C5">
-        <v>61.98286963184168</v>
+        <v>61.5492886213045</v>
       </c>
       <c r="D5">
-        <v>63.80686963184168</v>
+        <v>64.0102886213045</v>
       </c>
       <c r="E5">
-        <v>-28.689</v>
+        <v>-28.052</v>
       </c>
       <c r="F5">
-        <v>1.911</v>
+        <v>2.548</v>
       </c>
       <c r="G5">
         <v>0.08699999999999999</v>
@@ -1685,28 +1685,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M5">
-        <v>0.09612329999999999</v>
+        <v>0.1281644</v>
       </c>
       <c r="N5">
-        <v>9.682765588888889</v>
+        <v>9.650724488888891</v>
       </c>
       <c r="O5">
-        <v>2.130208429555556</v>
+        <v>2.123159387555556</v>
       </c>
       <c r="P5">
-        <v>7.552557159333334</v>
+        <v>7.527565101333335</v>
       </c>
       <c r="Q5">
-        <v>16.66255715933333</v>
+        <v>16.63756510133333</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.116739963527912</v>
+        <v>0.117320180161357</v>
       </c>
       <c r="T5">
-        <v>0.976515300117461</v>
+        <v>0.9845022004732636</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>101.7327629085652</v>
+        <v>76.29957218142395</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1141967329549027</v>
+        <v>0.1139786812877309</v>
       </c>
       <c r="C6">
-        <v>61.5492886213045</v>
+        <v>61.11700877555805</v>
       </c>
       <c r="D6">
-        <v>64.0102886213045</v>
+        <v>64.21500877555805</v>
       </c>
       <c r="E6">
-        <v>-28.052</v>
+        <v>-27.415</v>
       </c>
       <c r="F6">
-        <v>2.548</v>
+        <v>3.185</v>
       </c>
       <c r="G6">
         <v>0.08699999999999999</v>
@@ -1767,28 +1767,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M6">
-        <v>0.1281644</v>
+        <v>0.1602055</v>
       </c>
       <c r="N6">
-        <v>9.650724488888891</v>
+        <v>9.61868338888889</v>
       </c>
       <c r="O6">
-        <v>2.123159387555556</v>
+        <v>2.116110345555556</v>
       </c>
       <c r="P6">
-        <v>7.527565101333335</v>
+        <v>7.502573043333334</v>
       </c>
       <c r="Q6">
-        <v>16.63756510133333</v>
+        <v>16.61257304333333</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.117320180161357</v>
+        <v>0.117912611881822</v>
       </c>
       <c r="T6">
-        <v>0.9845022004732636</v>
+        <v>0.992657246099715</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>76.29957218142395</v>
+        <v>61.03965774513914</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1139786812877309</v>
+        <v>0.113760629620559</v>
       </c>
       <c r="C7">
-        <v>61.11700877555805</v>
+        <v>60.68604261896337</v>
       </c>
       <c r="D7">
-        <v>64.21500877555805</v>
+        <v>64.42104261896337</v>
       </c>
       <c r="E7">
-        <v>-27.415</v>
+        <v>-26.778</v>
       </c>
       <c r="F7">
-        <v>3.185</v>
+        <v>3.822000000000001</v>
       </c>
       <c r="G7">
         <v>0.08699999999999999</v>
@@ -1849,28 +1849,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M7">
-        <v>0.1602055</v>
+        <v>0.1922466</v>
       </c>
       <c r="N7">
-        <v>9.61868338888889</v>
+        <v>9.586642288888889</v>
       </c>
       <c r="O7">
-        <v>2.116110345555556</v>
+        <v>2.109061303555555</v>
       </c>
       <c r="P7">
-        <v>7.502573043333334</v>
+        <v>7.477580985333334</v>
       </c>
       <c r="Q7">
-        <v>16.61257304333333</v>
+        <v>16.58758098533333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.117912611881822</v>
+        <v>0.1185176485325095</v>
       </c>
       <c r="T7">
-        <v>0.992657246099715</v>
+        <v>1.000985803335239</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>61.03965774513914</v>
+        <v>50.86638145428262</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.113760629620559</v>
+        <v>0.1135425779533871</v>
       </c>
       <c r="C8">
-        <v>60.68604261896337</v>
+        <v>60.25640283713638</v>
       </c>
       <c r="D8">
-        <v>64.42104261896337</v>
+        <v>64.62840283713638</v>
       </c>
       <c r="E8">
-        <v>-26.778</v>
+        <v>-26.141</v>
       </c>
       <c r="F8">
-        <v>3.822</v>
+        <v>4.459</v>
       </c>
       <c r="G8">
         <v>0.08699999999999999</v>
@@ -1931,28 +1931,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M8">
-        <v>0.1922466</v>
+        <v>0.2242877</v>
       </c>
       <c r="N8">
-        <v>9.586642288888889</v>
+        <v>9.55460118888889</v>
       </c>
       <c r="O8">
-        <v>2.109061303555555</v>
+        <v>2.102012261555556</v>
       </c>
       <c r="P8">
-        <v>7.477580985333334</v>
+        <v>7.452588927333334</v>
       </c>
       <c r="Q8">
-        <v>16.58758098533333</v>
+        <v>16.56258892733333</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1185176485325095</v>
+        <v>0.1191356967240721</v>
       </c>
       <c r="T8">
-        <v>1.000985803335239</v>
+        <v>1.009493469328517</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>50.86638145428262</v>
+        <v>43.59975553224226</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1135425779533871</v>
+        <v>0.1133245262862152</v>
       </c>
       <c r="C9">
-        <v>60.25640283713638</v>
+        <v>59.82810227955174</v>
       </c>
       <c r="D9">
-        <v>64.62840283713638</v>
+        <v>64.83710227955174</v>
       </c>
       <c r="E9">
-        <v>-26.141</v>
+        <v>-25.504</v>
       </c>
       <c r="F9">
-        <v>4.459000000000001</v>
+        <v>5.096</v>
       </c>
       <c r="G9">
         <v>0.08699999999999999</v>
@@ -2013,28 +2013,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M9">
-        <v>0.2242877</v>
+        <v>0.2563288</v>
       </c>
       <c r="N9">
-        <v>9.55460118888889</v>
+        <v>9.522560088888889</v>
       </c>
       <c r="O9">
-        <v>2.102012261555556</v>
+        <v>2.094963219555556</v>
       </c>
       <c r="P9">
-        <v>7.452588927333334</v>
+        <v>7.427596869333334</v>
       </c>
       <c r="Q9">
-        <v>16.56258892733333</v>
+        <v>16.53759686933333</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1191356967240721</v>
+        <v>0.119767180745886</v>
       </c>
       <c r="T9">
-        <v>1.009493469328517</v>
+        <v>1.018186084582518</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>43.59975553224225</v>
+        <v>38.14978609071197</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1133245262862152</v>
+        <v>0.1131064746190433</v>
       </c>
       <c r="C10">
-        <v>59.82810227955174</v>
+        <v>59.40115396219702</v>
       </c>
       <c r="D10">
-        <v>64.83710227955174</v>
+        <v>65.04715396219702</v>
       </c>
       <c r="E10">
-        <v>-25.504</v>
+        <v>-24.867</v>
       </c>
       <c r="F10">
-        <v>5.096</v>
+        <v>5.733</v>
       </c>
       <c r="G10">
         <v>0.08699999999999999</v>
@@ -2095,28 +2095,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M10">
-        <v>0.2563288</v>
+        <v>0.2883699</v>
       </c>
       <c r="N10">
-        <v>9.522560088888889</v>
+        <v>9.490518988888891</v>
       </c>
       <c r="O10">
-        <v>2.094963219555556</v>
+        <v>2.087914177555556</v>
       </c>
       <c r="P10">
-        <v>7.427596869333334</v>
+        <v>7.402604811333335</v>
       </c>
       <c r="Q10">
-        <v>16.53759686933333</v>
+        <v>16.51260481133333</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.119767180745886</v>
+        <v>0.1204125435374102</v>
       </c>
       <c r="T10">
-        <v>1.018186084582518</v>
+        <v>1.027069746325619</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>38.14978609071197</v>
+        <v>33.91092096952175</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1131064746190433</v>
+        <v>0.1128884229518714</v>
       </c>
       <c r="C11">
-        <v>59.40115396219702</v>
+        <v>58.97557107027868</v>
       </c>
       <c r="D11">
-        <v>65.04715396219702</v>
+        <v>65.25857107027868</v>
       </c>
       <c r="E11">
-        <v>-24.867</v>
+        <v>-24.23</v>
       </c>
       <c r="F11">
-        <v>5.733</v>
+        <v>6.37</v>
       </c>
       <c r="G11">
         <v>0.08699999999999999</v>
@@ -2177,28 +2177,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M11">
-        <v>0.2883699</v>
+        <v>0.320411</v>
       </c>
       <c r="N11">
-        <v>9.490518988888891</v>
+        <v>9.45847788888889</v>
       </c>
       <c r="O11">
-        <v>2.087914177555556</v>
+        <v>2.080865135555556</v>
       </c>
       <c r="P11">
-        <v>7.402604811333335</v>
+        <v>7.377612753333334</v>
       </c>
       <c r="Q11">
-        <v>16.51260481133333</v>
+        <v>16.48761275333333</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1204125435374102</v>
+        <v>0.1210722477243015</v>
       </c>
       <c r="T11">
-        <v>1.027069746325619</v>
+        <v>1.036150822774121</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>33.91092096952175</v>
+        <v>30.51982887256957</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1128884229518714</v>
+        <v>0.1126703712846995</v>
       </c>
       <c r="C12">
-        <v>58.97557107027868</v>
+        <v>58.55136696098109</v>
       </c>
       <c r="D12">
-        <v>65.25857107027868</v>
+        <v>65.47136696098109</v>
       </c>
       <c r="E12">
-        <v>-24.23</v>
+        <v>-23.593</v>
       </c>
       <c r="F12">
-        <v>6.370000000000001</v>
+        <v>7.007000000000001</v>
       </c>
       <c r="G12">
         <v>0.08699999999999999</v>
@@ -2259,28 +2259,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M12">
-        <v>0.3204110000000001</v>
+        <v>0.3524521</v>
       </c>
       <c r="N12">
-        <v>9.45847788888889</v>
+        <v>9.426436788888889</v>
       </c>
       <c r="O12">
-        <v>2.080865135555556</v>
+        <v>2.073816093555556</v>
       </c>
       <c r="P12">
-        <v>7.377612753333334</v>
+        <v>7.352620695333334</v>
       </c>
       <c r="Q12">
-        <v>16.48761275333333</v>
+        <v>16.46262069533334</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1210722477243015</v>
+        <v>0.1217467767243814</v>
       </c>
       <c r="T12">
-        <v>1.036150822774121</v>
+        <v>1.045435968356298</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>30.51982887256957</v>
+        <v>27.74529897506325</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1126703712846995</v>
+        <v>0.1124523196175276</v>
       </c>
       <c r="C13">
-        <v>58.55136696098109</v>
+        <v>58.12855516627969</v>
       </c>
       <c r="D13">
-        <v>65.47136696098109</v>
+        <v>65.68555516627968</v>
       </c>
       <c r="E13">
-        <v>-23.593</v>
+        <v>-22.956</v>
       </c>
       <c r="F13">
-        <v>7.007000000000001</v>
+        <v>7.644</v>
       </c>
       <c r="G13">
         <v>0.08699999999999999</v>
@@ -2341,28 +2341,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M13">
-        <v>0.3524521</v>
+        <v>0.3844932</v>
       </c>
       <c r="N13">
-        <v>9.426436788888889</v>
+        <v>9.39439568888889</v>
       </c>
       <c r="O13">
-        <v>2.073816093555556</v>
+        <v>2.066767051555556</v>
       </c>
       <c r="P13">
-        <v>7.352620695333334</v>
+        <v>7.327628637333334</v>
       </c>
       <c r="Q13">
-        <v>16.46262069533334</v>
+        <v>16.43762863733333</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1217467767243814</v>
+        <v>0.1224366359290086</v>
       </c>
       <c r="T13">
-        <v>1.045435968356298</v>
+        <v>1.054932139974433</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>27.74529897506325</v>
+        <v>25.43319072714132</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1124523196175276</v>
+        <v>0.1122342679503557</v>
       </c>
       <c r="C14">
-        <v>58.12855516627969</v>
+        <v>57.70714939580926</v>
       </c>
       <c r="D14">
-        <v>65.68555516627968</v>
+        <v>65.90114939580926</v>
       </c>
       <c r="E14">
-        <v>-22.956</v>
+        <v>-22.319</v>
       </c>
       <c r="F14">
-        <v>7.644</v>
+        <v>8.281000000000001</v>
       </c>
       <c r="G14">
         <v>0.08699999999999999</v>
@@ -2423,28 +2423,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M14">
-        <v>0.3844932</v>
+        <v>0.4165343</v>
       </c>
       <c r="N14">
-        <v>9.39439568888889</v>
+        <v>9.362354588888889</v>
       </c>
       <c r="O14">
-        <v>2.066767051555556</v>
+        <v>2.059718009555556</v>
       </c>
       <c r="P14">
-        <v>7.327628637333334</v>
+        <v>7.302636579333334</v>
       </c>
       <c r="Q14">
-        <v>16.43762863733333</v>
+        <v>16.41263657933333</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1224366359290086</v>
+        <v>0.1231423539659261</v>
       </c>
       <c r="T14">
-        <v>1.054932139974433</v>
+        <v>1.064646614388387</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>25.43319072714132</v>
+        <v>23.47679144043813</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1122342679503557</v>
+        <v>0.1120162162831838</v>
       </c>
       <c r="C15">
-        <v>57.70714939580926</v>
+        <v>57.28716353978945</v>
       </c>
       <c r="D15">
-        <v>65.90114939580926</v>
+        <v>66.11816353978945</v>
       </c>
       <c r="E15">
-        <v>-22.319</v>
+        <v>-21.682</v>
       </c>
       <c r="F15">
-        <v>8.281000000000001</v>
+        <v>8.918000000000001</v>
       </c>
       <c r="G15">
         <v>0.08699999999999999</v>
@@ -2505,28 +2505,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M15">
-        <v>0.4165343</v>
+        <v>0.4485754</v>
       </c>
       <c r="N15">
-        <v>9.362354588888889</v>
+        <v>9.330313488888891</v>
       </c>
       <c r="O15">
-        <v>2.059718009555556</v>
+        <v>2.052668967555556</v>
       </c>
       <c r="P15">
-        <v>7.302636579333334</v>
+        <v>7.277644521333334</v>
       </c>
       <c r="Q15">
-        <v>16.41263657933333</v>
+        <v>16.38764452133334</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1231423539659261</v>
+        <v>0.1238644840502137</v>
       </c>
       <c r="T15">
-        <v>1.064646614388387</v>
+        <v>1.074587006811968</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>23.47679144043813</v>
+        <v>21.79987776612112</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1120162162831838</v>
+        <v>0.1117981646160119</v>
       </c>
       <c r="C16">
-        <v>57.28716353978945</v>
+        <v>56.86861167200762</v>
       </c>
       <c r="D16">
-        <v>66.11816353978945</v>
+        <v>66.33661167200762</v>
       </c>
       <c r="E16">
-        <v>-21.682</v>
+        <v>-21.045</v>
       </c>
       <c r="F16">
-        <v>8.918000000000001</v>
+        <v>9.555000000000001</v>
       </c>
       <c r="G16">
         <v>0.08699999999999999</v>
@@ -2587,28 +2587,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M16">
-        <v>0.4485754</v>
+        <v>0.4806165000000001</v>
       </c>
       <c r="N16">
-        <v>9.330313488888891</v>
+        <v>9.29827238888889</v>
       </c>
       <c r="O16">
-        <v>2.052668967555556</v>
+        <v>2.045619925555556</v>
       </c>
       <c r="P16">
-        <v>7.277644521333334</v>
+        <v>7.252652463333334</v>
       </c>
       <c r="Q16">
-        <v>16.38764452133334</v>
+        <v>16.36265246333333</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1238644840502137</v>
+        <v>0.1246036054306022</v>
       </c>
       <c r="T16">
-        <v>1.074587006811968</v>
+        <v>1.084761290821987</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>21.79987776612112</v>
+        <v>20.34655258171305</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1117981646160119</v>
+        <v>0.11158011294884</v>
       </c>
       <c r="C17">
-        <v>56.86861167200762</v>
+        <v>56.45150805286161</v>
       </c>
       <c r="D17">
-        <v>66.33661167200762</v>
+        <v>66.5565080528616</v>
       </c>
       <c r="E17">
-        <v>-21.045</v>
+        <v>-20.408</v>
       </c>
       <c r="F17">
-        <v>9.555</v>
+        <v>10.192</v>
       </c>
       <c r="G17">
         <v>0.08699999999999999</v>
@@ -2669,28 +2669,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M17">
-        <v>0.4806164999999999</v>
+        <v>0.5126575999999999</v>
       </c>
       <c r="N17">
-        <v>9.29827238888889</v>
+        <v>9.266231288888889</v>
       </c>
       <c r="O17">
-        <v>2.045619925555556</v>
+        <v>2.038570883555556</v>
       </c>
       <c r="P17">
-        <v>7.252652463333334</v>
+        <v>7.227660405333333</v>
       </c>
       <c r="Q17">
-        <v>16.36265246333333</v>
+        <v>16.33766040533333</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1246036054306022</v>
+        <v>0.1253603249390952</v>
       </c>
       <c r="T17">
-        <v>1.084761290821987</v>
+        <v>1.095177819689386</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>20.34655258171305</v>
+        <v>19.07489304535599</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.11158011294884</v>
+        <v>0.1113620612816681</v>
       </c>
       <c r="C18">
-        <v>56.45150805286161</v>
+        <v>56.03586713246278</v>
       </c>
       <c r="D18">
-        <v>66.5565080528616</v>
+        <v>66.77786713246277</v>
       </c>
       <c r="E18">
-        <v>-20.408</v>
+        <v>-19.771</v>
       </c>
       <c r="F18">
-        <v>10.192</v>
+        <v>10.829</v>
       </c>
       <c r="G18">
         <v>0.08699999999999999</v>
@@ -2751,28 +2751,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M18">
-        <v>0.5126575999999999</v>
+        <v>0.5446987</v>
       </c>
       <c r="N18">
-        <v>9.266231288888889</v>
+        <v>9.23419018888889</v>
       </c>
       <c r="O18">
-        <v>2.038570883555556</v>
+        <v>2.031521841555556</v>
       </c>
       <c r="P18">
-        <v>7.227660405333333</v>
+        <v>7.202668347333335</v>
       </c>
       <c r="Q18">
-        <v>16.33766040533333</v>
+        <v>16.31266834733334</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1253603249390952</v>
+        <v>0.1261352786526121</v>
       </c>
       <c r="T18">
-        <v>1.095177819689386</v>
+        <v>1.105845349252386</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>19.07489304535599</v>
+        <v>17.95284051327622</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1113620612816681</v>
+        <v>0.1111440096144962</v>
       </c>
       <c r="C19">
-        <v>56.03586713246278</v>
+        <v>55.62170355380149</v>
       </c>
       <c r="D19">
-        <v>66.77786713246277</v>
+        <v>67.00070355380149</v>
       </c>
       <c r="E19">
-        <v>-19.771</v>
+        <v>-19.134</v>
       </c>
       <c r="F19">
-        <v>10.829</v>
+        <v>11.466</v>
       </c>
       <c r="G19">
         <v>0.08699999999999999</v>
@@ -2833,28 +2833,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M19">
-        <v>0.5446987</v>
+        <v>0.5767398</v>
       </c>
       <c r="N19">
-        <v>9.23419018888889</v>
+        <v>9.202149088888889</v>
       </c>
       <c r="O19">
-        <v>2.031521841555556</v>
+        <v>2.024472799555556</v>
       </c>
       <c r="P19">
-        <v>7.202668347333335</v>
+        <v>7.177676289333334</v>
       </c>
       <c r="Q19">
-        <v>16.31266834733334</v>
+        <v>16.28767628933333</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1261352786526121</v>
+        <v>0.1269291336762149</v>
       </c>
       <c r="T19">
-        <v>1.105845349252386</v>
+        <v>1.116773062463264</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>17.95284051327622</v>
+        <v>16.95546048476087</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1111440096144962</v>
+        <v>0.1109259579473243</v>
       </c>
       <c r="C20">
-        <v>55.62170355380147</v>
+        <v>55.20903215597597</v>
       </c>
       <c r="D20">
-        <v>67.00070355380147</v>
+        <v>67.22503215597597</v>
       </c>
       <c r="E20">
-        <v>-19.134</v>
+        <v>-18.497</v>
       </c>
       <c r="F20">
-        <v>11.466</v>
+        <v>12.103</v>
       </c>
       <c r="G20">
         <v>0.08699999999999999</v>
@@ -2915,28 +2915,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M20">
-        <v>0.5767397999999999</v>
+        <v>0.6087809000000001</v>
       </c>
       <c r="N20">
-        <v>9.202149088888889</v>
+        <v>9.170107988888891</v>
       </c>
       <c r="O20">
-        <v>2.024472799555556</v>
+        <v>2.017423757555556</v>
       </c>
       <c r="P20">
-        <v>7.177676289333334</v>
+        <v>7.152684231333335</v>
       </c>
       <c r="Q20">
-        <v>16.28767628933333</v>
+        <v>16.26268423133333</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1269291336762149</v>
+        <v>0.127742590058425</v>
       </c>
       <c r="T20">
-        <v>1.116773062463264</v>
+        <v>1.127970595753423</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>16.95546048476088</v>
+        <v>16.0630678276682</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1109259579473243</v>
+        <v>0.1107079062801524</v>
       </c>
       <c r="C21">
-        <v>55.20903215597597</v>
+        <v>54.79786797748631</v>
       </c>
       <c r="D21">
-        <v>67.22503215597597</v>
+        <v>67.45086797748631</v>
       </c>
       <c r="E21">
-        <v>-18.497</v>
+        <v>-17.86</v>
       </c>
       <c r="F21">
-        <v>12.103</v>
+        <v>12.74</v>
       </c>
       <c r="G21">
         <v>0.08699999999999999</v>
@@ -2997,28 +2997,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M21">
-        <v>0.6087809000000001</v>
+        <v>0.6408220000000001</v>
       </c>
       <c r="N21">
-        <v>9.170107988888891</v>
+        <v>9.13806688888889</v>
       </c>
       <c r="O21">
-        <v>2.017423757555556</v>
+        <v>2.010374715555556</v>
       </c>
       <c r="P21">
-        <v>7.152684231333335</v>
+        <v>7.127692173333334</v>
       </c>
       <c r="Q21">
-        <v>16.26268423133333</v>
+        <v>16.23769217333333</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.127742590058425</v>
+        <v>0.1285763828501905</v>
       </c>
       <c r="T21">
-        <v>1.127970595753423</v>
+        <v>1.139448067375836</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>16.0630678276682</v>
+        <v>15.25991443628478</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1107079062801524</v>
+        <v>0.1104898546129805</v>
       </c>
       <c r="C22">
-        <v>54.79786797748631</v>
+        <v>54.38822625959522</v>
       </c>
       <c r="D22">
-        <v>67.45086797748631</v>
+        <v>67.67822625959522</v>
       </c>
       <c r="E22">
-        <v>-17.86</v>
+        <v>-17.223</v>
       </c>
       <c r="F22">
-        <v>12.74</v>
+        <v>13.377</v>
       </c>
       <c r="G22">
         <v>0.08699999999999999</v>
@@ -3079,28 +3079,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M22">
-        <v>0.6408220000000001</v>
+        <v>0.6728631</v>
       </c>
       <c r="N22">
-        <v>9.13806688888889</v>
+        <v>9.106025788888889</v>
       </c>
       <c r="O22">
-        <v>2.010374715555556</v>
+        <v>2.003325673555556</v>
       </c>
       <c r="P22">
-        <v>7.127692173333334</v>
+        <v>7.102700115333334</v>
       </c>
       <c r="Q22">
-        <v>16.23769217333333</v>
+        <v>16.21270011533333</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1285763828501905</v>
+        <v>0.1294312843202285</v>
       </c>
       <c r="T22">
-        <v>1.139448067375836</v>
+        <v>1.151216107900082</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>15.25991443628478</v>
+        <v>14.53325184408075</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1104898546129805</v>
+        <v>0.1102718029458086</v>
       </c>
       <c r="C23">
-        <v>54.38822625959522</v>
+        <v>53.98012244975677</v>
       </c>
       <c r="D23">
-        <v>67.67822625959522</v>
+        <v>67.90712244975677</v>
       </c>
       <c r="E23">
-        <v>-17.223</v>
+        <v>-16.586</v>
       </c>
       <c r="F23">
-        <v>13.377</v>
+        <v>14.014</v>
       </c>
       <c r="G23">
         <v>0.08699999999999999</v>
@@ -3161,28 +3161,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M23">
-        <v>0.6728631</v>
+        <v>0.7049042</v>
       </c>
       <c r="N23">
-        <v>9.106025788888889</v>
+        <v>9.07398468888889</v>
       </c>
       <c r="O23">
-        <v>2.003325673555556</v>
+        <v>1.996276631555556</v>
       </c>
       <c r="P23">
-        <v>7.102700115333334</v>
+        <v>7.077708057333334</v>
       </c>
       <c r="Q23">
-        <v>16.21270011533333</v>
+        <v>16.18770805733333</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1294312843202285</v>
+        <v>0.1303081063407802</v>
       </c>
       <c r="T23">
-        <v>1.151216107900081</v>
+        <v>1.163285893053154</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>14.53325184408075</v>
+        <v>13.87264948753162</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1102718029458086</v>
+        <v>0.1100537512786367</v>
       </c>
       <c r="C24">
-        <v>53.98012244975677</v>
+        <v>53.57357220511509</v>
       </c>
       <c r="D24">
-        <v>67.90712244975677</v>
+        <v>68.13757220511509</v>
       </c>
       <c r="E24">
-        <v>-16.586</v>
+        <v>-15.949</v>
       </c>
       <c r="F24">
-        <v>14.014</v>
+        <v>14.651</v>
       </c>
       <c r="G24">
         <v>0.08699999999999999</v>
@@ -3243,28 +3243,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M24">
-        <v>0.7049042</v>
+        <v>0.7369453</v>
       </c>
       <c r="N24">
-        <v>9.07398468888889</v>
+        <v>9.041943588888889</v>
       </c>
       <c r="O24">
-        <v>1.996276631555556</v>
+        <v>1.989227589555556</v>
       </c>
       <c r="P24">
-        <v>7.077708057333334</v>
+        <v>7.052715999333333</v>
       </c>
       <c r="Q24">
-        <v>16.18770805733333</v>
+        <v>16.16271599933333</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1303081063407802</v>
+        <v>0.1312077029592684</v>
       </c>
       <c r="T24">
-        <v>1.163285893053154</v>
+        <v>1.175669179119294</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>13.87264948753162</v>
+        <v>13.26949081416068</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1100537512786367</v>
+        <v>0.1101164996114648</v>
       </c>
       <c r="C25">
-        <v>53.57357220511509</v>
+        <v>52.8700959651976</v>
       </c>
       <c r="D25">
-        <v>68.13757220511509</v>
+        <v>68.0710959651976</v>
       </c>
       <c r="E25">
-        <v>-15.949</v>
+        <v>-15.312</v>
       </c>
       <c r="F25">
-        <v>14.651</v>
+        <v>15.288</v>
       </c>
       <c r="G25">
         <v>0.08699999999999999</v>
@@ -3325,45 +3325,45 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M25">
-        <v>0.7369453</v>
+        <v>0.7919184000000001</v>
       </c>
       <c r="N25">
-        <v>9.041943588888889</v>
+        <v>8.98697048888889</v>
       </c>
       <c r="O25">
-        <v>1.989227589555556</v>
+        <v>1.977133507555556</v>
       </c>
       <c r="P25">
-        <v>7.052715999333333</v>
+        <v>7.009836981333334</v>
       </c>
       <c r="Q25">
-        <v>16.16271599933333</v>
+        <v>16.11983698133333</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1312077029592684</v>
+        <v>0.13213097317298</v>
       </c>
       <c r="T25">
-        <v>1.175669179119294</v>
+        <v>1.188378341134542</v>
       </c>
       <c r="U25">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V25">
         <v>0.22</v>
       </c>
       <c r="W25">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y25">
-        <v>13.26949081416068</v>
+        <v>12.34835418508888</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1101164996114648</v>
+        <v>0.1099101479442929</v>
       </c>
       <c r="C26">
-        <v>52.87009596519761</v>
+        <v>52.45219675639908</v>
       </c>
       <c r="D26">
-        <v>68.0710959651976</v>
+        <v>68.29019675639907</v>
       </c>
       <c r="E26">
-        <v>-15.312</v>
+        <v>-14.675</v>
       </c>
       <c r="F26">
-        <v>15.288</v>
+        <v>15.925</v>
       </c>
       <c r="G26">
         <v>0.08699999999999999</v>
@@ -3407,28 +3407,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M26">
-        <v>0.7919184</v>
+        <v>0.8249150000000001</v>
       </c>
       <c r="N26">
-        <v>8.98697048888889</v>
+        <v>8.953973888888889</v>
       </c>
       <c r="O26">
-        <v>1.977133507555556</v>
+        <v>1.969874255555556</v>
       </c>
       <c r="P26">
-        <v>7.009836981333334</v>
+        <v>6.984099633333334</v>
       </c>
       <c r="Q26">
-        <v>16.11983698133333</v>
+        <v>16.09409963333333</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.13213097317298</v>
+        <v>0.1330788639257239</v>
       </c>
       <c r="T26">
-        <v>1.188378341134542</v>
+        <v>1.201426414136864</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>12.34835418508888</v>
+        <v>11.85442001768532</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1099101479442929</v>
+        <v>0.109703796277121</v>
       </c>
       <c r="C27">
-        <v>52.45219675639908</v>
+        <v>52.03571254377214</v>
       </c>
       <c r="D27">
-        <v>68.29019675639907</v>
+        <v>68.51071254377213</v>
       </c>
       <c r="E27">
-        <v>-14.675</v>
+        <v>-14.038</v>
       </c>
       <c r="F27">
-        <v>15.925</v>
+        <v>16.562</v>
       </c>
       <c r="G27">
         <v>0.08699999999999999</v>
@@ -3489,28 +3489,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M27">
-        <v>0.8249150000000001</v>
+        <v>0.8579116</v>
       </c>
       <c r="N27">
-        <v>8.953973888888889</v>
+        <v>8.92097728888889</v>
       </c>
       <c r="O27">
-        <v>1.969874255555556</v>
+        <v>1.962615003555556</v>
       </c>
       <c r="P27">
-        <v>6.984099633333334</v>
+        <v>6.958362285333335</v>
       </c>
       <c r="Q27">
-        <v>16.09409963333333</v>
+        <v>16.06836228533334</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1330788639257239</v>
+        <v>0.1340523733474608</v>
       </c>
       <c r="T27">
-        <v>1.201426414136864</v>
+        <v>1.21482713776087</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.85442001768532</v>
+        <v>11.39848078623589</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.109703796277121</v>
+        <v>0.1094974446099491</v>
       </c>
       <c r="C28">
-        <v>52.03571254377214</v>
+        <v>51.62065707921015</v>
       </c>
       <c r="D28">
-        <v>68.51071254377213</v>
+        <v>68.73265707921014</v>
       </c>
       <c r="E28">
-        <v>-14.038</v>
+        <v>-13.401</v>
       </c>
       <c r="F28">
-        <v>16.562</v>
+        <v>17.199</v>
       </c>
       <c r="G28">
         <v>0.08699999999999999</v>
@@ -3571,28 +3571,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M28">
-        <v>0.8579116</v>
+        <v>0.8909082</v>
       </c>
       <c r="N28">
-        <v>8.92097728888889</v>
+        <v>8.88798068888889</v>
       </c>
       <c r="O28">
-        <v>1.962615003555556</v>
+        <v>1.955355751555556</v>
       </c>
       <c r="P28">
-        <v>6.958362285333335</v>
+        <v>6.932624937333334</v>
       </c>
       <c r="Q28">
-        <v>16.06836228533334</v>
+        <v>16.04262493733333</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1340523733474608</v>
+        <v>0.1350525542602042</v>
       </c>
       <c r="T28">
-        <v>1.21482713776087</v>
+        <v>1.228595004497863</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.39848078623589</v>
+        <v>10.97631483119011</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1094974446099491</v>
+        <v>0.1092910929427772</v>
       </c>
       <c r="C29">
-        <v>51.62065707921015</v>
+        <v>51.20704429338572</v>
       </c>
       <c r="D29">
-        <v>68.73265707921014</v>
+        <v>68.95604429338572</v>
       </c>
       <c r="E29">
-        <v>-13.401</v>
+        <v>-12.764</v>
       </c>
       <c r="F29">
-        <v>17.199</v>
+        <v>17.836</v>
       </c>
       <c r="G29">
         <v>0.08699999999999999</v>
@@ -3653,28 +3653,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M29">
-        <v>0.8909082</v>
+        <v>0.9239048000000001</v>
       </c>
       <c r="N29">
-        <v>8.88798068888889</v>
+        <v>8.854984088888889</v>
       </c>
       <c r="O29">
-        <v>1.955355751555556</v>
+        <v>1.948096499555556</v>
       </c>
       <c r="P29">
-        <v>6.932624937333334</v>
+        <v>6.906887589333333</v>
       </c>
       <c r="Q29">
-        <v>16.04262493733333</v>
+        <v>16.01688758933333</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1350525542602042</v>
+        <v>0.1360805179760795</v>
       </c>
       <c r="T29">
-        <v>1.228595004497863</v>
+        <v>1.24274531197755</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.97631483119011</v>
+        <v>10.58430358721904</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1092910929427772</v>
+        <v>0.1090847412756053</v>
       </c>
       <c r="C30">
-        <v>51.20704429338572</v>
+        <v>50.79488829866577</v>
       </c>
       <c r="D30">
-        <v>68.95604429338572</v>
+        <v>69.18088829866576</v>
       </c>
       <c r="E30">
-        <v>-12.764</v>
+        <v>-12.127</v>
       </c>
       <c r="F30">
-        <v>17.836</v>
+        <v>18.473</v>
       </c>
       <c r="G30">
         <v>0.08699999999999999</v>
@@ -3735,28 +3735,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M30">
-        <v>0.9239048000000001</v>
+        <v>0.9569014000000001</v>
       </c>
       <c r="N30">
-        <v>8.854984088888889</v>
+        <v>8.82198748888889</v>
       </c>
       <c r="O30">
-        <v>1.948096499555556</v>
+        <v>1.940837247555556</v>
       </c>
       <c r="P30">
-        <v>6.906887589333333</v>
+        <v>6.881150241333335</v>
       </c>
       <c r="Q30">
-        <v>16.01688758933333</v>
+        <v>15.99115024133333</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1360805179760795</v>
+        <v>0.1371374384163455</v>
       </c>
       <c r="T30">
-        <v>1.24274531197755</v>
+        <v>1.257294219667932</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.58430358721904</v>
+        <v>10.21932760145287</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1090847412756053</v>
+        <v>0.1088783896084334</v>
       </c>
       <c r="C31">
-        <v>50.79488829866577</v>
+        <v>50.38420339208338</v>
       </c>
       <c r="D31">
-        <v>69.18088829866576</v>
+        <v>69.40720339208337</v>
       </c>
       <c r="E31">
-        <v>-12.127</v>
+        <v>-11.49</v>
       </c>
       <c r="F31">
-        <v>18.473</v>
+        <v>19.11</v>
       </c>
       <c r="G31">
         <v>0.08699999999999999</v>
@@ -3817,28 +3817,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M31">
-        <v>0.9569013999999999</v>
+        <v>0.9898979999999999</v>
       </c>
       <c r="N31">
-        <v>8.82198748888889</v>
+        <v>8.78899088888889</v>
       </c>
       <c r="O31">
-        <v>1.940837247555556</v>
+        <v>1.933577995555556</v>
       </c>
       <c r="P31">
-        <v>6.881150241333335</v>
+        <v>6.855412893333334</v>
       </c>
       <c r="Q31">
-        <v>15.99115024133333</v>
+        <v>15.96541289333333</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1371374384163455</v>
+        <v>0.1382245565834763</v>
       </c>
       <c r="T31">
-        <v>1.257294219667932</v>
+        <v>1.272258810435183</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.21932760145287</v>
+        <v>9.878683348071105</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1088783896084334</v>
+        <v>0.1090830979412615</v>
       </c>
       <c r="C32">
-        <v>50.38420339208338</v>
+        <v>49.522684786723</v>
       </c>
       <c r="D32">
-        <v>69.40720339208337</v>
+        <v>69.182684786723</v>
       </c>
       <c r="E32">
-        <v>-11.49</v>
+        <v>-10.853</v>
       </c>
       <c r="F32">
-        <v>19.11</v>
+        <v>19.747</v>
       </c>
       <c r="G32">
         <v>0.08699999999999999</v>
@@ -3899,45 +3899,45 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M32">
-        <v>0.9898979999999999</v>
+        <v>1.0564645</v>
       </c>
       <c r="N32">
-        <v>8.78899088888889</v>
+        <v>8.722424388888889</v>
       </c>
       <c r="O32">
-        <v>1.933577995555556</v>
+        <v>1.918933365555556</v>
       </c>
       <c r="P32">
-        <v>6.855412893333334</v>
+        <v>6.803491023333334</v>
       </c>
       <c r="Q32">
-        <v>15.96541289333333</v>
+        <v>15.91349102333333</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1382245565834763</v>
+        <v>0.1393431854221181</v>
       </c>
       <c r="T32">
-        <v>1.272258810435183</v>
+        <v>1.287657157456556</v>
       </c>
       <c r="U32">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V32">
         <v>0.22</v>
       </c>
       <c r="W32">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>9.878683348071105</v>
+        <v>9.256239929395536</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1090830979412615</v>
+        <v>0.1088900062740896</v>
       </c>
       <c r="C33">
-        <v>49.522684786723</v>
+        <v>49.09742355065433</v>
       </c>
       <c r="D33">
-        <v>69.182684786723</v>
+        <v>69.39442355065432</v>
       </c>
       <c r="E33">
-        <v>-10.853</v>
+        <v>-10.216</v>
       </c>
       <c r="F33">
-        <v>19.747</v>
+        <v>20.384</v>
       </c>
       <c r="G33">
         <v>0.08699999999999999</v>
@@ -3981,28 +3981,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M33">
-        <v>1.0564645</v>
+        <v>1.090544</v>
       </c>
       <c r="N33">
-        <v>8.722424388888889</v>
+        <v>8.68834488888889</v>
       </c>
       <c r="O33">
-        <v>1.918933365555556</v>
+        <v>1.911435875555556</v>
       </c>
       <c r="P33">
-        <v>6.803491023333334</v>
+        <v>6.776909013333334</v>
       </c>
       <c r="Q33">
-        <v>15.91349102333333</v>
+        <v>15.88690901333333</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1393431854221181</v>
+        <v>0.1404947151089553</v>
       </c>
       <c r="T33">
-        <v>1.287657157456556</v>
+        <v>1.303508397037382</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>9.256239929395536</v>
+        <v>8.966982431601926</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1088900062740896</v>
+        <v>0.1086969146069177</v>
       </c>
       <c r="C34">
-        <v>49.09742355065433</v>
+        <v>48.67346237806856</v>
       </c>
       <c r="D34">
-        <v>69.39442355065432</v>
+        <v>69.60746237806856</v>
       </c>
       <c r="E34">
-        <v>-10.216</v>
+        <v>-9.579000000000001</v>
       </c>
       <c r="F34">
-        <v>20.384</v>
+        <v>21.021</v>
       </c>
       <c r="G34">
         <v>0.08699999999999999</v>
@@ -4063,28 +4063,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M34">
-        <v>1.090544</v>
+        <v>1.1246235</v>
       </c>
       <c r="N34">
-        <v>8.68834488888889</v>
+        <v>8.65426538888889</v>
       </c>
       <c r="O34">
-        <v>1.911435875555556</v>
+        <v>1.903938385555556</v>
       </c>
       <c r="P34">
-        <v>6.776909013333334</v>
+        <v>6.750327003333334</v>
       </c>
       <c r="Q34">
-        <v>15.88690901333333</v>
+        <v>15.86032700333333</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1404947151089553</v>
+        <v>0.1416806188162951</v>
       </c>
       <c r="T34">
-        <v>1.303508397037382</v>
+        <v>1.319832807948979</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.966982431601926</v>
+        <v>8.695255691250352</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1086969146069177</v>
+        <v>0.1085038229397458</v>
       </c>
       <c r="C35">
-        <v>48.67346237806856</v>
+        <v>48.2508132793063</v>
       </c>
       <c r="D35">
-        <v>69.60746237806856</v>
+        <v>69.8218132793063</v>
       </c>
       <c r="E35">
-        <v>-9.579000000000001</v>
+        <v>-8.942</v>
       </c>
       <c r="F35">
-        <v>21.021</v>
+        <v>21.658</v>
       </c>
       <c r="G35">
         <v>0.08699999999999999</v>
@@ -4145,28 +4145,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M35">
-        <v>1.1246235</v>
+        <v>1.158703</v>
       </c>
       <c r="N35">
-        <v>8.65426538888889</v>
+        <v>8.620185888888891</v>
       </c>
       <c r="O35">
-        <v>1.903938385555556</v>
+        <v>1.896440895555556</v>
       </c>
       <c r="P35">
-        <v>6.750327003333334</v>
+        <v>6.723744993333335</v>
       </c>
       <c r="Q35">
-        <v>15.86032700333333</v>
+        <v>15.83374499333333</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1416806188162951</v>
+        <v>0.1429024589996148</v>
       </c>
       <c r="T35">
-        <v>1.319832807948979</v>
+        <v>1.336651897979109</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.695255691250352</v>
+        <v>8.439512876801812</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1085038229397458</v>
+        <v>0.1083107312725739</v>
       </c>
       <c r="C36">
-        <v>48.2508132793063</v>
+        <v>47.82948841310498</v>
       </c>
       <c r="D36">
-        <v>69.8218132793063</v>
+        <v>70.03748841310498</v>
       </c>
       <c r="E36">
-        <v>-8.942</v>
+        <v>-8.305</v>
       </c>
       <c r="F36">
-        <v>21.658</v>
+        <v>22.295</v>
       </c>
       <c r="G36">
         <v>0.08699999999999999</v>
@@ -4227,28 +4227,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M36">
-        <v>1.158703</v>
+        <v>1.1927825</v>
       </c>
       <c r="N36">
-        <v>8.620185888888891</v>
+        <v>8.58610638888889</v>
       </c>
       <c r="O36">
-        <v>1.896440895555556</v>
+        <v>1.888943405555556</v>
       </c>
       <c r="P36">
-        <v>6.723744993333335</v>
+        <v>6.697162983333334</v>
       </c>
       <c r="Q36">
-        <v>15.83374499333333</v>
+        <v>15.80716298333333</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1429024589996148</v>
+        <v>0.1441618942654983</v>
       </c>
       <c r="T36">
-        <v>1.336651897979109</v>
+        <v>1.353988498471704</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.439512876801812</v>
+        <v>8.198383937464616</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1083107312725739</v>
+        <v>0.108117639605402</v>
       </c>
       <c r="C37">
-        <v>47.82948841310498</v>
+        <v>47.40950008889777</v>
       </c>
       <c r="D37">
-        <v>70.03748841310498</v>
+        <v>70.25450008889777</v>
       </c>
       <c r="E37">
-        <v>-8.305</v>
+        <v>-7.667999999999999</v>
       </c>
       <c r="F37">
-        <v>22.295</v>
+        <v>22.932</v>
       </c>
       <c r="G37">
         <v>0.08699999999999999</v>
@@ -4309,28 +4309,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M37">
-        <v>1.1927825</v>
+        <v>1.226862</v>
       </c>
       <c r="N37">
-        <v>8.58610638888889</v>
+        <v>8.552026888888889</v>
       </c>
       <c r="O37">
-        <v>1.888943405555556</v>
+        <v>1.881445915555556</v>
       </c>
       <c r="P37">
-        <v>6.697162983333334</v>
+        <v>6.670580973333333</v>
       </c>
       <c r="Q37">
-        <v>15.80716298333333</v>
+        <v>15.78058097333333</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1441618942654983</v>
+        <v>0.1454606868834406</v>
       </c>
       <c r="T37">
-        <v>1.353988498471704</v>
+        <v>1.371866867729693</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.198383937464616</v>
+        <v>7.970651050312822</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.108117639605402</v>
+        <v>0.1079245479382301</v>
       </c>
       <c r="C38">
-        <v>47.40950008889776</v>
+        <v>46.99086076915545</v>
       </c>
       <c r="D38">
-        <v>70.25450008889776</v>
+        <v>70.47286076915545</v>
       </c>
       <c r="E38">
-        <v>-7.668000000000003</v>
+        <v>-7.031000000000002</v>
       </c>
       <c r="F38">
-        <v>22.932</v>
+        <v>23.569</v>
       </c>
       <c r="G38">
         <v>0.08699999999999999</v>
@@ -4391,28 +4391,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M38">
-        <v>1.226862</v>
+        <v>1.2609415</v>
       </c>
       <c r="N38">
-        <v>8.552026888888889</v>
+        <v>8.51794738888889</v>
       </c>
       <c r="O38">
-        <v>1.881445915555556</v>
+        <v>1.873948425555556</v>
       </c>
       <c r="P38">
-        <v>6.670580973333333</v>
+        <v>6.643998963333335</v>
       </c>
       <c r="Q38">
-        <v>15.78058097333333</v>
+        <v>15.75399896333333</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1454606868834406</v>
+        <v>0.1468007110130637</v>
       </c>
       <c r="T38">
-        <v>1.371866867729693</v>
+        <v>1.390312804265714</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.970651050312823</v>
+        <v>7.755228048953017</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1079245479382301</v>
+        <v>0.1079685762710582</v>
       </c>
       <c r="C39">
-        <v>46.99086076915545</v>
+        <v>46.30395126896414</v>
       </c>
       <c r="D39">
-        <v>70.47286076915545</v>
+        <v>70.42295126896414</v>
       </c>
       <c r="E39">
-        <v>-7.031000000000002</v>
+        <v>-6.393999999999998</v>
       </c>
       <c r="F39">
-        <v>23.569</v>
+        <v>24.206</v>
       </c>
       <c r="G39">
         <v>0.08699999999999999</v>
@@ -4473,45 +4473,45 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M39">
-        <v>1.2609415</v>
+        <v>1.3143858</v>
       </c>
       <c r="N39">
-        <v>8.51794738888889</v>
+        <v>8.46450308888889</v>
       </c>
       <c r="O39">
-        <v>1.873948425555556</v>
+        <v>1.862190679555556</v>
       </c>
       <c r="P39">
-        <v>6.643998963333335</v>
+        <v>6.602312409333334</v>
       </c>
       <c r="Q39">
-        <v>15.75399896333333</v>
+        <v>15.71231240933333</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1468007110130637</v>
+        <v>0.1481839617275132</v>
       </c>
       <c r="T39">
-        <v>1.390312804265714</v>
+        <v>1.409353771012573</v>
       </c>
       <c r="U39">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V39">
         <v>0.22</v>
       </c>
       <c r="W39">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y39">
-        <v>7.755228048953017</v>
+        <v>7.439892373220168</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1079685762710582</v>
+        <v>0.1077817246038863</v>
       </c>
       <c r="C40">
-        <v>46.30395126896414</v>
+        <v>45.87925007052004</v>
       </c>
       <c r="D40">
-        <v>70.42295126896414</v>
+        <v>70.63525007052004</v>
       </c>
       <c r="E40">
-        <v>-6.393999999999998</v>
+        <v>-5.756999999999998</v>
       </c>
       <c r="F40">
-        <v>24.206</v>
+        <v>24.843</v>
       </c>
       <c r="G40">
         <v>0.08699999999999999</v>
@@ -4555,28 +4555,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M40">
-        <v>1.3143858</v>
+        <v>1.3489749</v>
       </c>
       <c r="N40">
-        <v>8.46450308888889</v>
+        <v>8.42991398888889</v>
       </c>
       <c r="O40">
-        <v>1.862190679555556</v>
+        <v>1.854581077555556</v>
       </c>
       <c r="P40">
-        <v>6.602312409333334</v>
+        <v>6.575332911333334</v>
       </c>
       <c r="Q40">
-        <v>15.71231240933333</v>
+        <v>15.68533291133333</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1481839617275132</v>
+        <v>0.1496125649244038</v>
       </c>
       <c r="T40">
-        <v>1.409353771012573</v>
+        <v>1.429019031751134</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.439892373220168</v>
+        <v>7.249125902111958</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1077817246038863</v>
+        <v>0.1075948729367144</v>
       </c>
       <c r="C41">
-        <v>45.87925007052004</v>
+        <v>45.45583274509397</v>
       </c>
       <c r="D41">
-        <v>70.63525007052004</v>
+        <v>70.84883274509397</v>
       </c>
       <c r="E41">
-        <v>-5.756999999999998</v>
+        <v>-5.119999999999997</v>
       </c>
       <c r="F41">
-        <v>24.843</v>
+        <v>25.48</v>
       </c>
       <c r="G41">
         <v>0.08699999999999999</v>
@@ -4637,28 +4637,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M41">
-        <v>1.3489749</v>
+        <v>1.383564</v>
       </c>
       <c r="N41">
-        <v>8.42991398888889</v>
+        <v>8.39532488888889</v>
       </c>
       <c r="O41">
-        <v>1.854581077555556</v>
+        <v>1.846971475555556</v>
       </c>
       <c r="P41">
-        <v>6.575332911333334</v>
+        <v>6.548353413333334</v>
       </c>
       <c r="Q41">
-        <v>15.68533291133333</v>
+        <v>15.65835341333333</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1496125649244038</v>
+        <v>0.1510887882278573</v>
       </c>
       <c r="T41">
-        <v>1.429019031751134</v>
+        <v>1.449339801180979</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.249125902111958</v>
+        <v>7.067897754559159</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1075948729367144</v>
+        <v>0.1074080212695425</v>
       </c>
       <c r="C42">
-        <v>45.45583274509397</v>
+        <v>45.03371097430515</v>
       </c>
       <c r="D42">
-        <v>70.84883274509397</v>
+        <v>71.06371097430515</v>
       </c>
       <c r="E42">
-        <v>-5.119999999999997</v>
+        <v>-4.482999999999997</v>
       </c>
       <c r="F42">
-        <v>25.48</v>
+        <v>26.117</v>
       </c>
       <c r="G42">
         <v>0.08699999999999999</v>
@@ -4719,28 +4719,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M42">
-        <v>1.383564</v>
+        <v>1.4181531</v>
       </c>
       <c r="N42">
-        <v>8.39532488888889</v>
+        <v>8.36073578888889</v>
       </c>
       <c r="O42">
-        <v>1.846971475555556</v>
+        <v>1.839361873555556</v>
       </c>
       <c r="P42">
-        <v>6.548353413333334</v>
+        <v>6.521373915333334</v>
       </c>
       <c r="Q42">
-        <v>15.65835341333333</v>
+        <v>15.63137391533333</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1510887882278573</v>
+        <v>0.1526150529992246</v>
       </c>
       <c r="T42">
-        <v>1.449339801180979</v>
+        <v>1.470349410252514</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.067897754559159</v>
+        <v>6.89551000444796</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1074080212695425</v>
+        <v>0.1072211696023706</v>
       </c>
       <c r="C43">
-        <v>45.03371097430515</v>
+        <v>44.61289658192109</v>
       </c>
       <c r="D43">
-        <v>71.06371097430515</v>
+        <v>71.27989658192109</v>
       </c>
       <c r="E43">
-        <v>-4.482999999999997</v>
+        <v>-3.845999999999997</v>
       </c>
       <c r="F43">
-        <v>26.117</v>
+        <v>26.754</v>
       </c>
       <c r="G43">
         <v>0.08699999999999999</v>
@@ -4801,28 +4801,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M43">
-        <v>1.4181531</v>
+        <v>1.4527422</v>
       </c>
       <c r="N43">
-        <v>8.36073578888889</v>
+        <v>8.32614668888889</v>
       </c>
       <c r="O43">
-        <v>1.839361873555556</v>
+        <v>1.831752271555556</v>
       </c>
       <c r="P43">
-        <v>6.521373915333334</v>
+        <v>6.494394417333335</v>
       </c>
       <c r="Q43">
-        <v>15.63137391533333</v>
+        <v>15.60439441733334</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1526150529992246</v>
+        <v>0.1541939475902942</v>
       </c>
       <c r="T43">
-        <v>1.470349410252514</v>
+        <v>1.492083488602378</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.89551000444796</v>
+        <v>6.731331194818247</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1072211696023706</v>
+        <v>0.1070343179351987</v>
       </c>
       <c r="C44">
-        <v>44.61289658192108</v>
+        <v>44.1934015360265</v>
       </c>
       <c r="D44">
-        <v>71.27989658192108</v>
+        <v>71.4974015360265</v>
       </c>
       <c r="E44">
-        <v>-3.846</v>
+        <v>-3.209</v>
       </c>
       <c r="F44">
-        <v>26.754</v>
+        <v>27.391</v>
       </c>
       <c r="G44">
         <v>0.08699999999999999</v>
@@ -4883,28 +4883,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M44">
-        <v>1.4527422</v>
+        <v>1.4873313</v>
       </c>
       <c r="N44">
-        <v>8.32614668888889</v>
+        <v>8.291557588888889</v>
       </c>
       <c r="O44">
-        <v>1.831752271555556</v>
+        <v>1.824142669555556</v>
       </c>
       <c r="P44">
-        <v>6.494394417333335</v>
+        <v>6.467414919333333</v>
       </c>
       <c r="Q44">
-        <v>15.60439441733334</v>
+        <v>15.57741491933333</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1541939475902942</v>
+        <v>0.1558282419915767</v>
       </c>
       <c r="T44">
-        <v>1.492083488602378</v>
+        <v>1.514580166192588</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.731331194818248</v>
+        <v>6.57478860889224</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1070343179351987</v>
+        <v>0.1068474662680268</v>
       </c>
       <c r="C45">
-        <v>44.1934015360265</v>
+        <v>43.7752379512319</v>
       </c>
       <c r="D45">
-        <v>71.4974015360265</v>
+        <v>71.7162379512319</v>
       </c>
       <c r="E45">
-        <v>-3.209</v>
+        <v>-2.571999999999999</v>
       </c>
       <c r="F45">
-        <v>27.391</v>
+        <v>28.028</v>
       </c>
       <c r="G45">
         <v>0.08699999999999999</v>
@@ -4965,28 +4965,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M45">
-        <v>1.4873313</v>
+        <v>1.5219204</v>
       </c>
       <c r="N45">
-        <v>8.291557588888889</v>
+        <v>8.256968488888889</v>
       </c>
       <c r="O45">
-        <v>1.824142669555556</v>
+        <v>1.816533067555556</v>
       </c>
       <c r="P45">
-        <v>6.467414919333333</v>
+        <v>6.440435421333333</v>
       </c>
       <c r="Q45">
-        <v>15.57741491933333</v>
+        <v>15.55043542133333</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1558282419915767</v>
+        <v>0.1575209040500479</v>
       </c>
       <c r="T45">
-        <v>1.514580166192588</v>
+        <v>1.537880296553877</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.57478860889224</v>
+        <v>6.425361595053781</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1068474662680268</v>
+        <v>0.1066606146008549</v>
       </c>
       <c r="C46">
-        <v>43.7752379512319</v>
+        <v>43.35841809092268</v>
       </c>
       <c r="D46">
-        <v>71.7162379512319</v>
+        <v>71.93641809092269</v>
       </c>
       <c r="E46">
-        <v>-2.571999999999999</v>
+        <v>-1.934999999999999</v>
       </c>
       <c r="F46">
-        <v>28.028</v>
+        <v>28.665</v>
       </c>
       <c r="G46">
         <v>0.08699999999999999</v>
@@ -5047,28 +5047,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M46">
-        <v>1.5219204</v>
+        <v>1.5565095</v>
       </c>
       <c r="N46">
-        <v>8.256968488888889</v>
+        <v>8.222379388888889</v>
       </c>
       <c r="O46">
-        <v>1.816533067555556</v>
+        <v>1.808923465555556</v>
       </c>
       <c r="P46">
-        <v>6.440435421333333</v>
+        <v>6.413455923333333</v>
       </c>
       <c r="Q46">
-        <v>15.55043542133333</v>
+        <v>15.52345592333333</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1575209040500479</v>
+        <v>0.1592751174560998</v>
       </c>
       <c r="T46">
-        <v>1.537880296553877</v>
+        <v>1.562027704382849</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.425361595053781</v>
+        <v>6.282575781830364</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1066606146008549</v>
+        <v>0.106473762933683</v>
       </c>
       <c r="C47">
-        <v>43.35841809092268</v>
+        <v>42.94295436955032</v>
       </c>
       <c r="D47">
-        <v>71.93641809092269</v>
+        <v>72.15795436955032</v>
       </c>
       <c r="E47">
-        <v>-1.934999999999999</v>
+        <v>-1.297999999999998</v>
       </c>
       <c r="F47">
-        <v>28.665</v>
+        <v>29.302</v>
       </c>
       <c r="G47">
         <v>0.08699999999999999</v>
@@ -5129,28 +5129,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M47">
-        <v>1.5565095</v>
+        <v>1.5910986</v>
       </c>
       <c r="N47">
-        <v>8.222379388888889</v>
+        <v>8.187790288888889</v>
       </c>
       <c r="O47">
-        <v>1.808923465555556</v>
+        <v>1.801313863555556</v>
       </c>
       <c r="P47">
-        <v>6.413455923333333</v>
+        <v>6.386476425333334</v>
       </c>
       <c r="Q47">
-        <v>15.52345592333333</v>
+        <v>15.49647642533333</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1592751174560998</v>
+        <v>0.1610943017290426</v>
       </c>
       <c r="T47">
-        <v>1.562027704382849</v>
+        <v>1.587069460649932</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.282575781830364</v>
+        <v>6.145998047442747</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.106473762933683</v>
+        <v>0.1066535112665111</v>
       </c>
       <c r="C48">
-        <v>42.94295436955032</v>
+        <v>42.09281511549136</v>
       </c>
       <c r="D48">
-        <v>72.15795436955032</v>
+        <v>71.94481511549137</v>
       </c>
       <c r="E48">
-        <v>-1.297999999999998</v>
+        <v>-0.6609999999999978</v>
       </c>
       <c r="F48">
-        <v>29.302</v>
+        <v>29.939</v>
       </c>
       <c r="G48">
         <v>0.08699999999999999</v>
@@ -5211,45 +5211,45 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M48">
-        <v>1.5910986</v>
+        <v>1.6556267</v>
       </c>
       <c r="N48">
-        <v>8.187790288888889</v>
+        <v>8.123262188888889</v>
       </c>
       <c r="O48">
-        <v>1.801313863555556</v>
+        <v>1.787117681555556</v>
       </c>
       <c r="P48">
-        <v>6.386476425333334</v>
+        <v>6.336144507333334</v>
       </c>
       <c r="Q48">
-        <v>15.49647642533333</v>
+        <v>15.44614450733333</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1610943017290426</v>
+        <v>0.1629821344651153</v>
       </c>
       <c r="T48">
-        <v>1.587069460649932</v>
+        <v>1.613056188851621</v>
       </c>
       <c r="U48">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V48">
         <v>0.22</v>
       </c>
       <c r="W48">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y48">
-        <v>6.145998047442747</v>
+        <v>5.90645759028221</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1066535112665111</v>
+        <v>0.1064744595993392</v>
       </c>
       <c r="C49">
-        <v>42.09281511549136</v>
+        <v>41.66812585012116</v>
       </c>
       <c r="D49">
-        <v>71.94481511549137</v>
+        <v>72.15712585012116</v>
       </c>
       <c r="E49">
-        <v>-0.6609999999999978</v>
+        <v>-0.02399999999999736</v>
       </c>
       <c r="F49">
-        <v>29.939</v>
+        <v>30.576</v>
       </c>
       <c r="G49">
         <v>0.08699999999999999</v>
@@ -5293,28 +5293,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M49">
-        <v>1.6556267</v>
+        <v>1.6908528</v>
       </c>
       <c r="N49">
-        <v>8.123262188888889</v>
+        <v>8.08803608888889</v>
       </c>
       <c r="O49">
-        <v>1.787117681555556</v>
+        <v>1.779367939555556</v>
       </c>
       <c r="P49">
-        <v>6.336144507333334</v>
+        <v>6.308668149333334</v>
       </c>
       <c r="Q49">
-        <v>15.44614450733333</v>
+        <v>15.41866814933333</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1629821344651153</v>
+        <v>0.1649425761525754</v>
       </c>
       <c r="T49">
-        <v>1.613056188851621</v>
+        <v>1.640042406599529</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.90645759028221</v>
+        <v>5.783406390484664</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1064744595993392</v>
+        <v>0.1062954079321673</v>
       </c>
       <c r="C50">
-        <v>41.66812585012119</v>
+        <v>41.24469336083676</v>
       </c>
       <c r="D50">
-        <v>72.15712585012119</v>
+        <v>72.37069336083675</v>
       </c>
       <c r="E50">
-        <v>-0.02400000000000091</v>
+        <v>0.6129999999999995</v>
       </c>
       <c r="F50">
-        <v>30.576</v>
+        <v>31.213</v>
       </c>
       <c r="G50">
         <v>0.08699999999999999</v>
@@ -5375,28 +5375,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M50">
-        <v>1.6908528</v>
+        <v>1.7260789</v>
       </c>
       <c r="N50">
-        <v>8.08803608888889</v>
+        <v>8.052809988888889</v>
       </c>
       <c r="O50">
-        <v>1.779367939555556</v>
+        <v>1.771618197555556</v>
       </c>
       <c r="P50">
-        <v>6.308668149333334</v>
+        <v>6.281191791333333</v>
       </c>
       <c r="Q50">
-        <v>15.41866814933333</v>
+        <v>15.39119179133333</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1649425761525754</v>
+        <v>0.1669798979062104</v>
       </c>
       <c r="T50">
-        <v>1.640042406599529</v>
+        <v>1.668086907396374</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.783406390484665</v>
+        <v>5.665377688638038</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1062954079321673</v>
+        <v>0.1061163562649954</v>
       </c>
       <c r="C51">
-        <v>41.24469336083676</v>
+        <v>40.8225288400178</v>
       </c>
       <c r="D51">
-        <v>72.37069336083675</v>
+        <v>72.5855288400178</v>
       </c>
       <c r="E51">
-        <v>0.6129999999999995</v>
+        <v>1.25</v>
       </c>
       <c r="F51">
-        <v>31.213</v>
+        <v>31.85</v>
       </c>
       <c r="G51">
         <v>0.08699999999999999</v>
@@ -5457,28 +5457,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M51">
-        <v>1.7260789</v>
+        <v>1.761305</v>
       </c>
       <c r="N51">
-        <v>8.052809988888889</v>
+        <v>8.01758388888889</v>
       </c>
       <c r="O51">
-        <v>1.771618197555556</v>
+        <v>1.763868455555556</v>
       </c>
       <c r="P51">
-        <v>6.281191791333333</v>
+        <v>6.253715433333334</v>
       </c>
       <c r="Q51">
-        <v>15.39119179133333</v>
+        <v>15.36371543333333</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1669798979062104</v>
+        <v>0.1690987125299908</v>
       </c>
       <c r="T51">
-        <v>1.668086907396374</v>
+        <v>1.697253188225094</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.665377688638038</v>
+        <v>5.552070134865279</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1061163562649954</v>
+        <v>0.1059373045978235</v>
       </c>
       <c r="C52">
-        <v>40.8225288400178</v>
+        <v>40.40164361333986</v>
       </c>
       <c r="D52">
-        <v>72.5855288400178</v>
+        <v>72.80164361333986</v>
       </c>
       <c r="E52">
-        <v>1.25</v>
+        <v>1.887</v>
       </c>
       <c r="F52">
-        <v>31.85</v>
+        <v>32.487</v>
       </c>
       <c r="G52">
         <v>0.08699999999999999</v>
@@ -5539,28 +5539,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M52">
-        <v>1.761305</v>
+        <v>1.7965311</v>
       </c>
       <c r="N52">
-        <v>8.01758388888889</v>
+        <v>7.98235778888889</v>
       </c>
       <c r="O52">
-        <v>1.763868455555556</v>
+        <v>1.756118713555556</v>
       </c>
       <c r="P52">
-        <v>6.253715433333334</v>
+        <v>6.226239075333334</v>
       </c>
       <c r="Q52">
-        <v>15.36371543333333</v>
+        <v>15.33623907533333</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1690987125299908</v>
+        <v>0.1713040093833133</v>
       </c>
       <c r="T52">
-        <v>1.697253188225094</v>
+        <v>1.727609929495802</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.552070134865279</v>
+        <v>5.443206014573803</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1059373045978235</v>
+        <v>0.1057582529306516</v>
       </c>
       <c r="C53">
-        <v>40.40164361333986</v>
+        <v>39.98204914176478</v>
       </c>
       <c r="D53">
-        <v>72.80164361333986</v>
+        <v>73.01904914176478</v>
       </c>
       <c r="E53">
-        <v>1.887</v>
+        <v>2.524000000000001</v>
       </c>
       <c r="F53">
-        <v>32.487</v>
+        <v>33.124</v>
       </c>
       <c r="G53">
         <v>0.08699999999999999</v>
@@ -5621,28 +5621,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M53">
-        <v>1.7965311</v>
+        <v>1.8317572</v>
       </c>
       <c r="N53">
-        <v>7.98235778888889</v>
+        <v>7.94713168888889</v>
       </c>
       <c r="O53">
-        <v>1.756118713555556</v>
+        <v>1.748368971555556</v>
       </c>
       <c r="P53">
-        <v>6.226239075333334</v>
+        <v>6.198762717333334</v>
       </c>
       <c r="Q53">
-        <v>15.33623907533333</v>
+        <v>15.30876271733333</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1713040093833133</v>
+        <v>0.1736011936055242</v>
       </c>
       <c r="T53">
-        <v>1.727609929495802</v>
+        <v>1.759231534986123</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.443206014573803</v>
+        <v>5.338528975831998</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1057582529306516</v>
+        <v>0.1055792012634797</v>
       </c>
       <c r="C54">
-        <v>39.98204914176478</v>
+        <v>39.5637570235666</v>
       </c>
       <c r="D54">
-        <v>73.01904914176478</v>
+        <v>73.2377570235666</v>
       </c>
       <c r="E54">
-        <v>2.524000000000001</v>
+        <v>3.161000000000001</v>
       </c>
       <c r="F54">
-        <v>33.124</v>
+        <v>33.761</v>
       </c>
       <c r="G54">
         <v>0.08699999999999999</v>
@@ -5703,28 +5703,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M54">
-        <v>1.8317572</v>
+        <v>1.8669833</v>
       </c>
       <c r="N54">
-        <v>7.94713168888889</v>
+        <v>7.91190558888889</v>
       </c>
       <c r="O54">
-        <v>1.748368971555556</v>
+        <v>1.740619229555556</v>
       </c>
       <c r="P54">
-        <v>6.198762717333334</v>
+        <v>6.171286359333334</v>
       </c>
       <c r="Q54">
-        <v>15.30876271733333</v>
+        <v>15.28128635933333</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1736011936055242</v>
+        <v>0.1759961303478292</v>
       </c>
       <c r="T54">
-        <v>1.759231534986123</v>
+        <v>1.792198740710074</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.338528975831998</v>
+        <v>5.237802014023847</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1055792012634797</v>
+        <v>0.1054001495963078</v>
       </c>
       <c r="C55">
-        <v>39.5637570235666</v>
+        <v>39.14677899639418</v>
       </c>
       <c r="D55">
-        <v>73.2377570235666</v>
+        <v>73.45777899639418</v>
       </c>
       <c r="E55">
-        <v>3.161000000000001</v>
+        <v>3.798000000000002</v>
       </c>
       <c r="F55">
-        <v>33.761</v>
+        <v>34.398</v>
       </c>
       <c r="G55">
         <v>0.08699999999999999</v>
@@ -5785,28 +5785,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M55">
-        <v>1.8669833</v>
+        <v>1.9022094</v>
       </c>
       <c r="N55">
-        <v>7.91190558888889</v>
+        <v>7.87667948888889</v>
       </c>
       <c r="O55">
-        <v>1.740619229555556</v>
+        <v>1.732869487555556</v>
       </c>
       <c r="P55">
-        <v>6.171286359333334</v>
+        <v>6.143810001333334</v>
       </c>
       <c r="Q55">
-        <v>15.28128635933333</v>
+        <v>15.25381000133333</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1759961303478292</v>
+        <v>0.1784951947745823</v>
       </c>
       <c r="T55">
-        <v>1.792198740710074</v>
+        <v>1.826599303204632</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.237802014023847</v>
+        <v>5.140805680430813</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1054001495963078</v>
+        <v>0.1052210979291359</v>
       </c>
       <c r="C56">
-        <v>39.14677899639418</v>
+        <v>38.73112693937119</v>
       </c>
       <c r="D56">
-        <v>73.45777899639418</v>
+        <v>73.67912693937119</v>
       </c>
       <c r="E56">
-        <v>3.798000000000002</v>
+        <v>4.435000000000002</v>
       </c>
       <c r="F56">
-        <v>34.398</v>
+        <v>35.035</v>
       </c>
       <c r="G56">
         <v>0.08699999999999999</v>
@@ -5867,28 +5867,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M56">
-        <v>1.9022094</v>
+        <v>1.9374355</v>
       </c>
       <c r="N56">
-        <v>7.87667948888889</v>
+        <v>7.84145338888889</v>
       </c>
       <c r="O56">
-        <v>1.732869487555556</v>
+        <v>1.725119745555556</v>
       </c>
       <c r="P56">
-        <v>6.143810001333334</v>
+        <v>6.116333643333334</v>
       </c>
       <c r="Q56">
-        <v>15.25381000133333</v>
+        <v>15.22633364333333</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1784951947745823</v>
+        <v>0.1811053287314132</v>
       </c>
       <c r="T56">
-        <v>1.826599303204632</v>
+        <v>1.862528779587837</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.140805680430813</v>
+        <v>5.047336486241162</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1052210979291359</v>
+        <v>0.105042046261964</v>
       </c>
       <c r="C57">
-        <v>38.73112693937119</v>
+        <v>38.31681287523387</v>
       </c>
       <c r="D57">
-        <v>73.67912693937119</v>
+        <v>73.90181287523387</v>
       </c>
       <c r="E57">
-        <v>4.435000000000002</v>
+        <v>5.072000000000003</v>
       </c>
       <c r="F57">
-        <v>35.035</v>
+        <v>35.672</v>
       </c>
       <c r="G57">
         <v>0.08699999999999999</v>
@@ -5949,28 +5949,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M57">
-        <v>1.9374355</v>
+        <v>1.9726616</v>
       </c>
       <c r="N57">
-        <v>7.84145338888889</v>
+        <v>7.80622728888889</v>
       </c>
       <c r="O57">
-        <v>1.725119745555556</v>
+        <v>1.717370003555556</v>
       </c>
       <c r="P57">
-        <v>6.116333643333334</v>
+        <v>6.088857285333334</v>
       </c>
       <c r="Q57">
-        <v>15.22633364333333</v>
+        <v>15.19885728533333</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1811053287314132</v>
+        <v>0.1838341051408273</v>
       </c>
       <c r="T57">
-        <v>1.862528779587837</v>
+        <v>1.900091413988461</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.047336486241162</v>
+        <v>4.957205477558284</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.105042046261964</v>
+        <v>0.1048629945947921</v>
       </c>
       <c r="C58">
-        <v>38.31681287523387</v>
+        <v>37.90384897250792</v>
       </c>
       <c r="D58">
-        <v>73.90181287523387</v>
+        <v>74.12584897250792</v>
       </c>
       <c r="E58">
-        <v>5.072000000000003</v>
+        <v>5.709000000000003</v>
       </c>
       <c r="F58">
-        <v>35.672</v>
+        <v>36.309</v>
       </c>
       <c r="G58">
         <v>0.08699999999999999</v>
@@ -6031,28 +6031,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M58">
-        <v>1.9726616</v>
+        <v>2.0078877</v>
       </c>
       <c r="N58">
-        <v>7.80622728888889</v>
+        <v>7.771001188888889</v>
       </c>
       <c r="O58">
-        <v>1.717370003555556</v>
+        <v>1.709620261555556</v>
       </c>
       <c r="P58">
-        <v>6.088857285333334</v>
+        <v>6.061380927333333</v>
       </c>
       <c r="Q58">
-        <v>15.19885728533333</v>
+        <v>15.17138092733333</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1838341051408273</v>
+        <v>0.1866898013832375</v>
       </c>
       <c r="T58">
-        <v>1.900091413988461</v>
+        <v>1.939401147663532</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.957205477558284</v>
+        <v>4.870236960408138</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1048629945947921</v>
+        <v>0.1046839429276202</v>
       </c>
       <c r="C59">
-        <v>37.90384897250792</v>
+        <v>37.49224754772518</v>
       </c>
       <c r="D59">
-        <v>74.12584897250792</v>
+        <v>74.35124754772518</v>
       </c>
       <c r="E59">
-        <v>5.709000000000003</v>
+        <v>6.346000000000004</v>
       </c>
       <c r="F59">
-        <v>36.309</v>
+        <v>36.94600000000001</v>
       </c>
       <c r="G59">
         <v>0.08699999999999999</v>
@@ -6113,28 +6113,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M59">
-        <v>2.0078877</v>
+        <v>2.0431138</v>
       </c>
       <c r="N59">
-        <v>7.771001188888889</v>
+        <v>7.735775088888889</v>
       </c>
       <c r="O59">
-        <v>1.709620261555556</v>
+        <v>1.701870519555556</v>
       </c>
       <c r="P59">
-        <v>6.061380927333333</v>
+        <v>6.033904569333334</v>
       </c>
       <c r="Q59">
-        <v>15.17138092733333</v>
+        <v>15.14390456933333</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1866898013832375</v>
+        <v>0.1896814831610006</v>
       </c>
       <c r="T59">
-        <v>1.939401147663532</v>
+        <v>1.980582773418368</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.870236960408138</v>
+        <v>4.786267357642481</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1046839429276202</v>
+        <v>0.1045048912604483</v>
       </c>
       <c r="C60">
-        <v>37.49224754772519</v>
+        <v>37.0820210676806</v>
       </c>
       <c r="D60">
-        <v>74.35124754772518</v>
+        <v>74.5780210676806</v>
       </c>
       <c r="E60">
-        <v>6.345999999999997</v>
+        <v>6.982999999999997</v>
       </c>
       <c r="F60">
-        <v>36.946</v>
+        <v>37.583</v>
       </c>
       <c r="G60">
         <v>0.08699999999999999</v>
@@ -6195,28 +6195,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M60">
-        <v>2.0431138</v>
+        <v>2.0783399</v>
       </c>
       <c r="N60">
-        <v>7.735775088888889</v>
+        <v>7.70054898888889</v>
       </c>
       <c r="O60">
-        <v>1.701870519555556</v>
+        <v>1.694120777555556</v>
       </c>
       <c r="P60">
-        <v>6.033904569333334</v>
+        <v>6.006428211333334</v>
       </c>
       <c r="Q60">
-        <v>15.14390456933333</v>
+        <v>15.11642821133333</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1896814831610005</v>
+        <v>0.1928191006352398</v>
       </c>
       <c r="T60">
-        <v>1.980582773418368</v>
+        <v>2.023773258966123</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.786267357642481</v>
+        <v>4.705144182089219</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1045048912604483</v>
+        <v>0.1043258395932764</v>
       </c>
       <c r="C61">
-        <v>37.0820210676806</v>
+        <v>36.67318215173077</v>
       </c>
       <c r="D61">
-        <v>74.5780210676806</v>
+        <v>74.80618215173077</v>
       </c>
       <c r="E61">
-        <v>6.982999999999997</v>
+        <v>7.619999999999997</v>
       </c>
       <c r="F61">
-        <v>37.583</v>
+        <v>38.22</v>
       </c>
       <c r="G61">
         <v>0.08699999999999999</v>
@@ -6277,28 +6277,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M61">
-        <v>2.0783399</v>
+        <v>2.113566</v>
       </c>
       <c r="N61">
-        <v>7.70054898888889</v>
+        <v>7.665322888888889</v>
       </c>
       <c r="O61">
-        <v>1.694120777555556</v>
+        <v>1.686371035555556</v>
       </c>
       <c r="P61">
-        <v>6.006428211333334</v>
+        <v>5.978951853333333</v>
       </c>
       <c r="Q61">
-        <v>15.11642821133333</v>
+        <v>15.08895185333333</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1928191006352398</v>
+        <v>0.1961135989831911</v>
       </c>
       <c r="T61">
-        <v>2.023773258966123</v>
+        <v>2.069123268791266</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.705144182089219</v>
+        <v>4.626725112387732</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1043258395932764</v>
+        <v>0.1041467879261045</v>
       </c>
       <c r="C62">
-        <v>36.67318215173077</v>
+        <v>36.26574357413496</v>
       </c>
       <c r="D62">
-        <v>74.80618215173077</v>
+        <v>75.03574357413495</v>
       </c>
       <c r="E62">
-        <v>7.619999999999997</v>
+        <v>8.256999999999998</v>
       </c>
       <c r="F62">
-        <v>38.22</v>
+        <v>38.857</v>
       </c>
       <c r="G62">
         <v>0.08699999999999999</v>
@@ -6359,28 +6359,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M62">
-        <v>2.113566</v>
+        <v>2.1487921</v>
       </c>
       <c r="N62">
-        <v>7.665322888888889</v>
+        <v>7.63009678888889</v>
       </c>
       <c r="O62">
-        <v>1.686371035555556</v>
+        <v>1.678621293555556</v>
       </c>
       <c r="P62">
-        <v>5.978951853333333</v>
+        <v>5.951475495333335</v>
       </c>
       <c r="Q62">
-        <v>15.08895185333333</v>
+        <v>15.06147549533333</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1961135989831911</v>
+        <v>0.1995770459643706</v>
       </c>
       <c r="T62">
-        <v>2.069123268791266</v>
+        <v>2.116798920145903</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.626725112387732</v>
+        <v>4.550877159725639</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1041467879261045</v>
+        <v>0.1051767362589326</v>
       </c>
       <c r="C63">
-        <v>36.26574357413496</v>
+        <v>34.32717424132962</v>
       </c>
       <c r="D63">
-        <v>75.03574357413495</v>
+        <v>73.73417424132961</v>
       </c>
       <c r="E63">
-        <v>8.256999999999998</v>
+        <v>8.893999999999998</v>
       </c>
       <c r="F63">
-        <v>38.857</v>
+        <v>39.494</v>
       </c>
       <c r="G63">
         <v>0.08699999999999999</v>
@@ -6441,45 +6441,45 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M63">
-        <v>2.1487921</v>
+        <v>2.2827532</v>
       </c>
       <c r="N63">
-        <v>7.63009678888889</v>
+        <v>7.49613568888889</v>
       </c>
       <c r="O63">
-        <v>1.678621293555556</v>
+        <v>1.649149851555556</v>
       </c>
       <c r="P63">
-        <v>5.951475495333335</v>
+        <v>5.846985837333333</v>
       </c>
       <c r="Q63">
-        <v>15.06147549533333</v>
+        <v>14.95698583733333</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1995770459643706</v>
+        <v>0.2032227796287701</v>
       </c>
       <c r="T63">
-        <v>2.116798920145903</v>
+        <v>2.16698381630868</v>
       </c>
       <c r="U63">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V63">
         <v>0.22</v>
       </c>
       <c r="W63">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y63">
-        <v>4.550877159725639</v>
+        <v>4.283813462133747</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1051767362589326</v>
+        <v>0.1050171845917607</v>
       </c>
       <c r="C64">
-        <v>34.32717424132962</v>
+        <v>33.88883972177842</v>
       </c>
       <c r="D64">
-        <v>73.73417424132961</v>
+        <v>73.93283972177842</v>
       </c>
       <c r="E64">
-        <v>8.893999999999998</v>
+        <v>9.530999999999999</v>
       </c>
       <c r="F64">
-        <v>39.494</v>
+        <v>40.131</v>
       </c>
       <c r="G64">
         <v>0.08699999999999999</v>
@@ -6523,28 +6523,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M64">
-        <v>2.2827532</v>
+        <v>2.3195718</v>
       </c>
       <c r="N64">
-        <v>7.49613568888889</v>
+        <v>7.45931708888889</v>
       </c>
       <c r="O64">
-        <v>1.649149851555556</v>
+        <v>1.641049759555556</v>
       </c>
       <c r="P64">
-        <v>5.846985837333333</v>
+        <v>5.818267329333334</v>
       </c>
       <c r="Q64">
-        <v>14.95698583733333</v>
+        <v>14.92826732933333</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2032227796287701</v>
+        <v>0.2070655799777317</v>
       </c>
       <c r="T64">
-        <v>2.16698381630868</v>
+        <v>2.219881409561336</v>
       </c>
       <c r="U64">
         <v>0.0578</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.283813462133747</v>
+        <v>4.215816423052258</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1050171845917607</v>
+        <v>0.1048576329245888</v>
       </c>
       <c r="C65">
-        <v>33.88883972177842</v>
+        <v>33.45157864208741</v>
       </c>
       <c r="D65">
-        <v>73.93283972177842</v>
+        <v>74.13257864208741</v>
       </c>
       <c r="E65">
-        <v>9.530999999999999</v>
+        <v>10.168</v>
       </c>
       <c r="F65">
-        <v>40.131</v>
+        <v>40.768</v>
       </c>
       <c r="G65">
         <v>0.08699999999999999</v>
@@ -6605,28 +6605,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M65">
-        <v>2.3195718</v>
+        <v>2.3563904</v>
       </c>
       <c r="N65">
-        <v>7.45931708888889</v>
+        <v>7.422498488888889</v>
       </c>
       <c r="O65">
-        <v>1.641049759555556</v>
+        <v>1.632949667555556</v>
       </c>
       <c r="P65">
-        <v>5.818267329333334</v>
+        <v>5.789548821333334</v>
       </c>
       <c r="Q65">
-        <v>14.92826732933333</v>
+        <v>14.89954882133333</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2070655799777317</v>
+        <v>0.211121869234969</v>
       </c>
       <c r="T65">
-        <v>2.219881409561336</v>
+        <v>2.275717757994695</v>
       </c>
       <c r="U65">
         <v>0.0578</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.215816423052258</v>
+        <v>4.149944291442067</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1048576329245888</v>
+        <v>0.1046980812574169</v>
       </c>
       <c r="C66">
-        <v>33.45157864208741</v>
+        <v>33.01539972592548</v>
       </c>
       <c r="D66">
-        <v>74.13257864208741</v>
+        <v>74.33339972592547</v>
       </c>
       <c r="E66">
-        <v>10.168</v>
+        <v>10.805</v>
       </c>
       <c r="F66">
-        <v>40.768</v>
+        <v>41.405</v>
       </c>
       <c r="G66">
         <v>0.08699999999999999</v>
@@ -6687,28 +6687,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M66">
-        <v>2.3563904</v>
+        <v>2.393209</v>
       </c>
       <c r="N66">
-        <v>7.422498488888889</v>
+        <v>7.385679888888889</v>
       </c>
       <c r="O66">
-        <v>1.632949667555556</v>
+        <v>1.624849575555556</v>
       </c>
       <c r="P66">
-        <v>5.789548821333334</v>
+        <v>5.760830313333334</v>
       </c>
       <c r="Q66">
-        <v>14.89954882133333</v>
+        <v>14.87083031333333</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.211121869234969</v>
+        <v>0.2154099464497627</v>
       </c>
       <c r="T66">
-        <v>2.275717757994695</v>
+        <v>2.334744754909961</v>
       </c>
       <c r="U66">
         <v>0.0578</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.149944291442067</v>
+        <v>4.086098994650651</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1046980812574169</v>
+        <v>0.1045385295902451</v>
       </c>
       <c r="C67">
-        <v>33.01539972592548</v>
+        <v>32.580311791746</v>
       </c>
       <c r="D67">
-        <v>74.33339972592547</v>
+        <v>74.535311791746</v>
       </c>
       <c r="E67">
-        <v>10.805</v>
+        <v>11.442</v>
       </c>
       <c r="F67">
-        <v>41.405</v>
+        <v>42.042</v>
       </c>
       <c r="G67">
         <v>0.08699999999999999</v>
@@ -6769,28 +6769,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M67">
-        <v>2.393209</v>
+        <v>2.4300276</v>
       </c>
       <c r="N67">
-        <v>7.385679888888889</v>
+        <v>7.348861288888889</v>
       </c>
       <c r="O67">
-        <v>1.624849575555556</v>
+        <v>1.616749483555556</v>
       </c>
       <c r="P67">
-        <v>5.760830313333334</v>
+        <v>5.732111805333334</v>
       </c>
       <c r="Q67">
-        <v>14.87083031333333</v>
+        <v>14.84211180533333</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2154099464497627</v>
+        <v>0.2199502635007207</v>
       </c>
       <c r="T67">
-        <v>2.334744754909961</v>
+        <v>2.39724392811436</v>
       </c>
       <c r="U67">
         <v>0.0578</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.086098994650651</v>
+        <v>4.02418840382261</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1045385295902451</v>
+        <v>0.1062080779230731</v>
       </c>
       <c r="C68">
-        <v>32.580311791746</v>
+        <v>29.8833173370772</v>
       </c>
       <c r="D68">
-        <v>74.535311791746</v>
+        <v>72.4753173370772</v>
       </c>
       <c r="E68">
-        <v>11.442</v>
+        <v>12.079</v>
       </c>
       <c r="F68">
-        <v>42.042</v>
+        <v>42.679</v>
       </c>
       <c r="G68">
         <v>0.08699999999999999</v>
@@ -6851,45 +6851,45 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M68">
-        <v>2.4300276</v>
+        <v>2.6162227</v>
       </c>
       <c r="N68">
-        <v>7.348861288888889</v>
+        <v>7.16266618888889</v>
       </c>
       <c r="O68">
-        <v>1.616749483555556</v>
+        <v>1.575786561555556</v>
       </c>
       <c r="P68">
-        <v>5.732111805333334</v>
+        <v>5.586879627333334</v>
       </c>
       <c r="Q68">
-        <v>14.84211180533333</v>
+        <v>14.69687962733333</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2199502635007207</v>
+        <v>0.2247657512820398</v>
       </c>
       <c r="T68">
-        <v>2.39724392811436</v>
+        <v>2.463530929997813</v>
       </c>
       <c r="U68">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V68">
         <v>0.22</v>
       </c>
       <c r="W68">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y68">
-        <v>4.02418840382261</v>
+        <v>3.737789175550265</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1062080779230731</v>
+        <v>0.1060758262559013</v>
       </c>
       <c r="C69">
-        <v>29.8833173370772</v>
+        <v>29.40533600412869</v>
       </c>
       <c r="D69">
-        <v>72.4753173370772</v>
+        <v>72.63433600412868</v>
       </c>
       <c r="E69">
-        <v>12.079</v>
+        <v>12.716</v>
       </c>
       <c r="F69">
-        <v>42.679</v>
+        <v>43.316</v>
       </c>
       <c r="G69">
         <v>0.08699999999999999</v>
@@ -6933,28 +6933,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M69">
-        <v>2.6162227</v>
+        <v>2.6552708</v>
       </c>
       <c r="N69">
-        <v>7.16266618888889</v>
+        <v>7.12361808888889</v>
       </c>
       <c r="O69">
-        <v>1.575786561555556</v>
+        <v>1.567195979555556</v>
       </c>
       <c r="P69">
-        <v>5.586879627333334</v>
+        <v>5.556422109333334</v>
       </c>
       <c r="Q69">
-        <v>14.69687962733333</v>
+        <v>14.66642210933333</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2247657512820398</v>
+        <v>0.2298822070496915</v>
       </c>
       <c r="T69">
-        <v>2.463530929997813</v>
+        <v>2.533960869498982</v>
       </c>
       <c r="U69">
         <v>0.0613</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.737789175550265</v>
+        <v>3.682821687674526</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1060758262559013</v>
+        <v>0.1059435745887294</v>
       </c>
       <c r="C70">
-        <v>29.40533600412869</v>
+        <v>28.92805401384389</v>
       </c>
       <c r="D70">
-        <v>72.63433600412868</v>
+        <v>72.79405401384389</v>
       </c>
       <c r="E70">
-        <v>12.716</v>
+        <v>13.353</v>
       </c>
       <c r="F70">
-        <v>43.316</v>
+        <v>43.953</v>
       </c>
       <c r="G70">
         <v>0.08699999999999999</v>
@@ -7015,28 +7015,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M70">
-        <v>2.6552708</v>
+        <v>2.6943189</v>
       </c>
       <c r="N70">
-        <v>7.12361808888889</v>
+        <v>7.084569988888889</v>
       </c>
       <c r="O70">
-        <v>1.567195979555556</v>
+        <v>1.558605397555556</v>
       </c>
       <c r="P70">
-        <v>5.556422109333334</v>
+        <v>5.525964591333334</v>
       </c>
       <c r="Q70">
-        <v>14.66642210933333</v>
+        <v>14.63596459133333</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2298822070496915</v>
+        <v>0.2353287567378367</v>
       </c>
       <c r="T70">
-        <v>2.533960869498982</v>
+        <v>2.608934676064742</v>
       </c>
       <c r="U70">
         <v>0.0613</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.682821687674526</v>
+        <v>3.629447460316924</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1059435745887294</v>
+        <v>0.1058113229215574</v>
       </c>
       <c r="C71">
-        <v>28.92805401384389</v>
+        <v>28.45147598981194</v>
       </c>
       <c r="D71">
-        <v>72.79405401384389</v>
+        <v>72.95447598981194</v>
       </c>
       <c r="E71">
-        <v>13.353</v>
+        <v>13.99</v>
       </c>
       <c r="F71">
-        <v>43.953</v>
+        <v>44.59</v>
       </c>
       <c r="G71">
         <v>0.08699999999999999</v>
@@ -7097,28 +7097,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M71">
-        <v>2.6943189</v>
+        <v>2.733367</v>
       </c>
       <c r="N71">
-        <v>7.084569988888889</v>
+        <v>7.04552188888889</v>
       </c>
       <c r="O71">
-        <v>1.558605397555556</v>
+        <v>1.550014815555556</v>
       </c>
       <c r="P71">
-        <v>5.525964591333334</v>
+        <v>5.495507073333334</v>
       </c>
       <c r="Q71">
-        <v>14.63596459133333</v>
+        <v>14.60550707333333</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2353287567378367</v>
+        <v>0.2411384097385248</v>
       </c>
       <c r="T71">
-        <v>2.608934676064742</v>
+        <v>2.688906736401553</v>
       </c>
       <c r="U71">
         <v>0.0613</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.629447460316924</v>
+        <v>3.577598210883825</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1058113229215574</v>
+        <v>0.1056790712543856</v>
       </c>
       <c r="C72">
-        <v>28.45147598981194</v>
+        <v>27.97560659646939</v>
       </c>
       <c r="D72">
-        <v>72.95447598981194</v>
+        <v>73.11560659646939</v>
       </c>
       <c r="E72">
-        <v>13.99</v>
+        <v>14.627</v>
       </c>
       <c r="F72">
-        <v>44.59</v>
+        <v>45.227</v>
       </c>
       <c r="G72">
         <v>0.08699999999999999</v>
@@ -7179,28 +7179,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M72">
-        <v>2.733367</v>
+        <v>2.7724151</v>
       </c>
       <c r="N72">
-        <v>7.04552188888889</v>
+        <v>7.00647378888889</v>
       </c>
       <c r="O72">
-        <v>1.550014815555556</v>
+        <v>1.541424233555556</v>
       </c>
       <c r="P72">
-        <v>5.495507073333334</v>
+        <v>5.465049555333334</v>
       </c>
       <c r="Q72">
-        <v>14.60550707333333</v>
+        <v>14.57504955533333</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2411384097385248</v>
+        <v>0.2473487284633985</v>
       </c>
       <c r="T72">
-        <v>2.688906736401553</v>
+        <v>2.774394111244352</v>
       </c>
       <c r="U72">
         <v>0.0613</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.577598210883825</v>
+        <v>3.527209503688279</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1056790712543856</v>
+        <v>0.1071192995872137</v>
       </c>
       <c r="C73">
-        <v>27.9756065964694</v>
+        <v>25.62131417954644</v>
       </c>
       <c r="D73">
-        <v>73.11560659646939</v>
+        <v>71.39831417954643</v>
       </c>
       <c r="E73">
-        <v>14.627</v>
+        <v>15.264</v>
       </c>
       <c r="F73">
-        <v>45.227</v>
+        <v>45.864</v>
       </c>
       <c r="G73">
         <v>0.08699999999999999</v>
@@ -7261,45 +7261,45 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M73">
-        <v>2.7724151</v>
+        <v>2.9398824</v>
       </c>
       <c r="N73">
-        <v>7.00647378888889</v>
+        <v>6.83900648888889</v>
       </c>
       <c r="O73">
-        <v>1.541424233555556</v>
+        <v>1.504581427555556</v>
       </c>
       <c r="P73">
-        <v>5.465049555333334</v>
+        <v>5.334425061333334</v>
       </c>
       <c r="Q73">
-        <v>14.57504955533333</v>
+        <v>14.44442506133333</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2473487284633984</v>
+        <v>0.2540026413829059</v>
       </c>
       <c r="T73">
-        <v>2.774394111244351</v>
+        <v>2.86598772714735</v>
       </c>
       <c r="U73">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V73">
         <v>0.22</v>
       </c>
       <c r="W73">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y73">
-        <v>3.527209503688279</v>
+        <v>3.32628573472493</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1071192995872137</v>
+        <v>0.1070088879200417</v>
       </c>
       <c r="C74">
-        <v>25.62131417954644</v>
+        <v>25.11310604572325</v>
       </c>
       <c r="D74">
-        <v>71.39831417954643</v>
+        <v>71.52710604572324</v>
       </c>
       <c r="E74">
-        <v>15.264</v>
+        <v>15.901</v>
       </c>
       <c r="F74">
-        <v>45.864</v>
+        <v>46.501</v>
       </c>
       <c r="G74">
         <v>0.08699999999999999</v>
@@ -7343,28 +7343,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M74">
-        <v>2.9398824</v>
+        <v>2.9807141</v>
       </c>
       <c r="N74">
-        <v>6.83900648888889</v>
+        <v>6.79817478888889</v>
       </c>
       <c r="O74">
-        <v>1.504581427555556</v>
+        <v>1.495598453555556</v>
       </c>
       <c r="P74">
-        <v>5.334425061333334</v>
+        <v>5.302576335333334</v>
       </c>
       <c r="Q74">
-        <v>14.44442506133333</v>
+        <v>14.41257633533333</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2540026413829059</v>
+        <v>0.2611494367408953</v>
       </c>
       <c r="T74">
-        <v>2.86598772714735</v>
+        <v>2.964366055339458</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.32628573472493</v>
+        <v>3.280720176714999</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1070088879200417</v>
+        <v>0.1068984762528698</v>
       </c>
       <c r="C75">
-        <v>25.11310604572325</v>
+        <v>24.60536339403752</v>
       </c>
       <c r="D75">
-        <v>71.52710604572324</v>
+        <v>71.65636339403751</v>
       </c>
       <c r="E75">
-        <v>15.901</v>
+        <v>16.538</v>
       </c>
       <c r="F75">
-        <v>46.501</v>
+        <v>47.138</v>
       </c>
       <c r="G75">
         <v>0.08699999999999999</v>
@@ -7425,28 +7425,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M75">
-        <v>2.9807141</v>
+        <v>3.0215458</v>
       </c>
       <c r="N75">
-        <v>6.79817478888889</v>
+        <v>6.75734308888889</v>
       </c>
       <c r="O75">
-        <v>1.495598453555556</v>
+        <v>1.486615479555556</v>
       </c>
       <c r="P75">
-        <v>5.302576335333334</v>
+        <v>5.270727609333334</v>
       </c>
       <c r="Q75">
-        <v>14.41257633533333</v>
+        <v>14.38072760933333</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2611494367408953</v>
+        <v>0.2688459855879609</v>
       </c>
       <c r="T75">
-        <v>2.964366055339458</v>
+        <v>3.070311947238653</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.280720176714999</v>
+        <v>3.236386120272905</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1068984762528698</v>
+        <v>0.106788064585698</v>
       </c>
       <c r="C76">
-        <v>24.60536339403752</v>
+        <v>24.09808875259014</v>
       </c>
       <c r="D76">
-        <v>71.65636339403751</v>
+        <v>71.78608875259015</v>
       </c>
       <c r="E76">
-        <v>16.538</v>
+        <v>17.175</v>
       </c>
       <c r="F76">
-        <v>47.138</v>
+        <v>47.77500000000001</v>
       </c>
       <c r="G76">
         <v>0.08699999999999999</v>
@@ -7507,28 +7507,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M76">
-        <v>3.0215458</v>
+        <v>3.062377500000001</v>
       </c>
       <c r="N76">
-        <v>6.75734308888889</v>
+        <v>6.71651138888889</v>
       </c>
       <c r="O76">
-        <v>1.486615479555556</v>
+        <v>1.477632505555556</v>
       </c>
       <c r="P76">
-        <v>5.270727609333334</v>
+        <v>5.238878883333334</v>
       </c>
       <c r="Q76">
-        <v>14.38072760933333</v>
+        <v>14.34887888333333</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2688459855879609</v>
+        <v>0.2771582583427918</v>
       </c>
       <c r="T76">
-        <v>3.070311947238653</v>
+        <v>3.184733510489782</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.236386120272905</v>
+        <v>3.193234305335932</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.106788064585698</v>
+        <v>0.1066776529185261</v>
       </c>
       <c r="C77">
-        <v>24.09808875259014</v>
+        <v>23.59128466782244</v>
       </c>
       <c r="D77">
-        <v>71.78608875259015</v>
+        <v>71.91628466782244</v>
       </c>
       <c r="E77">
-        <v>17.175</v>
+        <v>17.812</v>
       </c>
       <c r="F77">
-        <v>47.77500000000001</v>
+        <v>48.41200000000001</v>
       </c>
       <c r="G77">
         <v>0.08699999999999999</v>
@@ -7589,28 +7589,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M77">
-        <v>3.062377500000001</v>
+        <v>3.103209200000001</v>
       </c>
       <c r="N77">
-        <v>6.71651138888889</v>
+        <v>6.67567968888889</v>
       </c>
       <c r="O77">
-        <v>1.477632505555556</v>
+        <v>1.468649531555556</v>
       </c>
       <c r="P77">
-        <v>5.238878883333334</v>
+        <v>5.207030157333334</v>
       </c>
       <c r="Q77">
-        <v>14.34887888333333</v>
+        <v>14.31703015733333</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2771582583427918</v>
+        <v>0.2861632204938586</v>
       </c>
       <c r="T77">
-        <v>3.184733510489782</v>
+        <v>3.30869020401184</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.193234305335932</v>
+        <v>3.151218064476249</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1066776529185261</v>
+        <v>0.1065672412513541</v>
       </c>
       <c r="C78">
-        <v>23.59128466782244</v>
+        <v>23.08495370468297</v>
       </c>
       <c r="D78">
-        <v>71.91628466782244</v>
+        <v>72.04695370468298</v>
       </c>
       <c r="E78">
-        <v>17.812</v>
+        <v>18.44900000000001</v>
       </c>
       <c r="F78">
-        <v>48.41200000000001</v>
+        <v>49.04900000000001</v>
       </c>
       <c r="G78">
         <v>0.08699999999999999</v>
@@ -7671,28 +7671,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M78">
-        <v>3.103209200000001</v>
+        <v>3.144040900000001</v>
       </c>
       <c r="N78">
-        <v>6.67567968888889</v>
+        <v>6.63484798888889</v>
       </c>
       <c r="O78">
-        <v>1.468649531555556</v>
+        <v>1.459666557555556</v>
       </c>
       <c r="P78">
-        <v>5.207030157333334</v>
+        <v>5.175181431333334</v>
       </c>
       <c r="Q78">
-        <v>14.31703015733333</v>
+        <v>14.28518143133333</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2861632204938586</v>
+        <v>0.2959512228319746</v>
       </c>
       <c r="T78">
-        <v>3.30869020401184</v>
+        <v>3.443425740448859</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.151218064476249</v>
+        <v>3.110293154547986</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1065672412513541</v>
+        <v>0.1064568295841823</v>
       </c>
       <c r="C79">
-        <v>23.08495370468297</v>
+        <v>22.57909844679561</v>
       </c>
       <c r="D79">
-        <v>72.04695370468298</v>
+        <v>72.17809844679562</v>
       </c>
       <c r="E79">
-        <v>18.44900000000001</v>
+        <v>19.08600000000001</v>
       </c>
       <c r="F79">
-        <v>49.04900000000001</v>
+        <v>49.68600000000001</v>
       </c>
       <c r="G79">
         <v>0.08699999999999999</v>
@@ -7753,28 +7753,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M79">
-        <v>3.144040900000001</v>
+        <v>3.184872600000001</v>
       </c>
       <c r="N79">
-        <v>6.63484798888889</v>
+        <v>6.59401628888889</v>
       </c>
       <c r="O79">
-        <v>1.459666557555556</v>
+        <v>1.450683583555556</v>
       </c>
       <c r="P79">
-        <v>5.175181431333334</v>
+        <v>5.143332705333334</v>
       </c>
       <c r="Q79">
-        <v>14.28518143133333</v>
+        <v>14.25333270533333</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2959512228319746</v>
+        <v>0.3066290435644649</v>
       </c>
       <c r="T79">
-        <v>3.443425740448859</v>
+        <v>3.590409962016517</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.110293154547986</v>
+        <v>3.07041760128455</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1064568295841823</v>
+        <v>0.1063464179170104</v>
       </c>
       <c r="C80">
-        <v>22.57909844679561</v>
+        <v>22.0737214966304</v>
       </c>
       <c r="D80">
-        <v>72.17809844679562</v>
+        <v>72.3097214966304</v>
       </c>
       <c r="E80">
-        <v>19.08600000000001</v>
+        <v>19.72300000000001</v>
       </c>
       <c r="F80">
-        <v>49.68600000000001</v>
+        <v>50.32300000000001</v>
       </c>
       <c r="G80">
         <v>0.08699999999999999</v>
@@ -7835,28 +7835,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M80">
-        <v>3.184872600000001</v>
+        <v>3.225704300000001</v>
       </c>
       <c r="N80">
-        <v>6.59401628888889</v>
+        <v>6.55318458888889</v>
       </c>
       <c r="O80">
-        <v>1.450683583555556</v>
+        <v>1.441700609555556</v>
       </c>
       <c r="P80">
-        <v>5.143332705333334</v>
+        <v>5.111483979333334</v>
       </c>
       <c r="Q80">
-        <v>14.25333270533333</v>
+        <v>14.22148397933333</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3066290435644649</v>
+        <v>0.3183237996048113</v>
       </c>
       <c r="T80">
-        <v>3.590409962016517</v>
+        <v>3.751392680876332</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.07041760128455</v>
+        <v>3.03155155569867</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1063464179170104</v>
+        <v>0.1111032062498385</v>
       </c>
       <c r="C81">
-        <v>22.0737214966304</v>
+        <v>16.16956756471959</v>
       </c>
       <c r="D81">
-        <v>72.3097214966304</v>
+        <v>67.04256756471959</v>
       </c>
       <c r="E81">
-        <v>19.72300000000001</v>
+        <v>20.36000000000001</v>
       </c>
       <c r="F81">
-        <v>50.32300000000001</v>
+        <v>50.96000000000001</v>
       </c>
       <c r="G81">
         <v>0.08699999999999999</v>
@@ -7917,45 +7917,45 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M81">
-        <v>3.225704300000001</v>
+        <v>3.664024000000001</v>
       </c>
       <c r="N81">
-        <v>6.55318458888889</v>
+        <v>6.114864888888889</v>
       </c>
       <c r="O81">
-        <v>1.441700609555556</v>
+        <v>1.345270275555555</v>
       </c>
       <c r="P81">
-        <v>5.111483979333334</v>
+        <v>4.769594613333333</v>
       </c>
       <c r="Q81">
-        <v>14.22148397933333</v>
+        <v>13.87959461333333</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3183237996048113</v>
+        <v>0.3311880312491923</v>
       </c>
       <c r="T81">
-        <v>3.751392680876332</v>
+        <v>3.928473671622128</v>
       </c>
       <c r="U81">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V81">
         <v>0.22</v>
       </c>
       <c r="W81">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y81">
-        <v>3.03155155569867</v>
+        <v>2.668893241116566</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1111032062498385</v>
+        <v>0.1110536345826666</v>
       </c>
       <c r="C82">
-        <v>16.16956756471959</v>
+        <v>15.58349824263388</v>
       </c>
       <c r="D82">
-        <v>67.04256756471959</v>
+        <v>67.09349824263388</v>
       </c>
       <c r="E82">
-        <v>20.36000000000001</v>
+        <v>20.99700000000001</v>
       </c>
       <c r="F82">
-        <v>50.96000000000001</v>
+        <v>51.59700000000001</v>
       </c>
       <c r="G82">
         <v>0.08699999999999999</v>
@@ -7999,28 +7999,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M82">
-        <v>3.664024000000001</v>
+        <v>3.709824300000001</v>
       </c>
       <c r="N82">
-        <v>6.114864888888889</v>
+        <v>6.069064588888889</v>
       </c>
       <c r="O82">
-        <v>1.345270275555555</v>
+        <v>1.335194209555556</v>
       </c>
       <c r="P82">
-        <v>4.769594613333333</v>
+        <v>4.733870379333333</v>
       </c>
       <c r="Q82">
-        <v>13.87959461333333</v>
+        <v>13.84387037933333</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3311880312491923</v>
+        <v>0.3454063925403504</v>
       </c>
       <c r="T82">
-        <v>3.928473671622128</v>
+        <v>4.124194766656956</v>
       </c>
       <c r="U82">
         <v>0.07190000000000001</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.668893241116566</v>
+        <v>2.635943941843522</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1110536345826666</v>
+        <v>0.1110040629154947</v>
       </c>
       <c r="C83">
-        <v>15.58349824263388</v>
+        <v>14.99750636107879</v>
       </c>
       <c r="D83">
-        <v>67.09349824263388</v>
+        <v>67.1445063610788</v>
       </c>
       <c r="E83">
-        <v>20.99700000000001</v>
+        <v>21.63400000000001</v>
       </c>
       <c r="F83">
-        <v>51.59700000000001</v>
+        <v>52.23400000000001</v>
       </c>
       <c r="G83">
         <v>0.08699999999999999</v>
@@ -8081,28 +8081,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M83">
-        <v>3.709824300000001</v>
+        <v>3.755624600000001</v>
       </c>
       <c r="N83">
-        <v>6.069064588888889</v>
+        <v>6.023264288888889</v>
       </c>
       <c r="O83">
-        <v>1.335194209555556</v>
+        <v>1.325118143555556</v>
       </c>
       <c r="P83">
-        <v>4.733870379333333</v>
+        <v>4.698146145333333</v>
       </c>
       <c r="Q83">
-        <v>13.84387037933333</v>
+        <v>13.80814614533333</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3454063925403504</v>
+        <v>0.3612045717527482</v>
       </c>
       <c r="T83">
-        <v>4.124194766656956</v>
+        <v>4.341662650028987</v>
       </c>
       <c r="U83">
         <v>0.07190000000000001</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.635943941843522</v>
+        <v>2.603798284016163</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1110040629154947</v>
+        <v>0.1109544912483228</v>
       </c>
       <c r="C84">
-        <v>14.99750636107879</v>
+        <v>14.41159209681214</v>
       </c>
       <c r="D84">
-        <v>67.1445063610788</v>
+        <v>67.19559209681215</v>
       </c>
       <c r="E84">
-        <v>21.63400000000001</v>
+        <v>22.27100000000001</v>
       </c>
       <c r="F84">
-        <v>52.23400000000001</v>
+        <v>52.87100000000001</v>
       </c>
       <c r="G84">
         <v>0.08699999999999999</v>
@@ -8163,28 +8163,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M84">
-        <v>3.755624600000001</v>
+        <v>3.801424900000001</v>
       </c>
       <c r="N84">
-        <v>6.023264288888889</v>
+        <v>5.977463988888889</v>
       </c>
       <c r="O84">
-        <v>1.325118143555556</v>
+        <v>1.315042077555556</v>
       </c>
       <c r="P84">
-        <v>4.698146145333333</v>
+        <v>4.662421911333333</v>
       </c>
       <c r="Q84">
-        <v>13.80814614533333</v>
+        <v>13.77242191133333</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3612045717527482</v>
+        <v>0.3788613602842517</v>
       </c>
       <c r="T84">
-        <v>4.341662650028987</v>
+        <v>4.584714990268315</v>
       </c>
       <c r="U84">
         <v>0.07190000000000001</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.603798284016163</v>
+        <v>2.572427220353317</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1109544912483228</v>
+        <v>0.1109049195811509</v>
       </c>
       <c r="C85">
-        <v>14.41159209681214</v>
+        <v>13.82575562713015</v>
       </c>
       <c r="D85">
-        <v>67.19559209681215</v>
+        <v>67.24675562713016</v>
       </c>
       <c r="E85">
-        <v>22.27100000000001</v>
+        <v>22.90800000000001</v>
       </c>
       <c r="F85">
-        <v>52.87100000000001</v>
+        <v>53.50800000000001</v>
       </c>
       <c r="G85">
         <v>0.08699999999999999</v>
@@ -8245,28 +8245,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M85">
-        <v>3.801424900000001</v>
+        <v>3.847225200000001</v>
       </c>
       <c r="N85">
-        <v>5.977463988888889</v>
+        <v>5.931663688888889</v>
       </c>
       <c r="O85">
-        <v>1.315042077555556</v>
+        <v>1.304966011555556</v>
       </c>
       <c r="P85">
-        <v>4.662421911333333</v>
+        <v>4.626697677333333</v>
       </c>
       <c r="Q85">
-        <v>13.77242191133333</v>
+        <v>13.73669767733333</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3788613602842517</v>
+        <v>0.3987252473821931</v>
       </c>
       <c r="T85">
-        <v>4.584714990268315</v>
+        <v>4.858148873037561</v>
       </c>
       <c r="U85">
         <v>0.07190000000000001</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.572427220353317</v>
+        <v>2.541803086777683</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1109049195811509</v>
+        <v>0.110855347913979</v>
       </c>
       <c r="C86">
-        <v>13.82575562713014</v>
+        <v>13.23999712986942</v>
       </c>
       <c r="D86">
-        <v>67.24675562713014</v>
+        <v>67.29799712986942</v>
       </c>
       <c r="E86">
-        <v>22.908</v>
+        <v>23.545</v>
       </c>
       <c r="F86">
-        <v>53.508</v>
+        <v>54.145</v>
       </c>
       <c r="G86">
         <v>0.08699999999999999</v>
@@ -8327,28 +8327,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M86">
-        <v>3.8472252</v>
+        <v>3.893025500000001</v>
       </c>
       <c r="N86">
-        <v>5.931663688888889</v>
+        <v>5.88586338888889</v>
       </c>
       <c r="O86">
-        <v>1.304966011555556</v>
+        <v>1.294889945555556</v>
       </c>
       <c r="P86">
-        <v>4.626697677333333</v>
+        <v>4.590973443333334</v>
       </c>
       <c r="Q86">
-        <v>13.73669767733333</v>
+        <v>13.70097344333333</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3987252473821929</v>
+        <v>0.4212376527598597</v>
       </c>
       <c r="T86">
-        <v>4.858148873037558</v>
+        <v>5.168040606842701</v>
       </c>
       <c r="U86">
         <v>0.07190000000000001</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.541803086777683</v>
+        <v>2.511899521050887</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.110855347913979</v>
+        <v>0.1134218962468071</v>
       </c>
       <c r="C87">
-        <v>13.23999712986942</v>
+        <v>10.04874219288971</v>
       </c>
       <c r="D87">
-        <v>67.29799712986942</v>
+        <v>64.74374219288971</v>
       </c>
       <c r="E87">
-        <v>23.545</v>
+        <v>24.182</v>
       </c>
       <c r="F87">
-        <v>54.145</v>
+        <v>54.782</v>
       </c>
       <c r="G87">
         <v>0.08699999999999999</v>
@@ -8409,45 +8409,45 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M87">
-        <v>3.893025500000001</v>
+        <v>4.152475600000001</v>
       </c>
       <c r="N87">
-        <v>5.88586338888889</v>
+        <v>5.626413288888889</v>
       </c>
       <c r="O87">
-        <v>1.294889945555556</v>
+        <v>1.237810923555556</v>
       </c>
       <c r="P87">
-        <v>4.590973443333334</v>
+        <v>4.388602365333334</v>
       </c>
       <c r="Q87">
-        <v>13.70097344333333</v>
+        <v>13.49860236533333</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4212376527598597</v>
+        <v>0.4469661160486219</v>
       </c>
       <c r="T87">
-        <v>5.168040606842701</v>
+        <v>5.522202588334293</v>
       </c>
       <c r="U87">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V87">
         <v>0.22</v>
       </c>
       <c r="W87">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y87">
-        <v>2.511899521050887</v>
+        <v>2.354953967433039</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1134218962468071</v>
+        <v>0.1134027445796352</v>
       </c>
       <c r="C88">
-        <v>10.04874219288971</v>
+        <v>9.430083912736315</v>
       </c>
       <c r="D88">
-        <v>64.74374219288971</v>
+        <v>64.76208391273632</v>
       </c>
       <c r="E88">
-        <v>24.182</v>
+        <v>24.819</v>
       </c>
       <c r="F88">
-        <v>54.782</v>
+        <v>55.419</v>
       </c>
       <c r="G88">
         <v>0.08699999999999999</v>
@@ -8491,28 +8491,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M88">
-        <v>4.152475600000001</v>
+        <v>4.2007602</v>
       </c>
       <c r="N88">
-        <v>5.626413288888889</v>
+        <v>5.578128688888889</v>
       </c>
       <c r="O88">
-        <v>1.237810923555556</v>
+        <v>1.227188311555556</v>
       </c>
       <c r="P88">
-        <v>4.388602365333334</v>
+        <v>4.350940377333334</v>
       </c>
       <c r="Q88">
-        <v>13.49860236533333</v>
+        <v>13.46094037733333</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4469661160486219</v>
+        <v>0.476652804458732</v>
       </c>
       <c r="T88">
-        <v>5.522202588334293</v>
+        <v>5.9308510285169</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.354953967433039</v>
+        <v>2.327885531025763</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1134027445796352</v>
+        <v>0.1133835929124633</v>
       </c>
       <c r="C89">
-        <v>9.430083912736315</v>
+        <v>8.811436027843037</v>
       </c>
       <c r="D89">
-        <v>64.76208391273632</v>
+        <v>64.78043602784304</v>
       </c>
       <c r="E89">
-        <v>24.819</v>
+        <v>25.456</v>
       </c>
       <c r="F89">
-        <v>55.419</v>
+        <v>56.056</v>
       </c>
       <c r="G89">
         <v>0.08699999999999999</v>
@@ -8573,28 +8573,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M89">
-        <v>4.2007602</v>
+        <v>4.249044800000001</v>
       </c>
       <c r="N89">
-        <v>5.578128688888889</v>
+        <v>5.529844088888889</v>
       </c>
       <c r="O89">
-        <v>1.227188311555556</v>
+        <v>1.216565699555556</v>
       </c>
       <c r="P89">
-        <v>4.350940377333334</v>
+        <v>4.313278389333333</v>
       </c>
       <c r="Q89">
-        <v>13.46094037733333</v>
+        <v>13.42327838933333</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.476652804458732</v>
+        <v>0.5112872742705272</v>
       </c>
       <c r="T89">
-        <v>5.9308510285169</v>
+        <v>6.407607542063276</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.327885531025763</v>
+        <v>2.301432286355015</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1133835929124633</v>
+        <v>0.1133644412452914</v>
       </c>
       <c r="C90">
-        <v>8.811436027843037</v>
+        <v>8.192798547049712</v>
       </c>
       <c r="D90">
-        <v>64.78043602784304</v>
+        <v>64.79879854704971</v>
       </c>
       <c r="E90">
-        <v>25.456</v>
+        <v>26.093</v>
       </c>
       <c r="F90">
-        <v>56.056</v>
+        <v>56.693</v>
       </c>
       <c r="G90">
         <v>0.08699999999999999</v>
@@ -8655,28 +8655,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M90">
-        <v>4.249044800000001</v>
+        <v>4.297329400000001</v>
       </c>
       <c r="N90">
-        <v>5.529844088888889</v>
+        <v>5.481559488888889</v>
       </c>
       <c r="O90">
-        <v>1.216565699555556</v>
+        <v>1.205943087555556</v>
       </c>
       <c r="P90">
-        <v>4.313278389333333</v>
+        <v>4.275616401333334</v>
       </c>
       <c r="Q90">
-        <v>13.42327838933333</v>
+        <v>13.38561640133333</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5112872742705272</v>
+        <v>0.5522189204117397</v>
       </c>
       <c r="T90">
-        <v>6.407607542063276</v>
+        <v>6.971047058072628</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.301432286355015</v>
+        <v>2.275573496620689</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1133644412452914</v>
+        <v>0.1133452895781195</v>
       </c>
       <c r="C91">
-        <v>8.192798547049712</v>
+        <v>7.574171479206264</v>
       </c>
       <c r="D91">
-        <v>64.79879854704971</v>
+        <v>64.81717147920627</v>
       </c>
       <c r="E91">
-        <v>26.093</v>
+        <v>26.73</v>
       </c>
       <c r="F91">
-        <v>56.693</v>
+        <v>57.33000000000001</v>
       </c>
       <c r="G91">
         <v>0.08699999999999999</v>
@@ -8737,28 +8737,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M91">
-        <v>4.297329400000001</v>
+        <v>4.345614000000001</v>
       </c>
       <c r="N91">
-        <v>5.481559488888889</v>
+        <v>5.433274888888889</v>
       </c>
       <c r="O91">
-        <v>1.205943087555556</v>
+        <v>1.195320475555556</v>
       </c>
       <c r="P91">
-        <v>4.275616401333334</v>
+        <v>4.237954413333333</v>
       </c>
       <c r="Q91">
-        <v>13.38561640133333</v>
+        <v>13.34795441333333</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5522189204117397</v>
+        <v>0.6013368957811948</v>
       </c>
       <c r="T91">
-        <v>6.971047058072628</v>
+        <v>7.647174477283851</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.275573496620689</v>
+        <v>2.250289346658237</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1133452895781195</v>
+        <v>0.1133261379109476</v>
       </c>
       <c r="C92">
-        <v>7.574171479206264</v>
+        <v>6.955554833172563</v>
       </c>
       <c r="D92">
-        <v>64.81717147920627</v>
+        <v>64.83555483317257</v>
       </c>
       <c r="E92">
-        <v>26.73</v>
+        <v>27.367</v>
       </c>
       <c r="F92">
-        <v>57.33000000000001</v>
+        <v>57.96700000000001</v>
       </c>
       <c r="G92">
         <v>0.08699999999999999</v>
@@ -8819,28 +8819,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M92">
-        <v>4.345614000000001</v>
+        <v>4.393898600000001</v>
       </c>
       <c r="N92">
-        <v>5.433274888888889</v>
+        <v>5.384990288888889</v>
       </c>
       <c r="O92">
-        <v>1.195320475555556</v>
+        <v>1.184697863555556</v>
       </c>
       <c r="P92">
-        <v>4.237954413333333</v>
+        <v>4.200292425333333</v>
       </c>
       <c r="Q92">
-        <v>13.34795441333333</v>
+        <v>13.31029242533333</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6013368957811948</v>
+        <v>0.6613699767883064</v>
       </c>
       <c r="T92">
-        <v>7.647174477283851</v>
+        <v>8.473552434097568</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.250289346658237</v>
+        <v>2.225560892299355</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1133261379109476</v>
+        <v>0.1133069862437757</v>
       </c>
       <c r="C93">
-        <v>6.955554833172563</v>
+        <v>6.336948617818571</v>
       </c>
       <c r="D93">
-        <v>64.83555483317257</v>
+        <v>64.85394861781857</v>
       </c>
       <c r="E93">
-        <v>27.367</v>
+        <v>28.004</v>
       </c>
       <c r="F93">
-        <v>57.96700000000001</v>
+        <v>58.60400000000001</v>
       </c>
       <c r="G93">
         <v>0.08699999999999999</v>
@@ -8901,28 +8901,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M93">
-        <v>4.393898600000001</v>
+        <v>4.442183200000001</v>
       </c>
       <c r="N93">
-        <v>5.384990288888889</v>
+        <v>5.336705688888889</v>
       </c>
       <c r="O93">
-        <v>1.184697863555556</v>
+        <v>1.174075251555556</v>
       </c>
       <c r="P93">
-        <v>4.200292425333333</v>
+        <v>4.162630437333334</v>
       </c>
       <c r="Q93">
-        <v>13.31029242533333</v>
+        <v>13.27263043733333</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6613699767883064</v>
+        <v>0.7364113280471962</v>
       </c>
       <c r="T93">
-        <v>8.473552434097568</v>
+        <v>9.506524880114716</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.225560892299355</v>
+        <v>2.201370013035232</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1133069862437757</v>
+        <v>0.1132878345766038</v>
       </c>
       <c r="C94">
-        <v>6.336948617818571</v>
+        <v>5.718352842024395</v>
       </c>
       <c r="D94">
-        <v>64.85394861781857</v>
+        <v>64.8723528420244</v>
       </c>
       <c r="E94">
-        <v>28.004</v>
+        <v>28.64100000000001</v>
       </c>
       <c r="F94">
-        <v>58.60400000000001</v>
+        <v>59.24100000000001</v>
       </c>
       <c r="G94">
         <v>0.08699999999999999</v>
@@ -8983,28 +8983,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M94">
-        <v>4.442183200000001</v>
+        <v>4.490467800000001</v>
       </c>
       <c r="N94">
-        <v>5.336705688888889</v>
+        <v>5.288421088888889</v>
       </c>
       <c r="O94">
-        <v>1.174075251555556</v>
+        <v>1.163452639555556</v>
       </c>
       <c r="P94">
-        <v>4.162630437333334</v>
+        <v>4.124968449333333</v>
       </c>
       <c r="Q94">
-        <v>13.27263043733333</v>
+        <v>13.23496844933333</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7364113280471962</v>
+        <v>0.8328930653800544</v>
       </c>
       <c r="T94">
-        <v>9.506524880114716</v>
+        <v>10.83463231070819</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.201370013035232</v>
+        <v>2.177699367733778</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1132878345766038</v>
+        <v>0.1132686829094319</v>
       </c>
       <c r="C95">
-        <v>5.718352842024395</v>
+        <v>5.099767514680089</v>
       </c>
       <c r="D95">
-        <v>64.8723528420244</v>
+        <v>64.89076751468009</v>
       </c>
       <c r="E95">
-        <v>28.64100000000001</v>
+        <v>29.27800000000001</v>
       </c>
       <c r="F95">
-        <v>59.24100000000001</v>
+        <v>59.87800000000001</v>
       </c>
       <c r="G95">
         <v>0.08699999999999999</v>
@@ -9065,28 +9065,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M95">
-        <v>4.490467800000001</v>
+        <v>4.538752400000001</v>
       </c>
       <c r="N95">
-        <v>5.288421088888889</v>
+        <v>5.240136488888889</v>
       </c>
       <c r="O95">
-        <v>1.163452639555556</v>
+        <v>1.152830027555556</v>
       </c>
       <c r="P95">
-        <v>4.124968449333333</v>
+        <v>4.087306461333333</v>
       </c>
       <c r="Q95">
-        <v>13.23496844933333</v>
+        <v>13.19730646133333</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8328930653800544</v>
+        <v>0.9615353818238654</v>
       </c>
       <c r="T95">
-        <v>10.83463231070819</v>
+        <v>12.60544221816616</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.177699367733778</v>
+        <v>2.154532353183418</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1132686829094319</v>
+        <v>0.11324953124226</v>
       </c>
       <c r="C96">
-        <v>5.099767514680089</v>
+        <v>4.481192644685898</v>
       </c>
       <c r="D96">
-        <v>64.89076751468009</v>
+        <v>64.9091926446859</v>
       </c>
       <c r="E96">
-        <v>29.27800000000001</v>
+        <v>29.91500000000001</v>
       </c>
       <c r="F96">
-        <v>59.87800000000001</v>
+        <v>60.51500000000001</v>
       </c>
       <c r="G96">
         <v>0.08699999999999999</v>
@@ -9147,28 +9147,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M96">
-        <v>4.538752400000001</v>
+        <v>4.587037000000001</v>
       </c>
       <c r="N96">
-        <v>5.240136488888889</v>
+        <v>5.191851888888888</v>
       </c>
       <c r="O96">
-        <v>1.152830027555556</v>
+        <v>1.142207415555555</v>
       </c>
       <c r="P96">
-        <v>4.087306461333333</v>
+        <v>4.049644473333333</v>
       </c>
       <c r="Q96">
-        <v>13.19730646133333</v>
+        <v>13.15964447333333</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9615353818238654</v>
+        <v>1.141634624845201</v>
       </c>
       <c r="T96">
-        <v>12.60544221816616</v>
+        <v>15.08457608860732</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.154532353183418</v>
+        <v>2.131853065255171</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.11324953124226</v>
+        <v>0.1132303795750881</v>
       </c>
       <c r="C97">
-        <v>4.481192644685898</v>
+        <v>3.862628240952169</v>
       </c>
       <c r="D97">
-        <v>64.9091926446859</v>
+        <v>64.92762824095217</v>
       </c>
       <c r="E97">
-        <v>29.91500000000001</v>
+        <v>30.55200000000001</v>
       </c>
       <c r="F97">
-        <v>60.51500000000001</v>
+        <v>61.15200000000001</v>
       </c>
       <c r="G97">
         <v>0.08699999999999999</v>
@@ -9229,28 +9229,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M97">
-        <v>4.587037000000001</v>
+        <v>4.635321600000001</v>
       </c>
       <c r="N97">
-        <v>5.191851888888888</v>
+        <v>5.143567288888889</v>
       </c>
       <c r="O97">
-        <v>1.142207415555555</v>
+        <v>1.131584803555556</v>
       </c>
       <c r="P97">
-        <v>4.049644473333333</v>
+        <v>4.011982485333333</v>
       </c>
       <c r="Q97">
-        <v>13.15964447333333</v>
+        <v>13.12198248533333</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.141634624845201</v>
+        <v>1.411783489377205</v>
       </c>
       <c r="T97">
-        <v>15.08457608860732</v>
+        <v>18.80327689426905</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.131853065255171</v>
+        <v>2.109646262492097</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1132303795750881</v>
+        <v>0.1132112279079162</v>
       </c>
       <c r="C98">
-        <v>3.862628240952162</v>
+        <v>3.244074312399334</v>
       </c>
       <c r="D98">
-        <v>64.92762824095216</v>
+        <v>64.94607431239933</v>
       </c>
       <c r="E98">
-        <v>30.552</v>
+        <v>31.189</v>
       </c>
       <c r="F98">
-        <v>61.152</v>
+        <v>61.789</v>
       </c>
       <c r="G98">
         <v>0.08699999999999999</v>
@@ -9311,28 +9311,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M98">
-        <v>4.6353216</v>
+        <v>4.683606200000001</v>
       </c>
       <c r="N98">
-        <v>5.14356728888889</v>
+        <v>5.095282688888889</v>
       </c>
       <c r="O98">
-        <v>1.131584803555556</v>
+        <v>1.120962191555556</v>
       </c>
       <c r="P98">
-        <v>4.011982485333334</v>
+        <v>3.974320497333333</v>
       </c>
       <c r="Q98">
-        <v>13.12198248533333</v>
+        <v>13.08432049733333</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.411783489377201</v>
+        <v>1.862031596930538</v>
       </c>
       <c r="T98">
-        <v>18.803276894269</v>
+        <v>25.00111157037187</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.109646262492098</v>
+        <v>2.087897331950942</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1132112279079162</v>
+        <v>0.1131920762407443</v>
       </c>
       <c r="C99">
-        <v>3.244074312399334</v>
+        <v>2.625530867958034</v>
       </c>
       <c r="D99">
-        <v>64.94607431239933</v>
+        <v>64.96453086795803</v>
       </c>
       <c r="E99">
-        <v>31.189</v>
+        <v>31.826</v>
       </c>
       <c r="F99">
-        <v>61.789</v>
+        <v>62.426</v>
       </c>
       <c r="G99">
         <v>0.08699999999999999</v>
@@ -9393,28 +9393,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M99">
-        <v>4.683606200000001</v>
+        <v>4.7318908</v>
       </c>
       <c r="N99">
-        <v>5.095282688888889</v>
+        <v>5.046998088888889</v>
       </c>
       <c r="O99">
-        <v>1.120962191555556</v>
+        <v>1.110339579555556</v>
       </c>
       <c r="P99">
-        <v>3.974320497333333</v>
+        <v>3.936658509333334</v>
       </c>
       <c r="Q99">
-        <v>13.08432049733333</v>
+        <v>13.04665850933333</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.862031596930538</v>
+        <v>2.762527812037212</v>
       </c>
       <c r="T99">
-        <v>25.00111157037187</v>
+        <v>37.3967809225776</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.087897331950942</v>
+        <v>2.066592257135116</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1131920762407443</v>
+        <v>0.1131729245735724</v>
       </c>
       <c r="C100">
-        <v>2.625530867958034</v>
+        <v>2.006997916568977</v>
       </c>
       <c r="D100">
-        <v>64.96453086795803</v>
+        <v>64.98299791656898</v>
       </c>
       <c r="E100">
-        <v>31.826</v>
+        <v>32.463</v>
       </c>
       <c r="F100">
-        <v>62.426</v>
+        <v>63.063</v>
       </c>
       <c r="G100">
         <v>0.08699999999999999</v>
@@ -9475,28 +9475,28 @@
         <v>9.77888888888889</v>
       </c>
       <c r="M100">
-        <v>4.7318908</v>
+        <v>4.780175400000001</v>
       </c>
       <c r="N100">
-        <v>5.046998088888889</v>
+        <v>4.998713488888889</v>
       </c>
       <c r="O100">
-        <v>1.110339579555556</v>
+        <v>1.099716967555556</v>
       </c>
       <c r="P100">
-        <v>3.936658509333334</v>
+        <v>3.898996521333333</v>
       </c>
       <c r="Q100">
-        <v>13.04665850933333</v>
+        <v>13.00899652133333</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.762527812037212</v>
+        <v>5.464016457357234</v>
       </c>
       <c r="T100">
-        <v>37.3967809225776</v>
+        <v>74.58378897919479</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.066592257135116</v>
+        <v>2.045717587871124</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1131729245735724</v>
-      </c>
-      <c r="C101">
-        <v>2.006997916568977</v>
-      </c>
-      <c r="D101">
-        <v>64.98299791656898</v>
-      </c>
-      <c r="E101">
-        <v>32.463</v>
-      </c>
-      <c r="F101">
-        <v>63.063</v>
-      </c>
-      <c r="G101">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="H101">
-        <v>33.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>18.88888888888889</v>
-      </c>
-      <c r="K101">
-        <v>9.109999999999999</v>
-      </c>
-      <c r="L101">
-        <v>9.77888888888889</v>
-      </c>
-      <c r="M101">
-        <v>4.780175400000001</v>
-      </c>
-      <c r="N101">
-        <v>4.998713488888889</v>
-      </c>
-      <c r="O101">
-        <v>1.099716967555556</v>
-      </c>
-      <c r="P101">
-        <v>3.898996521333333</v>
-      </c>
-      <c r="Q101">
-        <v>13.00899652133333</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.464016457357234</v>
-      </c>
-      <c r="T101">
-        <v>74.58378897919479</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.22</v>
-      </c>
-      <c r="W101">
-        <v>0.05912400000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.045717587871124</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
